--- a/個人別作業達成度と改善分析_2026.4_目標到達分析.xlsx
+++ b/個人別作業達成度と改善分析_2026.4_目標到達分析.xlsx
@@ -23286,12 +23286,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:M65"/>
+  <dimension ref="B1:P65"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="13" width="11.5" customWidth="1"/>
+    <col min="3" max="16" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -23304,7 +23304,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="B2" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">目標＝1.6分/個。各担当者が目標に到達するには「1個あたり何分縮めるか（必要短縮）」を算出。件数を掛けた「短縮効果（分）」＝目標達成で減らせる総作業時間。実績が目標より速い人は必要短縮0（達成）。</t>
+          <t xml:space="preserve">目標＝1.6分/個。必要短縮＝目標到達に1個あたり縮める分。短縮効果(分)＝必要短縮×件数。追加可能件数＝短縮効果(分)÷目標1.6分/個（浮いた時間で追加処理できる件数）。</t>
         </is>
       </c>
     </row>
@@ -23388,7 +23388,7 @@
     <row r="10" ht="16" customHeight="1">
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">▼ 担当者別：目標(1.6分/個)に到達するための 1個あたり短縮 と 短縮効果（分）</t>
+          <t xml:space="preserve">▼ 担当者別：目標(1.6分/個)到達に必要な 1個あたり短縮・短縮効果(分)、および短縮効果で追加処理できる件数</t>
         </is>
       </c>
     </row>
@@ -23407,22 +23407,30 @@
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="25"/>
+      <c r="I11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">梱包（目標 1.6 分/個）</t>
         </is>
       </c>
-      <c r="I11" s="25"/>
       <c r="J11" s="25"/>
       <c r="K11" s="25"/>
       <c r="L11" s="25"/>
-      <c r="M11" s="25" t="inlineStr">
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">合計短縮効果(分)</t>
         </is>
       </c>
+      <c r="P11" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合計追加可能件数</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="25"/>
       <c r="C12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">現状(分/個)</t>
@@ -23450,31 +23458,41 @@
       </c>
       <c r="H12" s="25" t="inlineStr">
         <is>
+          <t xml:space="preserve">追加可能件数</t>
+        </is>
+      </c>
+      <c r="I12" s="25" t="inlineStr">
+        <is>
           <t xml:space="preserve">現状(分/個)</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="J12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">必要短縮(分/個)</t>
         </is>
       </c>
-      <c r="J12" s="25" t="inlineStr">
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">件数</t>
         </is>
       </c>
-      <c r="K12" s="25" t="inlineStr">
+      <c r="L12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">現状総時間(分)</t>
         </is>
       </c>
-      <c r="L12" s="25" t="inlineStr">
+      <c r="M12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">短縮効果(分)</t>
         </is>
       </c>
-      <c r="B12" s="25"/>
-      <c r="M12" s="25"/>
+      <c r="N12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">追加可能件数</t>
+        </is>
+      </c>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
     </row>
     <row r="13">
       <c r="B13" s="7" t="str">
@@ -23501,28 +23519,40 @@
         <f>IF(AND(ISNUMBER(入力!$C9),ISNUMBER(入力!$O9)),MAX(0,入力!$C9-入力!$B$5)*入力!$O9,"")</f>
         <v>0</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
+        <f>IF(ISNUMBER(G13),ROUND(G13/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
         <f>IF(入力!$B9="","",IF(ISNUMBER(入力!$D9),入力!$D9,""))</f>
         <v>0.5</v>
       </c>
-      <c r="I13" s="5">
+      <c r="J13" s="5">
         <f>IF(ISNUMBER(入力!$D9),MAX(0,入力!$D9-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="J13" s="4">
+      <c r="K13" s="4">
         <f>IF(入力!$B9="","",IF(ISNUMBER(入力!$P9),入力!$P9,""))</f>
         <v>505</v>
       </c>
-      <c r="K13" s="5">
+      <c r="L13" s="5">
         <f>IF(AND(ISNUMBER(入力!$D9),ISNUMBER(入力!$P9)),入力!$D9*入力!$P9,"")</f>
         <v>252.5</v>
       </c>
-      <c r="L13" s="5">
+      <c r="M13" s="5">
         <f>IF(AND(ISNUMBER(入力!$D9),ISNUMBER(入力!$P9)),MAX(0,入力!$D9-入力!$C$5)*入力!$P9,"")</f>
         <v>0</v>
       </c>
-      <c r="M13" s="5">
-        <f>IF(入力!$B9="","",IF(AND(NOT(ISNUMBER(G13)),NOT(ISNUMBER(L13))),"",IF(ISNUMBER(G13),G13,0)+IF(ISNUMBER(L13),L13,0)))</f>
+      <c r="N13" s="4">
+        <f>IF(ISNUMBER(M13),ROUND(M13/入力!$C$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="5">
+        <f>IF(入力!$B9="","",IF(AND(NOT(ISNUMBER(G13)),NOT(ISNUMBER(M13))),"",IF(ISNUMBER(G13),G13,0)+IF(ISNUMBER(M13),M13,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="4">
+        <f>IF(入力!$B9="","",IF(AND(NOT(ISNUMBER(H13)),NOT(ISNUMBER(N13))),"",IF(ISNUMBER(H13),H13,0)+IF(ISNUMBER(N13),N13,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -23551,28 +23581,40 @@
         <f>IF(AND(ISNUMBER(入力!$C10),ISNUMBER(入力!$O10)),MAX(0,入力!$C10-入力!$B$5)*入力!$O10,"")</f>
         <v>0</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
+        <f>IF(ISNUMBER(G14),ROUND(G14/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
         <f>IF(入力!$B10="","",IF(ISNUMBER(入力!$D10),入力!$D10,""))</f>
         <v>1</v>
       </c>
-      <c r="I14" s="5">
+      <c r="J14" s="5">
         <f>IF(ISNUMBER(入力!$D10),MAX(0,入力!$D10-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="J14" s="4">
+      <c r="K14" s="4">
         <f>IF(入力!$B10="","",IF(ISNUMBER(入力!$P10),入力!$P10,""))</f>
         <v>656</v>
       </c>
-      <c r="K14" s="5">
+      <c r="L14" s="5">
         <f>IF(AND(ISNUMBER(入力!$D10),ISNUMBER(入力!$P10)),入力!$D10*入力!$P10,"")</f>
         <v>656</v>
       </c>
-      <c r="L14" s="5">
+      <c r="M14" s="5">
         <f>IF(AND(ISNUMBER(入力!$D10),ISNUMBER(入力!$P10)),MAX(0,入力!$D10-入力!$C$5)*入力!$P10,"")</f>
         <v>0</v>
       </c>
-      <c r="M14" s="5">
-        <f>IF(入力!$B10="","",IF(AND(NOT(ISNUMBER(G14)),NOT(ISNUMBER(L14))),"",IF(ISNUMBER(G14),G14,0)+IF(ISNUMBER(L14),L14,0)))</f>
+      <c r="N14" s="4">
+        <f>IF(ISNUMBER(M14),ROUND(M14/入力!$C$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="5">
+        <f>IF(入力!$B10="","",IF(AND(NOT(ISNUMBER(G14)),NOT(ISNUMBER(M14))),"",IF(ISNUMBER(G14),G14,0)+IF(ISNUMBER(M14),M14,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="4">
+        <f>IF(入力!$B10="","",IF(AND(NOT(ISNUMBER(H14)),NOT(ISNUMBER(N14))),"",IF(ISNUMBER(H14),H14,0)+IF(ISNUMBER(N14),N14,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -23601,29 +23643,41 @@
         <f>IF(AND(ISNUMBER(入力!$C11),ISNUMBER(入力!$O11)),MAX(0,入力!$C11-入力!$B$5)*入力!$O11,"")</f>
         <v>0</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
+        <f>IF(ISNUMBER(G15),ROUND(G15/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
         <f>IF(入力!$B11="","",IF(ISNUMBER(入力!$D11),入力!$D11,""))</f>
         <v>2.1</v>
       </c>
-      <c r="I15" s="5">
+      <c r="J15" s="5">
         <f>IF(ISNUMBER(入力!$D11),MAX(0,入力!$D11-入力!$C$5),"")</f>
         <v>0.5</v>
       </c>
-      <c r="J15" s="4">
+      <c r="K15" s="4">
         <f>IF(入力!$B11="","",IF(ISNUMBER(入力!$P11),入力!$P11,""))</f>
         <v>224</v>
       </c>
-      <c r="K15" s="5">
+      <c r="L15" s="5">
         <f>IF(AND(ISNUMBER(入力!$D11),ISNUMBER(入力!$P11)),入力!$D11*入力!$P11,"")</f>
         <v>470.4</v>
       </c>
-      <c r="L15" s="5">
+      <c r="M15" s="5">
         <f>IF(AND(ISNUMBER(入力!$D11),ISNUMBER(入力!$P11)),MAX(0,入力!$D11-入力!$C$5)*入力!$P11,"")</f>
         <v>112</v>
       </c>
-      <c r="M15" s="5">
-        <f>IF(入力!$B11="","",IF(AND(NOT(ISNUMBER(G15)),NOT(ISNUMBER(L15))),"",IF(ISNUMBER(G15),G15,0)+IF(ISNUMBER(L15),L15,0)))</f>
+      <c r="N15" s="4">
+        <f>IF(ISNUMBER(M15),ROUND(M15/入力!$C$5,0),"")</f>
+        <v>70</v>
+      </c>
+      <c r="O15" s="5">
+        <f>IF(入力!$B11="","",IF(AND(NOT(ISNUMBER(G15)),NOT(ISNUMBER(M15))),"",IF(ISNUMBER(G15),G15,0)+IF(ISNUMBER(M15),M15,0)))</f>
         <v>112</v>
+      </c>
+      <c r="P15" s="4">
+        <f>IF(入力!$B11="","",IF(AND(NOT(ISNUMBER(H15)),NOT(ISNUMBER(N15))),"",IF(ISNUMBER(H15),H15,0)+IF(ISNUMBER(N15),N15,0)))</f>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -23651,28 +23705,40 @@
         <f>IF(AND(ISNUMBER(入力!$C12),ISNUMBER(入力!$O12)),MAX(0,入力!$C12-入力!$B$5)*入力!$O12,"")</f>
         <v>0</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
+        <f>IF(ISNUMBER(G16),ROUND(G16/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
         <f>IF(入力!$B12="","",IF(ISNUMBER(入力!$D12),入力!$D12,""))</f>
         <v>1.6</v>
       </c>
-      <c r="I16" s="5">
+      <c r="J16" s="5">
         <f>IF(ISNUMBER(入力!$D12),MAX(0,入力!$D12-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="J16" s="4">
+      <c r="K16" s="4">
         <f>IF(入力!$B12="","",IF(ISNUMBER(入力!$P12),入力!$P12,""))</f>
         <v>939</v>
       </c>
-      <c r="K16" s="5">
+      <c r="L16" s="5">
         <f>IF(AND(ISNUMBER(入力!$D12),ISNUMBER(入力!$P12)),入力!$D12*入力!$P12,"")</f>
         <v>1502.4</v>
       </c>
-      <c r="L16" s="5">
+      <c r="M16" s="5">
         <f>IF(AND(ISNUMBER(入力!$D12),ISNUMBER(入力!$P12)),MAX(0,入力!$D12-入力!$C$5)*入力!$P12,"")</f>
         <v>0</v>
       </c>
-      <c r="M16" s="5">
-        <f>IF(入力!$B12="","",IF(AND(NOT(ISNUMBER(G16)),NOT(ISNUMBER(L16))),"",IF(ISNUMBER(G16),G16,0)+IF(ISNUMBER(L16),L16,0)))</f>
+      <c r="N16" s="4">
+        <f>IF(ISNUMBER(M16),ROUND(M16/入力!$C$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="5">
+        <f>IF(入力!$B12="","",IF(AND(NOT(ISNUMBER(G16)),NOT(ISNUMBER(M16))),"",IF(ISNUMBER(G16),G16,0)+IF(ISNUMBER(M16),M16,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="4">
+        <f>IF(入力!$B12="","",IF(AND(NOT(ISNUMBER(H16)),NOT(ISNUMBER(N16))),"",IF(ISNUMBER(H16),H16,0)+IF(ISNUMBER(N16),N16,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -23701,29 +23767,41 @@
         <f>IF(AND(ISNUMBER(入力!$C13),ISNUMBER(入力!$O13)),MAX(0,入力!$C13-入力!$B$5)*入力!$O13,"")</f>
         <v>68.1</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
+        <f>IF(ISNUMBER(G17),ROUND(G17/入力!$B$5,0),"")</f>
+        <v>43</v>
+      </c>
+      <c r="I17" s="5">
         <f>IF(入力!$B13="","",IF(ISNUMBER(入力!$D13),入力!$D13,""))</f>
         <v>0.6</v>
       </c>
-      <c r="I17" s="5">
+      <c r="J17" s="5">
         <f>IF(ISNUMBER(入力!$D13),MAX(0,入力!$D13-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="J17" s="4">
+      <c r="K17" s="4">
         <f>IF(入力!$B13="","",IF(ISNUMBER(入力!$P13),入力!$P13,""))</f>
         <v>1223</v>
       </c>
-      <c r="K17" s="5">
+      <c r="L17" s="5">
         <f>IF(AND(ISNUMBER(入力!$D13),ISNUMBER(入力!$P13)),入力!$D13*入力!$P13,"")</f>
         <v>733.8</v>
       </c>
-      <c r="L17" s="5">
+      <c r="M17" s="5">
         <f>IF(AND(ISNUMBER(入力!$D13),ISNUMBER(入力!$P13)),MAX(0,入力!$D13-入力!$C$5)*入力!$P13,"")</f>
         <v>0</v>
       </c>
-      <c r="M17" s="5">
-        <f>IF(入力!$B13="","",IF(AND(NOT(ISNUMBER(G17)),NOT(ISNUMBER(L17))),"",IF(ISNUMBER(G17),G17,0)+IF(ISNUMBER(L17),L17,0)))</f>
+      <c r="N17" s="4">
+        <f>IF(ISNUMBER(M17),ROUND(M17/入力!$C$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="5">
+        <f>IF(入力!$B13="","",IF(AND(NOT(ISNUMBER(G17)),NOT(ISNUMBER(M17))),"",IF(ISNUMBER(G17),G17,0)+IF(ISNUMBER(M17),M17,0)))</f>
         <v>68.1</v>
+      </c>
+      <c r="P17" s="4">
+        <f>IF(入力!$B13="","",IF(AND(NOT(ISNUMBER(H17)),NOT(ISNUMBER(N17))),"",IF(ISNUMBER(H17),H17,0)+IF(ISNUMBER(N17),N17,0)))</f>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -23751,29 +23829,41 @@
         <f>IF(AND(ISNUMBER(入力!$C14),ISNUMBER(入力!$O14)),MAX(0,入力!$C14-入力!$B$5)*入力!$O14,"")</f>
         <v>99</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
+        <f>IF(ISNUMBER(G18),ROUND(G18/入力!$B$5,0),"")</f>
+        <v>62</v>
+      </c>
+      <c r="I18" s="5">
         <f>IF(入力!$B14="","",IF(ISNUMBER(入力!$D14),入力!$D14,""))</f>
         <v>0.6</v>
       </c>
-      <c r="I18" s="5">
+      <c r="J18" s="5">
         <f>IF(ISNUMBER(入力!$D14),MAX(0,入力!$D14-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="J18" s="4">
+      <c r="K18" s="4">
         <f>IF(入力!$B14="","",IF(ISNUMBER(入力!$P14),入力!$P14,""))</f>
         <v>16</v>
       </c>
-      <c r="K18" s="5">
+      <c r="L18" s="5">
         <f>IF(AND(ISNUMBER(入力!$D14),ISNUMBER(入力!$P14)),入力!$D14*入力!$P14,"")</f>
         <v>9.6</v>
       </c>
-      <c r="L18" s="5">
+      <c r="M18" s="5">
         <f>IF(AND(ISNUMBER(入力!$D14),ISNUMBER(入力!$P14)),MAX(0,入力!$D14-入力!$C$5)*入力!$P14,"")</f>
         <v>0</v>
       </c>
-      <c r="M18" s="5">
-        <f>IF(入力!$B14="","",IF(AND(NOT(ISNUMBER(G18)),NOT(ISNUMBER(L18))),"",IF(ISNUMBER(G18),G18,0)+IF(ISNUMBER(L18),L18,0)))</f>
+      <c r="N18" s="4">
+        <f>IF(ISNUMBER(M18),ROUND(M18/入力!$C$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="5">
+        <f>IF(入力!$B14="","",IF(AND(NOT(ISNUMBER(G18)),NOT(ISNUMBER(M18))),"",IF(ISNUMBER(G18),G18,0)+IF(ISNUMBER(M18),M18,0)))</f>
         <v>99</v>
+      </c>
+      <c r="P18" s="4">
+        <f>IF(入力!$B14="","",IF(AND(NOT(ISNUMBER(H18)),NOT(ISNUMBER(N18))),"",IF(ISNUMBER(H18),H18,0)+IF(ISNUMBER(N18),N18,0)))</f>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -23801,29 +23891,41 @@
         <f>IF(AND(ISNUMBER(入力!$C15),ISNUMBER(入力!$O15)),MAX(0,入力!$C15-入力!$B$5)*入力!$O15,"")</f>
         <v>0</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
+        <f>IF(ISNUMBER(G19),ROUND(G19/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
         <f>IF(入力!$B15="","",IF(ISNUMBER(入力!$D15),入力!$D15,""))</f>
         <v>1.9</v>
       </c>
-      <c r="I19" s="5">
+      <c r="J19" s="5">
         <f>IF(ISNUMBER(入力!$D15),MAX(0,入力!$D15-入力!$C$5),"")</f>
         <v>0.3</v>
       </c>
-      <c r="J19" s="4">
+      <c r="K19" s="4">
         <f>IF(入力!$B15="","",IF(ISNUMBER(入力!$P15),入力!$P15,""))</f>
         <v>1421</v>
       </c>
-      <c r="K19" s="5">
+      <c r="L19" s="5">
         <f>IF(AND(ISNUMBER(入力!$D15),ISNUMBER(入力!$P15)),入力!$D15*入力!$P15,"")</f>
         <v>2699.9</v>
       </c>
-      <c r="L19" s="5">
+      <c r="M19" s="5">
         <f>IF(AND(ISNUMBER(入力!$D15),ISNUMBER(入力!$P15)),MAX(0,入力!$D15-入力!$C$5)*入力!$P15,"")</f>
         <v>426.3</v>
       </c>
-      <c r="M19" s="5">
-        <f>IF(入力!$B15="","",IF(AND(NOT(ISNUMBER(G19)),NOT(ISNUMBER(L19))),"",IF(ISNUMBER(G19),G19,0)+IF(ISNUMBER(L19),L19,0)))</f>
+      <c r="N19" s="4">
+        <f>IF(ISNUMBER(M19),ROUND(M19/入力!$C$5,0),"")</f>
+        <v>266</v>
+      </c>
+      <c r="O19" s="5">
+        <f>IF(入力!$B15="","",IF(AND(NOT(ISNUMBER(G19)),NOT(ISNUMBER(M19))),"",IF(ISNUMBER(G19),G19,0)+IF(ISNUMBER(M19),M19,0)))</f>
         <v>426.3</v>
+      </c>
+      <c r="P19" s="4">
+        <f>IF(入力!$B15="","",IF(AND(NOT(ISNUMBER(H19)),NOT(ISNUMBER(N19))),"",IF(ISNUMBER(H19),H19,0)+IF(ISNUMBER(N19),N19,0)))</f>
+        <v>266</v>
       </c>
     </row>
     <row r="20">
@@ -23851,29 +23953,41 @@
         <f>IF(AND(ISNUMBER(入力!$C16),ISNUMBER(入力!$O16)),MAX(0,入力!$C16-入力!$B$5)*入力!$O16,"")</f>
         <v>0</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
+        <f>IF(ISNUMBER(G20),ROUND(G20/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="5">
         <f>IF(入力!$B16="","",IF(ISNUMBER(入力!$D16),入力!$D16,""))</f>
         <v>1.8</v>
       </c>
-      <c r="I20" s="5">
+      <c r="J20" s="5">
         <f>IF(ISNUMBER(入力!$D16),MAX(0,入力!$D16-入力!$C$5),"")</f>
         <v>0.2</v>
       </c>
-      <c r="J20" s="4">
+      <c r="K20" s="4">
         <f>IF(入力!$B16="","",IF(ISNUMBER(入力!$P16),入力!$P16,""))</f>
         <v>1548</v>
       </c>
-      <c r="K20" s="5">
+      <c r="L20" s="5">
         <f>IF(AND(ISNUMBER(入力!$D16),ISNUMBER(入力!$P16)),入力!$D16*入力!$P16,"")</f>
         <v>2786.4</v>
       </c>
-      <c r="L20" s="5">
+      <c r="M20" s="5">
         <f>IF(AND(ISNUMBER(入力!$D16),ISNUMBER(入力!$P16)),MAX(0,入力!$D16-入力!$C$5)*入力!$P16,"")</f>
         <v>309.6</v>
       </c>
-      <c r="M20" s="5">
-        <f>IF(入力!$B16="","",IF(AND(NOT(ISNUMBER(G20)),NOT(ISNUMBER(L20))),"",IF(ISNUMBER(G20),G20,0)+IF(ISNUMBER(L20),L20,0)))</f>
+      <c r="N20" s="4">
+        <f>IF(ISNUMBER(M20),ROUND(M20/入力!$C$5,0),"")</f>
+        <v>193</v>
+      </c>
+      <c r="O20" s="5">
+        <f>IF(入力!$B16="","",IF(AND(NOT(ISNUMBER(G20)),NOT(ISNUMBER(M20))),"",IF(ISNUMBER(G20),G20,0)+IF(ISNUMBER(M20),M20,0)))</f>
         <v>309.6</v>
+      </c>
+      <c r="P20" s="4">
+        <f>IF(入力!$B16="","",IF(AND(NOT(ISNUMBER(H20)),NOT(ISNUMBER(N20))),"",IF(ISNUMBER(H20),H20,0)+IF(ISNUMBER(N20),N20,0)))</f>
+        <v>193</v>
       </c>
     </row>
     <row r="21">
@@ -23901,28 +24015,40 @@
         <f>IF(AND(ISNUMBER(入力!$C17),ISNUMBER(入力!$O17)),MAX(0,入力!$C17-入力!$B$5)*入力!$O17,"")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="4">
+        <f>IF(ISNUMBER(G21),ROUND(G21/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="5">
         <f>IF(入力!$B17="","",IF(ISNUMBER(入力!$D17),入力!$D17,""))</f>
         <v>1</v>
       </c>
-      <c r="I21" s="5">
+      <c r="J21" s="5">
         <f>IF(ISNUMBER(入力!$D17),MAX(0,入力!$D17-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="J21" s="4">
+      <c r="K21" s="4">
         <f>IF(入力!$B17="","",IF(ISNUMBER(入力!$P17),入力!$P17,""))</f>
         <v>2493</v>
       </c>
-      <c r="K21" s="5">
+      <c r="L21" s="5">
         <f>IF(AND(ISNUMBER(入力!$D17),ISNUMBER(入力!$P17)),入力!$D17*入力!$P17,"")</f>
         <v>2493</v>
       </c>
-      <c r="L21" s="5">
+      <c r="M21" s="5">
         <f>IF(AND(ISNUMBER(入力!$D17),ISNUMBER(入力!$P17)),MAX(0,入力!$D17-入力!$C$5)*入力!$P17,"")</f>
         <v>0</v>
       </c>
-      <c r="M21" s="5">
-        <f>IF(入力!$B17="","",IF(AND(NOT(ISNUMBER(G21)),NOT(ISNUMBER(L21))),"",IF(ISNUMBER(G21),G21,0)+IF(ISNUMBER(L21),L21,0)))</f>
+      <c r="N21" s="4">
+        <f>IF(ISNUMBER(M21),ROUND(M21/入力!$C$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="5">
+        <f>IF(入力!$B17="","",IF(AND(NOT(ISNUMBER(G21)),NOT(ISNUMBER(M21))),"",IF(ISNUMBER(G21),G21,0)+IF(ISNUMBER(M21),M21,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="4">
+        <f>IF(入力!$B17="","",IF(AND(NOT(ISNUMBER(H21)),NOT(ISNUMBER(N21))),"",IF(ISNUMBER(H21),H21,0)+IF(ISNUMBER(N21),N21,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -23951,28 +24077,40 @@
         <f>IF(AND(ISNUMBER(入力!$C18),ISNUMBER(入力!$O18)),MAX(0,入力!$C18-入力!$B$5)*入力!$O18,"")</f>
         <v/>
       </c>
-      <c r="H22" s="5" t="str">
+      <c r="H22" s="4" t="str">
+        <f>IF(ISNUMBER(G22),ROUND(G22/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="5" t="str">
         <f>IF(入力!$B18="","",IF(ISNUMBER(入力!$D18),入力!$D18,""))</f>
         <v/>
       </c>
-      <c r="I22" s="5" t="str">
+      <c r="J22" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D18),MAX(0,入力!$D18-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J22" s="4" t="str">
+      <c r="K22" s="4" t="str">
         <f>IF(入力!$B18="","",IF(ISNUMBER(入力!$P18),入力!$P18,""))</f>
         <v/>
       </c>
-      <c r="K22" s="5" t="str">
+      <c r="L22" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D18),ISNUMBER(入力!$P18)),入力!$D18*入力!$P18,"")</f>
         <v/>
       </c>
-      <c r="L22" s="5" t="str">
+      <c r="M22" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D18),ISNUMBER(入力!$P18)),MAX(0,入力!$D18-入力!$C$5)*入力!$P18,"")</f>
         <v/>
       </c>
-      <c r="M22" s="5" t="str">
-        <f>IF(入力!$B18="","",IF(AND(NOT(ISNUMBER(G22)),NOT(ISNUMBER(L22))),"",IF(ISNUMBER(G22),G22,0)+IF(ISNUMBER(L22),L22,0)))</f>
+      <c r="N22" s="4" t="str">
+        <f>IF(ISNUMBER(M22),ROUND(M22/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O22" s="5" t="str">
+        <f>IF(入力!$B18="","",IF(AND(NOT(ISNUMBER(G22)),NOT(ISNUMBER(M22))),"",IF(ISNUMBER(G22),G22,0)+IF(ISNUMBER(M22),M22,0)))</f>
+        <v/>
+      </c>
+      <c r="P22" s="4" t="str">
+        <f>IF(入力!$B18="","",IF(AND(NOT(ISNUMBER(H22)),NOT(ISNUMBER(N22))),"",IF(ISNUMBER(H22),H22,0)+IF(ISNUMBER(N22),N22,0)))</f>
         <v/>
       </c>
     </row>
@@ -24001,28 +24139,40 @@
         <f>IF(AND(ISNUMBER(入力!$C19),ISNUMBER(入力!$O19)),MAX(0,入力!$C19-入力!$B$5)*入力!$O19,"")</f>
         <v>0</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
+        <f>IF(ISNUMBER(G23),ROUND(G23/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="5">
         <f>IF(入力!$B19="","",IF(ISNUMBER(入力!$D19),入力!$D19,""))</f>
         <v>1.2</v>
       </c>
-      <c r="I23" s="5">
+      <c r="J23" s="5">
         <f>IF(ISNUMBER(入力!$D19),MAX(0,入力!$D19-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="J23" s="4">
+      <c r="K23" s="4">
         <f>IF(入力!$B19="","",IF(ISNUMBER(入力!$P19),入力!$P19,""))</f>
         <v>2616</v>
       </c>
-      <c r="K23" s="5">
+      <c r="L23" s="5">
         <f>IF(AND(ISNUMBER(入力!$D19),ISNUMBER(入力!$P19)),入力!$D19*入力!$P19,"")</f>
         <v>3139.2</v>
       </c>
-      <c r="L23" s="5">
+      <c r="M23" s="5">
         <f>IF(AND(ISNUMBER(入力!$D19),ISNUMBER(入力!$P19)),MAX(0,入力!$D19-入力!$C$5)*入力!$P19,"")</f>
         <v>0</v>
       </c>
-      <c r="M23" s="5">
-        <f>IF(入力!$B19="","",IF(AND(NOT(ISNUMBER(G23)),NOT(ISNUMBER(L23))),"",IF(ISNUMBER(G23),G23,0)+IF(ISNUMBER(L23),L23,0)))</f>
+      <c r="N23" s="4">
+        <f>IF(ISNUMBER(M23),ROUND(M23/入力!$C$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="5">
+        <f>IF(入力!$B19="","",IF(AND(NOT(ISNUMBER(G23)),NOT(ISNUMBER(M23))),"",IF(ISNUMBER(G23),G23,0)+IF(ISNUMBER(M23),M23,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="4">
+        <f>IF(入力!$B19="","",IF(AND(NOT(ISNUMBER(H23)),NOT(ISNUMBER(N23))),"",IF(ISNUMBER(H23),H23,0)+IF(ISNUMBER(N23),N23,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -24051,29 +24201,41 @@
         <f>IF(AND(ISNUMBER(入力!$C20),ISNUMBER(入力!$O20)),MAX(0,入力!$C20-入力!$B$5)*入力!$O20,"")</f>
         <v>69.1</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="4">
+        <f>IF(ISNUMBER(G24),ROUND(G24/入力!$B$5,0),"")</f>
+        <v>43</v>
+      </c>
+      <c r="I24" s="5">
         <f>IF(入力!$B20="","",IF(ISNUMBER(入力!$D20),入力!$D20,""))</f>
         <v>2.2</v>
       </c>
-      <c r="I24" s="5">
+      <c r="J24" s="5">
         <f>IF(ISNUMBER(入力!$D20),MAX(0,入力!$D20-入力!$C$5),"")</f>
         <v>0.6</v>
       </c>
-      <c r="J24" s="4">
+      <c r="K24" s="4">
         <f>IF(入力!$B20="","",IF(ISNUMBER(入力!$P20),入力!$P20,""))</f>
         <v>1750</v>
       </c>
-      <c r="K24" s="5">
+      <c r="L24" s="5">
         <f>IF(AND(ISNUMBER(入力!$D20),ISNUMBER(入力!$P20)),入力!$D20*入力!$P20,"")</f>
         <v>3850</v>
       </c>
-      <c r="L24" s="5">
+      <c r="M24" s="5">
         <f>IF(AND(ISNUMBER(入力!$D20),ISNUMBER(入力!$P20)),MAX(0,入力!$D20-入力!$C$5)*入力!$P20,"")</f>
         <v>1050</v>
       </c>
-      <c r="M24" s="5">
-        <f>IF(入力!$B20="","",IF(AND(NOT(ISNUMBER(G24)),NOT(ISNUMBER(L24))),"",IF(ISNUMBER(G24),G24,0)+IF(ISNUMBER(L24),L24,0)))</f>
+      <c r="N24" s="4">
+        <f>IF(ISNUMBER(M24),ROUND(M24/入力!$C$5,0),"")</f>
+        <v>656</v>
+      </c>
+      <c r="O24" s="5">
+        <f>IF(入力!$B20="","",IF(AND(NOT(ISNUMBER(G24)),NOT(ISNUMBER(M24))),"",IF(ISNUMBER(G24),G24,0)+IF(ISNUMBER(M24),M24,0)))</f>
         <v>1119.1</v>
+      </c>
+      <c r="P24" s="4">
+        <f>IF(入力!$B20="","",IF(AND(NOT(ISNUMBER(H24)),NOT(ISNUMBER(N24))),"",IF(ISNUMBER(H24),H24,0)+IF(ISNUMBER(N24),N24,0)))</f>
+        <v>699</v>
       </c>
     </row>
     <row r="25">
@@ -24101,28 +24263,40 @@
         <f>IF(AND(ISNUMBER(入力!$C21),ISNUMBER(入力!$O21)),MAX(0,入力!$C21-入力!$B$5)*入力!$O21,"")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="4">
+        <f>IF(ISNUMBER(G25),ROUND(G25/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="5">
         <f>IF(入力!$B21="","",IF(ISNUMBER(入力!$D21),入力!$D21,""))</f>
         <v>1.4</v>
       </c>
-      <c r="I25" s="5">
+      <c r="J25" s="5">
         <f>IF(ISNUMBER(入力!$D21),MAX(0,入力!$D21-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="J25" s="4">
+      <c r="K25" s="4">
         <f>IF(入力!$B21="","",IF(ISNUMBER(入力!$P21),入力!$P21,""))</f>
         <v>2881</v>
       </c>
-      <c r="K25" s="5">
+      <c r="L25" s="5">
         <f>IF(AND(ISNUMBER(入力!$D21),ISNUMBER(入力!$P21)),入力!$D21*入力!$P21,"")</f>
         <v>4033.4</v>
       </c>
-      <c r="L25" s="5">
+      <c r="M25" s="5">
         <f>IF(AND(ISNUMBER(入力!$D21),ISNUMBER(入力!$P21)),MAX(0,入力!$D21-入力!$C$5)*入力!$P21,"")</f>
         <v>0</v>
       </c>
-      <c r="M25" s="5">
-        <f>IF(入力!$B21="","",IF(AND(NOT(ISNUMBER(G25)),NOT(ISNUMBER(L25))),"",IF(ISNUMBER(G25),G25,0)+IF(ISNUMBER(L25),L25,0)))</f>
+      <c r="N25" s="4">
+        <f>IF(ISNUMBER(M25),ROUND(M25/入力!$C$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="5">
+        <f>IF(入力!$B21="","",IF(AND(NOT(ISNUMBER(G25)),NOT(ISNUMBER(M25))),"",IF(ISNUMBER(G25),G25,0)+IF(ISNUMBER(M25),M25,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="4">
+        <f>IF(入力!$B21="","",IF(AND(NOT(ISNUMBER(H25)),NOT(ISNUMBER(N25))),"",IF(ISNUMBER(H25),H25,0)+IF(ISNUMBER(N25),N25,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -24151,29 +24325,41 @@
         <f>IF(AND(ISNUMBER(入力!$C22),ISNUMBER(入力!$O22)),MAX(0,入力!$C22-入力!$B$5)*入力!$O22,"")</f>
         <v>0</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
+        <f>IF(ISNUMBER(G26),ROUND(G26/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="5">
         <f>IF(入力!$B22="","",IF(ISNUMBER(入力!$D22),入力!$D22,""))</f>
         <v>3.1</v>
       </c>
-      <c r="I26" s="5">
+      <c r="J26" s="5">
         <f>IF(ISNUMBER(入力!$D22),MAX(0,入力!$D22-入力!$C$5),"")</f>
         <v>1.5</v>
       </c>
-      <c r="J26" s="4">
+      <c r="K26" s="4">
         <f>IF(入力!$B22="","",IF(ISNUMBER(入力!$P22),入力!$P22,""))</f>
         <v>630</v>
       </c>
-      <c r="K26" s="5">
+      <c r="L26" s="5">
         <f>IF(AND(ISNUMBER(入力!$D22),ISNUMBER(入力!$P22)),入力!$D22*入力!$P22,"")</f>
         <v>1953</v>
       </c>
-      <c r="L26" s="5">
+      <c r="M26" s="5">
         <f>IF(AND(ISNUMBER(入力!$D22),ISNUMBER(入力!$P22)),MAX(0,入力!$D22-入力!$C$5)*入力!$P22,"")</f>
         <v>945</v>
       </c>
-      <c r="M26" s="5">
-        <f>IF(入力!$B22="","",IF(AND(NOT(ISNUMBER(G26)),NOT(ISNUMBER(L26))),"",IF(ISNUMBER(G26),G26,0)+IF(ISNUMBER(L26),L26,0)))</f>
+      <c r="N26" s="4">
+        <f>IF(ISNUMBER(M26),ROUND(M26/入力!$C$5,0),"")</f>
+        <v>591</v>
+      </c>
+      <c r="O26" s="5">
+        <f>IF(入力!$B22="","",IF(AND(NOT(ISNUMBER(G26)),NOT(ISNUMBER(M26))),"",IF(ISNUMBER(G26),G26,0)+IF(ISNUMBER(M26),M26,0)))</f>
         <v>945</v>
+      </c>
+      <c r="P26" s="4">
+        <f>IF(入力!$B22="","",IF(AND(NOT(ISNUMBER(H26)),NOT(ISNUMBER(N26))),"",IF(ISNUMBER(H26),H26,0)+IF(ISNUMBER(N26),N26,0)))</f>
+        <v>591</v>
       </c>
     </row>
     <row r="27">
@@ -24201,29 +24387,41 @@
         <f>IF(AND(ISNUMBER(入力!$C23),ISNUMBER(入力!$O23)),MAX(0,入力!$C23-入力!$B$5)*入力!$O23,"")</f>
         <v>54.2</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="4">
+        <f>IF(ISNUMBER(G27),ROUND(G27/入力!$B$5,0),"")</f>
+        <v>34</v>
+      </c>
+      <c r="I27" s="5">
         <f>IF(入力!$B23="","",IF(ISNUMBER(入力!$D23),入力!$D23,""))</f>
         <v>1.4</v>
       </c>
-      <c r="I27" s="5">
+      <c r="J27" s="5">
         <f>IF(ISNUMBER(入力!$D23),MAX(0,入力!$D23-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="J27" s="4">
+      <c r="K27" s="4">
         <f>IF(入力!$B23="","",IF(ISNUMBER(入力!$P23),入力!$P23,""))</f>
         <v>1061</v>
       </c>
-      <c r="K27" s="5">
+      <c r="L27" s="5">
         <f>IF(AND(ISNUMBER(入力!$D23),ISNUMBER(入力!$P23)),入力!$D23*入力!$P23,"")</f>
         <v>1485.4</v>
       </c>
-      <c r="L27" s="5">
+      <c r="M27" s="5">
         <f>IF(AND(ISNUMBER(入力!$D23),ISNUMBER(入力!$P23)),MAX(0,入力!$D23-入力!$C$5)*入力!$P23,"")</f>
         <v>0</v>
       </c>
-      <c r="M27" s="5">
-        <f>IF(入力!$B23="","",IF(AND(NOT(ISNUMBER(G27)),NOT(ISNUMBER(L27))),"",IF(ISNUMBER(G27),G27,0)+IF(ISNUMBER(L27),L27,0)))</f>
+      <c r="N27" s="4">
+        <f>IF(ISNUMBER(M27),ROUND(M27/入力!$C$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="5">
+        <f>IF(入力!$B23="","",IF(AND(NOT(ISNUMBER(G27)),NOT(ISNUMBER(M27))),"",IF(ISNUMBER(G27),G27,0)+IF(ISNUMBER(M27),M27,0)))</f>
         <v>54.2</v>
+      </c>
+      <c r="P27" s="4">
+        <f>IF(入力!$B23="","",IF(AND(NOT(ISNUMBER(H27)),NOT(ISNUMBER(N27))),"",IF(ISNUMBER(H27),H27,0)+IF(ISNUMBER(N27),N27,0)))</f>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
@@ -24251,28 +24449,40 @@
         <f>IF(AND(ISNUMBER(入力!$C24),ISNUMBER(入力!$O24)),MAX(0,入力!$C24-入力!$B$5)*入力!$O24,"")</f>
         <v>0</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
+        <f>IF(ISNUMBER(G28),ROUND(G28/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="5">
         <f>IF(入力!$B24="","",IF(ISNUMBER(入力!$D24),入力!$D24,""))</f>
         <v>1.6</v>
       </c>
-      <c r="I28" s="5">
+      <c r="J28" s="5">
         <f>IF(ISNUMBER(入力!$D24),MAX(0,入力!$D24-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="J28" s="4">
+      <c r="K28" s="4">
         <f>IF(入力!$B24="","",IF(ISNUMBER(入力!$P24),入力!$P24,""))</f>
         <v>970</v>
       </c>
-      <c r="K28" s="5">
+      <c r="L28" s="5">
         <f>IF(AND(ISNUMBER(入力!$D24),ISNUMBER(入力!$P24)),入力!$D24*入力!$P24,"")</f>
         <v>1552</v>
       </c>
-      <c r="L28" s="5">
+      <c r="M28" s="5">
         <f>IF(AND(ISNUMBER(入力!$D24),ISNUMBER(入力!$P24)),MAX(0,入力!$D24-入力!$C$5)*入力!$P24,"")</f>
         <v>0</v>
       </c>
-      <c r="M28" s="5">
-        <f>IF(入力!$B24="","",IF(AND(NOT(ISNUMBER(G28)),NOT(ISNUMBER(L28))),"",IF(ISNUMBER(G28),G28,0)+IF(ISNUMBER(L28),L28,0)))</f>
+      <c r="N28" s="4">
+        <f>IF(ISNUMBER(M28),ROUND(M28/入力!$C$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O28" s="5">
+        <f>IF(入力!$B24="","",IF(AND(NOT(ISNUMBER(G28)),NOT(ISNUMBER(M28))),"",IF(ISNUMBER(G28),G28,0)+IF(ISNUMBER(M28),M28,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P28" s="4">
+        <f>IF(入力!$B24="","",IF(AND(NOT(ISNUMBER(H28)),NOT(ISNUMBER(N28))),"",IF(ISNUMBER(H28),H28,0)+IF(ISNUMBER(N28),N28,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -24301,29 +24511,41 @@
         <f>IF(AND(ISNUMBER(入力!$C25),ISNUMBER(入力!$O25)),MAX(0,入力!$C25-入力!$B$5)*入力!$O25,"")</f>
         <v>188.2</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="4">
+        <f>IF(ISNUMBER(G29),ROUND(G29/入力!$B$5,0),"")</f>
+        <v>118</v>
+      </c>
+      <c r="I29" s="5">
         <f>IF(入力!$B25="","",IF(ISNUMBER(入力!$D25),入力!$D25,""))</f>
         <v>1.7</v>
       </c>
-      <c r="I29" s="5">
+      <c r="J29" s="5">
         <f>IF(ISNUMBER(入力!$D25),MAX(0,入力!$D25-入力!$C$5),"")</f>
         <v>0.1</v>
       </c>
-      <c r="J29" s="4">
+      <c r="K29" s="4">
         <f>IF(入力!$B25="","",IF(ISNUMBER(入力!$P25),入力!$P25,""))</f>
         <v>1183</v>
       </c>
-      <c r="K29" s="5">
+      <c r="L29" s="5">
         <f>IF(AND(ISNUMBER(入力!$D25),ISNUMBER(入力!$P25)),入力!$D25*入力!$P25,"")</f>
         <v>2011.1</v>
       </c>
-      <c r="L29" s="5">
+      <c r="M29" s="5">
         <f>IF(AND(ISNUMBER(入力!$D25),ISNUMBER(入力!$P25)),MAX(0,入力!$D25-入力!$C$5)*入力!$P25,"")</f>
         <v>118.3</v>
       </c>
-      <c r="M29" s="5">
-        <f>IF(入力!$B25="","",IF(AND(NOT(ISNUMBER(G29)),NOT(ISNUMBER(L29))),"",IF(ISNUMBER(G29),G29,0)+IF(ISNUMBER(L29),L29,0)))</f>
+      <c r="N29" s="4">
+        <f>IF(ISNUMBER(M29),ROUND(M29/入力!$C$5,0),"")</f>
+        <v>74</v>
+      </c>
+      <c r="O29" s="5">
+        <f>IF(入力!$B25="","",IF(AND(NOT(ISNUMBER(G29)),NOT(ISNUMBER(M29))),"",IF(ISNUMBER(G29),G29,0)+IF(ISNUMBER(M29),M29,0)))</f>
         <v>306.5</v>
+      </c>
+      <c r="P29" s="4">
+        <f>IF(入力!$B25="","",IF(AND(NOT(ISNUMBER(H29)),NOT(ISNUMBER(N29))),"",IF(ISNUMBER(H29),H29,0)+IF(ISNUMBER(N29),N29,0)))</f>
+        <v>192</v>
       </c>
     </row>
     <row r="30">
@@ -24351,28 +24573,40 @@
         <f>IF(AND(ISNUMBER(入力!$C26),ISNUMBER(入力!$O26)),MAX(0,入力!$C26-入力!$B$5)*入力!$O26,"")</f>
         <v>0</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="4">
+        <f>IF(ISNUMBER(G30),ROUND(G30/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="5">
         <f>IF(入力!$B26="","",IF(ISNUMBER(入力!$D26),入力!$D26,""))</f>
         <v>1.2</v>
       </c>
-      <c r="I30" s="5">
+      <c r="J30" s="5">
         <f>IF(ISNUMBER(入力!$D26),MAX(0,入力!$D26-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="J30" s="4" t="str">
+      <c r="K30" s="4" t="str">
         <f>IF(入力!$B26="","",IF(ISNUMBER(入力!$P26),入力!$P26,""))</f>
         <v/>
       </c>
-      <c r="K30" s="5" t="str">
+      <c r="L30" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D26),ISNUMBER(入力!$P26)),入力!$D26*入力!$P26,"")</f>
         <v/>
       </c>
-      <c r="L30" s="5" t="str">
+      <c r="M30" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D26),ISNUMBER(入力!$P26)),MAX(0,入力!$D26-入力!$C$5)*入力!$P26,"")</f>
         <v/>
       </c>
-      <c r="M30" s="5">
-        <f>IF(入力!$B26="","",IF(AND(NOT(ISNUMBER(G30)),NOT(ISNUMBER(L30))),"",IF(ISNUMBER(G30),G30,0)+IF(ISNUMBER(L30),L30,0)))</f>
+      <c r="N30" s="4" t="str">
+        <f>IF(ISNUMBER(M30),ROUND(M30/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O30" s="5">
+        <f>IF(入力!$B26="","",IF(AND(NOT(ISNUMBER(G30)),NOT(ISNUMBER(M30))),"",IF(ISNUMBER(G30),G30,0)+IF(ISNUMBER(M30),M30,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="4">
+        <f>IF(入力!$B26="","",IF(AND(NOT(ISNUMBER(H30)),NOT(ISNUMBER(N30))),"",IF(ISNUMBER(H30),H30,0)+IF(ISNUMBER(N30),N30,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -24401,28 +24635,40 @@
         <f>IF(AND(ISNUMBER(入力!$C27),ISNUMBER(入力!$O27)),MAX(0,入力!$C27-入力!$B$5)*入力!$O27,"")</f>
         <v>0</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="4">
+        <f>IF(ISNUMBER(G31),ROUND(G31/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="5">
         <f>IF(入力!$B27="","",IF(ISNUMBER(入力!$D27),入力!$D27,""))</f>
         <v>1.8</v>
       </c>
-      <c r="I31" s="5">
+      <c r="J31" s="5">
         <f>IF(ISNUMBER(入力!$D27),MAX(0,入力!$D27-入力!$C$5),"")</f>
         <v>0.2</v>
       </c>
-      <c r="J31" s="4" t="str">
+      <c r="K31" s="4" t="str">
         <f>IF(入力!$B27="","",IF(ISNUMBER(入力!$P27),入力!$P27,""))</f>
         <v/>
       </c>
-      <c r="K31" s="5" t="str">
+      <c r="L31" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D27),ISNUMBER(入力!$P27)),入力!$D27*入力!$P27,"")</f>
         <v/>
       </c>
-      <c r="L31" s="5" t="str">
+      <c r="M31" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D27),ISNUMBER(入力!$P27)),MAX(0,入力!$D27-入力!$C$5)*入力!$P27,"")</f>
         <v/>
       </c>
-      <c r="M31" s="5">
-        <f>IF(入力!$B27="","",IF(AND(NOT(ISNUMBER(G31)),NOT(ISNUMBER(L31))),"",IF(ISNUMBER(G31),G31,0)+IF(ISNUMBER(L31),L31,0)))</f>
+      <c r="N31" s="4" t="str">
+        <f>IF(ISNUMBER(M31),ROUND(M31/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O31" s="5">
+        <f>IF(入力!$B27="","",IF(AND(NOT(ISNUMBER(G31)),NOT(ISNUMBER(M31))),"",IF(ISNUMBER(G31),G31,0)+IF(ISNUMBER(M31),M31,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="4">
+        <f>IF(入力!$B27="","",IF(AND(NOT(ISNUMBER(H31)),NOT(ISNUMBER(N31))),"",IF(ISNUMBER(H31),H31,0)+IF(ISNUMBER(N31),N31,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -24451,29 +24697,41 @@
         <f>IF(AND(ISNUMBER(入力!$C28),ISNUMBER(入力!$O28)),MAX(0,入力!$C28-入力!$B$5)*入力!$O28,"")</f>
         <v>42.2</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="4">
+        <f>IF(ISNUMBER(G32),ROUND(G32/入力!$B$5,0),"")</f>
+        <v>26</v>
+      </c>
+      <c r="I32" s="5">
         <f>IF(入力!$B28="","",IF(ISNUMBER(入力!$D28),入力!$D28,""))</f>
         <v>2.5</v>
       </c>
-      <c r="I32" s="5">
+      <c r="J32" s="5">
         <f>IF(ISNUMBER(入力!$D28),MAX(0,入力!$D28-入力!$C$5),"")</f>
         <v>0.9</v>
       </c>
-      <c r="J32" s="4" t="str">
+      <c r="K32" s="4" t="str">
         <f>IF(入力!$B28="","",IF(ISNUMBER(入力!$P28),入力!$P28,""))</f>
         <v/>
       </c>
-      <c r="K32" s="5" t="str">
+      <c r="L32" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D28),ISNUMBER(入力!$P28)),入力!$D28*入力!$P28,"")</f>
         <v/>
       </c>
-      <c r="L32" s="5" t="str">
+      <c r="M32" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D28),ISNUMBER(入力!$P28)),MAX(0,入力!$D28-入力!$C$5)*入力!$P28,"")</f>
         <v/>
       </c>
-      <c r="M32" s="5">
-        <f>IF(入力!$B28="","",IF(AND(NOT(ISNUMBER(G32)),NOT(ISNUMBER(L32))),"",IF(ISNUMBER(G32),G32,0)+IF(ISNUMBER(L32),L32,0)))</f>
+      <c r="N32" s="4" t="str">
+        <f>IF(ISNUMBER(M32),ROUND(M32/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O32" s="5">
+        <f>IF(入力!$B28="","",IF(AND(NOT(ISNUMBER(G32)),NOT(ISNUMBER(M32))),"",IF(ISNUMBER(G32),G32,0)+IF(ISNUMBER(M32),M32,0)))</f>
         <v>42.2</v>
+      </c>
+      <c r="P32" s="4">
+        <f>IF(入力!$B28="","",IF(AND(NOT(ISNUMBER(H32)),NOT(ISNUMBER(N32))),"",IF(ISNUMBER(H32),H32,0)+IF(ISNUMBER(N32),N32,0)))</f>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
@@ -24501,29 +24759,41 @@
         <f>IF(AND(ISNUMBER(入力!$C29),ISNUMBER(入力!$O29)),MAX(0,入力!$C29-入力!$B$5)*入力!$O29,"")</f>
         <v>222.4</v>
       </c>
-      <c r="H33" s="5" t="str">
+      <c r="H33" s="4">
+        <f>IF(ISNUMBER(G33),ROUND(G33/入力!$B$5,0),"")</f>
+        <v>139</v>
+      </c>
+      <c r="I33" s="5" t="str">
         <f>IF(入力!$B29="","",IF(ISNUMBER(入力!$D29),入力!$D29,""))</f>
         <v/>
       </c>
-      <c r="I33" s="5" t="str">
+      <c r="J33" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D29),MAX(0,入力!$D29-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J33" s="4" t="str">
+      <c r="K33" s="4" t="str">
         <f>IF(入力!$B29="","",IF(ISNUMBER(入力!$P29),入力!$P29,""))</f>
         <v/>
       </c>
-      <c r="K33" s="5" t="str">
+      <c r="L33" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D29),ISNUMBER(入力!$P29)),入力!$D29*入力!$P29,"")</f>
         <v/>
       </c>
-      <c r="L33" s="5" t="str">
+      <c r="M33" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D29),ISNUMBER(入力!$P29)),MAX(0,入力!$D29-入力!$C$5)*入力!$P29,"")</f>
         <v/>
       </c>
-      <c r="M33" s="5">
-        <f>IF(入力!$B29="","",IF(AND(NOT(ISNUMBER(G33)),NOT(ISNUMBER(L33))),"",IF(ISNUMBER(G33),G33,0)+IF(ISNUMBER(L33),L33,0)))</f>
+      <c r="N33" s="4" t="str">
+        <f>IF(ISNUMBER(M33),ROUND(M33/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O33" s="5">
+        <f>IF(入力!$B29="","",IF(AND(NOT(ISNUMBER(G33)),NOT(ISNUMBER(M33))),"",IF(ISNUMBER(G33),G33,0)+IF(ISNUMBER(M33),M33,0)))</f>
         <v>222.4</v>
+      </c>
+      <c r="P33" s="4">
+        <f>IF(入力!$B29="","",IF(AND(NOT(ISNUMBER(H33)),NOT(ISNUMBER(N33))),"",IF(ISNUMBER(H33),H33,0)+IF(ISNUMBER(N33),N33,0)))</f>
+        <v>139</v>
       </c>
     </row>
     <row r="34">
@@ -24551,29 +24821,41 @@
         <f>IF(AND(ISNUMBER(入力!$C30),ISNUMBER(入力!$O30)),MAX(0,入力!$C30-入力!$B$5)*入力!$O30,"")</f>
         <v>171.6</v>
       </c>
-      <c r="H34" s="5" t="str">
+      <c r="H34" s="4">
+        <f>IF(ISNUMBER(G34),ROUND(G34/入力!$B$5,0),"")</f>
+        <v>107</v>
+      </c>
+      <c r="I34" s="5" t="str">
         <f>IF(入力!$B30="","",IF(ISNUMBER(入力!$D30),入力!$D30,""))</f>
         <v/>
       </c>
-      <c r="I34" s="5" t="str">
+      <c r="J34" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D30),MAX(0,入力!$D30-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J34" s="4" t="str">
+      <c r="K34" s="4" t="str">
         <f>IF(入力!$B30="","",IF(ISNUMBER(入力!$P30),入力!$P30,""))</f>
         <v/>
       </c>
-      <c r="K34" s="5" t="str">
+      <c r="L34" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D30),ISNUMBER(入力!$P30)),入力!$D30*入力!$P30,"")</f>
         <v/>
       </c>
-      <c r="L34" s="5" t="str">
+      <c r="M34" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D30),ISNUMBER(入力!$P30)),MAX(0,入力!$D30-入力!$C$5)*入力!$P30,"")</f>
         <v/>
       </c>
-      <c r="M34" s="5">
-        <f>IF(入力!$B30="","",IF(AND(NOT(ISNUMBER(G34)),NOT(ISNUMBER(L34))),"",IF(ISNUMBER(G34),G34,0)+IF(ISNUMBER(L34),L34,0)))</f>
+      <c r="N34" s="4" t="str">
+        <f>IF(ISNUMBER(M34),ROUND(M34/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="5">
+        <f>IF(入力!$B30="","",IF(AND(NOT(ISNUMBER(G34)),NOT(ISNUMBER(M34))),"",IF(ISNUMBER(G34),G34,0)+IF(ISNUMBER(M34),M34,0)))</f>
         <v>171.6</v>
+      </c>
+      <c r="P34" s="4">
+        <f>IF(入力!$B30="","",IF(AND(NOT(ISNUMBER(H34)),NOT(ISNUMBER(N34))),"",IF(ISNUMBER(H34),H34,0)+IF(ISNUMBER(N34),N34,0)))</f>
+        <v>107</v>
       </c>
     </row>
     <row r="35">
@@ -24601,28 +24883,40 @@
         <f>IF(AND(ISNUMBER(入力!$C31),ISNUMBER(入力!$O31)),MAX(0,入力!$C31-入力!$B$5)*入力!$O31,"")</f>
         <v>0</v>
       </c>
-      <c r="H35" s="5" t="str">
+      <c r="H35" s="4">
+        <f>IF(ISNUMBER(G35),ROUND(G35/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="str">
         <f>IF(入力!$B31="","",IF(ISNUMBER(入力!$D31),入力!$D31,""))</f>
         <v/>
       </c>
-      <c r="I35" s="5" t="str">
+      <c r="J35" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D31),MAX(0,入力!$D31-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J35" s="4" t="str">
+      <c r="K35" s="4" t="str">
         <f>IF(入力!$B31="","",IF(ISNUMBER(入力!$P31),入力!$P31,""))</f>
         <v/>
       </c>
-      <c r="K35" s="5" t="str">
+      <c r="L35" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D31),ISNUMBER(入力!$P31)),入力!$D31*入力!$P31,"")</f>
         <v/>
       </c>
-      <c r="L35" s="5" t="str">
+      <c r="M35" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D31),ISNUMBER(入力!$P31)),MAX(0,入力!$D31-入力!$C$5)*入力!$P31,"")</f>
         <v/>
       </c>
-      <c r="M35" s="5">
-        <f>IF(入力!$B31="","",IF(AND(NOT(ISNUMBER(G35)),NOT(ISNUMBER(L35))),"",IF(ISNUMBER(G35),G35,0)+IF(ISNUMBER(L35),L35,0)))</f>
+      <c r="N35" s="4" t="str">
+        <f>IF(ISNUMBER(M35),ROUND(M35/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="5">
+        <f>IF(入力!$B31="","",IF(AND(NOT(ISNUMBER(G35)),NOT(ISNUMBER(M35))),"",IF(ISNUMBER(G35),G35,0)+IF(ISNUMBER(M35),M35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P35" s="4">
+        <f>IF(入力!$B31="","",IF(AND(NOT(ISNUMBER(H35)),NOT(ISNUMBER(N35))),"",IF(ISNUMBER(H35),H35,0)+IF(ISNUMBER(N35),N35,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -24651,29 +24945,41 @@
         <f>IF(AND(ISNUMBER(入力!$C32),ISNUMBER(入力!$O32)),MAX(0,入力!$C32-入力!$B$5)*入力!$O32,"")</f>
         <v>327</v>
       </c>
-      <c r="H36" s="5" t="str">
+      <c r="H36" s="4">
+        <f>IF(ISNUMBER(G36),ROUND(G36/入力!$B$5,0),"")</f>
+        <v>204</v>
+      </c>
+      <c r="I36" s="5" t="str">
         <f>IF(入力!$B32="","",IF(ISNUMBER(入力!$D32),入力!$D32,""))</f>
         <v/>
       </c>
-      <c r="I36" s="5" t="str">
+      <c r="J36" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D32),MAX(0,入力!$D32-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J36" s="4" t="str">
+      <c r="K36" s="4" t="str">
         <f>IF(入力!$B32="","",IF(ISNUMBER(入力!$P32),入力!$P32,""))</f>
         <v/>
       </c>
-      <c r="K36" s="5" t="str">
+      <c r="L36" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D32),ISNUMBER(入力!$P32)),入力!$D32*入力!$P32,"")</f>
         <v/>
       </c>
-      <c r="L36" s="5" t="str">
+      <c r="M36" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D32),ISNUMBER(入力!$P32)),MAX(0,入力!$D32-入力!$C$5)*入力!$P32,"")</f>
         <v/>
       </c>
-      <c r="M36" s="5">
-        <f>IF(入力!$B32="","",IF(AND(NOT(ISNUMBER(G36)),NOT(ISNUMBER(L36))),"",IF(ISNUMBER(G36),G36,0)+IF(ISNUMBER(L36),L36,0)))</f>
+      <c r="N36" s="4" t="str">
+        <f>IF(ISNUMBER(M36),ROUND(M36/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O36" s="5">
+        <f>IF(入力!$B32="","",IF(AND(NOT(ISNUMBER(G36)),NOT(ISNUMBER(M36))),"",IF(ISNUMBER(G36),G36,0)+IF(ISNUMBER(M36),M36,0)))</f>
         <v>327</v>
+      </c>
+      <c r="P36" s="4">
+        <f>IF(入力!$B32="","",IF(AND(NOT(ISNUMBER(H36)),NOT(ISNUMBER(N36))),"",IF(ISNUMBER(H36),H36,0)+IF(ISNUMBER(N36),N36,0)))</f>
+        <v>204</v>
       </c>
     </row>
     <row r="37">
@@ -24701,29 +25007,41 @@
         <f>IF(AND(ISNUMBER(入力!$C33),ISNUMBER(入力!$O33)),MAX(0,入力!$C33-入力!$B$5)*入力!$O33,"")</f>
         <v>335.2</v>
       </c>
-      <c r="H37" s="5" t="str">
+      <c r="H37" s="4">
+        <f>IF(ISNUMBER(G37),ROUND(G37/入力!$B$5,0),"")</f>
+        <v>209</v>
+      </c>
+      <c r="I37" s="5" t="str">
         <f>IF(入力!$B33="","",IF(ISNUMBER(入力!$D33),入力!$D33,""))</f>
         <v/>
       </c>
-      <c r="I37" s="5" t="str">
+      <c r="J37" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D33),MAX(0,入力!$D33-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J37" s="4" t="str">
+      <c r="K37" s="4" t="str">
         <f>IF(入力!$B33="","",IF(ISNUMBER(入力!$P33),入力!$P33,""))</f>
         <v/>
       </c>
-      <c r="K37" s="5" t="str">
+      <c r="L37" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D33),ISNUMBER(入力!$P33)),入力!$D33*入力!$P33,"")</f>
         <v/>
       </c>
-      <c r="L37" s="5" t="str">
+      <c r="M37" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D33),ISNUMBER(入力!$P33)),MAX(0,入力!$D33-入力!$C$5)*入力!$P33,"")</f>
         <v/>
       </c>
-      <c r="M37" s="5">
-        <f>IF(入力!$B33="","",IF(AND(NOT(ISNUMBER(G37)),NOT(ISNUMBER(L37))),"",IF(ISNUMBER(G37),G37,0)+IF(ISNUMBER(L37),L37,0)))</f>
+      <c r="N37" s="4" t="str">
+        <f>IF(ISNUMBER(M37),ROUND(M37/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O37" s="5">
+        <f>IF(入力!$B33="","",IF(AND(NOT(ISNUMBER(G37)),NOT(ISNUMBER(M37))),"",IF(ISNUMBER(G37),G37,0)+IF(ISNUMBER(M37),M37,0)))</f>
         <v>335.2</v>
+      </c>
+      <c r="P37" s="4">
+        <f>IF(入力!$B33="","",IF(AND(NOT(ISNUMBER(H37)),NOT(ISNUMBER(N37))),"",IF(ISNUMBER(H37),H37,0)+IF(ISNUMBER(N37),N37,0)))</f>
+        <v>209</v>
       </c>
     </row>
     <row r="38">
@@ -24751,28 +25069,40 @@
         <f>IF(AND(ISNUMBER(入力!$C34),ISNUMBER(入力!$O34)),MAX(0,入力!$C34-入力!$B$5)*入力!$O34,"")</f>
         <v/>
       </c>
-      <c r="H38" s="5" t="str">
+      <c r="H38" s="4" t="str">
+        <f>IF(ISNUMBER(G38),ROUND(G38/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="5" t="str">
         <f>IF(入力!$B34="","",IF(ISNUMBER(入力!$D34),入力!$D34,""))</f>
         <v/>
       </c>
-      <c r="I38" s="5" t="str">
+      <c r="J38" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D34),MAX(0,入力!$D34-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J38" s="4" t="str">
+      <c r="K38" s="4" t="str">
         <f>IF(入力!$B34="","",IF(ISNUMBER(入力!$P34),入力!$P34,""))</f>
         <v/>
       </c>
-      <c r="K38" s="5" t="str">
+      <c r="L38" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D34),ISNUMBER(入力!$P34)),入力!$D34*入力!$P34,"")</f>
         <v/>
       </c>
-      <c r="L38" s="5" t="str">
+      <c r="M38" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D34),ISNUMBER(入力!$P34)),MAX(0,入力!$D34-入力!$C$5)*入力!$P34,"")</f>
         <v/>
       </c>
-      <c r="M38" s="5" t="str">
-        <f>IF(入力!$B34="","",IF(AND(NOT(ISNUMBER(G38)),NOT(ISNUMBER(L38))),"",IF(ISNUMBER(G38),G38,0)+IF(ISNUMBER(L38),L38,0)))</f>
+      <c r="N38" s="4" t="str">
+        <f>IF(ISNUMBER(M38),ROUND(M38/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O38" s="5" t="str">
+        <f>IF(入力!$B34="","",IF(AND(NOT(ISNUMBER(G38)),NOT(ISNUMBER(M38))),"",IF(ISNUMBER(G38),G38,0)+IF(ISNUMBER(M38),M38,0)))</f>
+        <v/>
+      </c>
+      <c r="P38" s="4" t="str">
+        <f>IF(入力!$B34="","",IF(AND(NOT(ISNUMBER(H38)),NOT(ISNUMBER(N38))),"",IF(ISNUMBER(H38),H38,0)+IF(ISNUMBER(N38),N38,0)))</f>
         <v/>
       </c>
     </row>
@@ -24801,28 +25131,40 @@
         <f>IF(AND(ISNUMBER(入力!$C35),ISNUMBER(入力!$O35)),MAX(0,入力!$C35-入力!$B$5)*入力!$O35,"")</f>
         <v/>
       </c>
-      <c r="H39" s="5" t="str">
+      <c r="H39" s="4" t="str">
+        <f>IF(ISNUMBER(G39),ROUND(G39/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="5" t="str">
         <f>IF(入力!$B35="","",IF(ISNUMBER(入力!$D35),入力!$D35,""))</f>
         <v/>
       </c>
-      <c r="I39" s="5" t="str">
+      <c r="J39" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D35),MAX(0,入力!$D35-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J39" s="4" t="str">
+      <c r="K39" s="4" t="str">
         <f>IF(入力!$B35="","",IF(ISNUMBER(入力!$P35),入力!$P35,""))</f>
         <v/>
       </c>
-      <c r="K39" s="5" t="str">
+      <c r="L39" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D35),ISNUMBER(入力!$P35)),入力!$D35*入力!$P35,"")</f>
         <v/>
       </c>
-      <c r="L39" s="5" t="str">
+      <c r="M39" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D35),ISNUMBER(入力!$P35)),MAX(0,入力!$D35-入力!$C$5)*入力!$P35,"")</f>
         <v/>
       </c>
-      <c r="M39" s="5" t="str">
-        <f>IF(入力!$B35="","",IF(AND(NOT(ISNUMBER(G39)),NOT(ISNUMBER(L39))),"",IF(ISNUMBER(G39),G39,0)+IF(ISNUMBER(L39),L39,0)))</f>
+      <c r="N39" s="4" t="str">
+        <f>IF(ISNUMBER(M39),ROUND(M39/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O39" s="5" t="str">
+        <f>IF(入力!$B35="","",IF(AND(NOT(ISNUMBER(G39)),NOT(ISNUMBER(M39))),"",IF(ISNUMBER(G39),G39,0)+IF(ISNUMBER(M39),M39,0)))</f>
+        <v/>
+      </c>
+      <c r="P39" s="4" t="str">
+        <f>IF(入力!$B35="","",IF(AND(NOT(ISNUMBER(H39)),NOT(ISNUMBER(N39))),"",IF(ISNUMBER(H39),H39,0)+IF(ISNUMBER(N39),N39,0)))</f>
         <v/>
       </c>
     </row>
@@ -24851,28 +25193,40 @@
         <f>IF(AND(ISNUMBER(入力!$C36),ISNUMBER(入力!$O36)),MAX(0,入力!$C36-入力!$B$5)*入力!$O36,"")</f>
         <v/>
       </c>
-      <c r="H40" s="5" t="str">
+      <c r="H40" s="4" t="str">
+        <f>IF(ISNUMBER(G40),ROUND(G40/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="5" t="str">
         <f>IF(入力!$B36="","",IF(ISNUMBER(入力!$D36),入力!$D36,""))</f>
         <v/>
       </c>
-      <c r="I40" s="5" t="str">
+      <c r="J40" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D36),MAX(0,入力!$D36-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J40" s="4" t="str">
+      <c r="K40" s="4" t="str">
         <f>IF(入力!$B36="","",IF(ISNUMBER(入力!$P36),入力!$P36,""))</f>
         <v/>
       </c>
-      <c r="K40" s="5" t="str">
+      <c r="L40" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D36),ISNUMBER(入力!$P36)),入力!$D36*入力!$P36,"")</f>
         <v/>
       </c>
-      <c r="L40" s="5" t="str">
+      <c r="M40" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D36),ISNUMBER(入力!$P36)),MAX(0,入力!$D36-入力!$C$5)*入力!$P36,"")</f>
         <v/>
       </c>
-      <c r="M40" s="5" t="str">
-        <f>IF(入力!$B36="","",IF(AND(NOT(ISNUMBER(G40)),NOT(ISNUMBER(L40))),"",IF(ISNUMBER(G40),G40,0)+IF(ISNUMBER(L40),L40,0)))</f>
+      <c r="N40" s="4" t="str">
+        <f>IF(ISNUMBER(M40),ROUND(M40/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O40" s="5" t="str">
+        <f>IF(入力!$B36="","",IF(AND(NOT(ISNUMBER(G40)),NOT(ISNUMBER(M40))),"",IF(ISNUMBER(G40),G40,0)+IF(ISNUMBER(M40),M40,0)))</f>
+        <v/>
+      </c>
+      <c r="P40" s="4" t="str">
+        <f>IF(入力!$B36="","",IF(AND(NOT(ISNUMBER(H40)),NOT(ISNUMBER(N40))),"",IF(ISNUMBER(H40),H40,0)+IF(ISNUMBER(N40),N40,0)))</f>
         <v/>
       </c>
     </row>
@@ -24901,28 +25255,40 @@
         <f>IF(AND(ISNUMBER(入力!$C37),ISNUMBER(入力!$O37)),MAX(0,入力!$C37-入力!$B$5)*入力!$O37,"")</f>
         <v/>
       </c>
-      <c r="H41" s="5" t="str">
+      <c r="H41" s="4" t="str">
+        <f>IF(ISNUMBER(G41),ROUND(G41/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="5" t="str">
         <f>IF(入力!$B37="","",IF(ISNUMBER(入力!$D37),入力!$D37,""))</f>
         <v/>
       </c>
-      <c r="I41" s="5" t="str">
+      <c r="J41" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D37),MAX(0,入力!$D37-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J41" s="4" t="str">
+      <c r="K41" s="4" t="str">
         <f>IF(入力!$B37="","",IF(ISNUMBER(入力!$P37),入力!$P37,""))</f>
         <v/>
       </c>
-      <c r="K41" s="5" t="str">
+      <c r="L41" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D37),ISNUMBER(入力!$P37)),入力!$D37*入力!$P37,"")</f>
         <v/>
       </c>
-      <c r="L41" s="5" t="str">
+      <c r="M41" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D37),ISNUMBER(入力!$P37)),MAX(0,入力!$D37-入力!$C$5)*入力!$P37,"")</f>
         <v/>
       </c>
-      <c r="M41" s="5" t="str">
-        <f>IF(入力!$B37="","",IF(AND(NOT(ISNUMBER(G41)),NOT(ISNUMBER(L41))),"",IF(ISNUMBER(G41),G41,0)+IF(ISNUMBER(L41),L41,0)))</f>
+      <c r="N41" s="4" t="str">
+        <f>IF(ISNUMBER(M41),ROUND(M41/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O41" s="5" t="str">
+        <f>IF(入力!$B37="","",IF(AND(NOT(ISNUMBER(G41)),NOT(ISNUMBER(M41))),"",IF(ISNUMBER(G41),G41,0)+IF(ISNUMBER(M41),M41,0)))</f>
+        <v/>
+      </c>
+      <c r="P41" s="4" t="str">
+        <f>IF(入力!$B37="","",IF(AND(NOT(ISNUMBER(H41)),NOT(ISNUMBER(N41))),"",IF(ISNUMBER(H41),H41,0)+IF(ISNUMBER(N41),N41,0)))</f>
         <v/>
       </c>
     </row>
@@ -24951,28 +25317,40 @@
         <f>IF(AND(ISNUMBER(入力!$C38),ISNUMBER(入力!$O38)),MAX(0,入力!$C38-入力!$B$5)*入力!$O38,"")</f>
         <v/>
       </c>
-      <c r="H42" s="5" t="str">
+      <c r="H42" s="4" t="str">
+        <f>IF(ISNUMBER(G42),ROUND(G42/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="5" t="str">
         <f>IF(入力!$B38="","",IF(ISNUMBER(入力!$D38),入力!$D38,""))</f>
         <v/>
       </c>
-      <c r="I42" s="5" t="str">
+      <c r="J42" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D38),MAX(0,入力!$D38-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J42" s="4" t="str">
+      <c r="K42" s="4" t="str">
         <f>IF(入力!$B38="","",IF(ISNUMBER(入力!$P38),入力!$P38,""))</f>
         <v/>
       </c>
-      <c r="K42" s="5" t="str">
+      <c r="L42" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D38),ISNUMBER(入力!$P38)),入力!$D38*入力!$P38,"")</f>
         <v/>
       </c>
-      <c r="L42" s="5" t="str">
+      <c r="M42" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D38),ISNUMBER(入力!$P38)),MAX(0,入力!$D38-入力!$C$5)*入力!$P38,"")</f>
         <v/>
       </c>
-      <c r="M42" s="5" t="str">
-        <f>IF(入力!$B38="","",IF(AND(NOT(ISNUMBER(G42)),NOT(ISNUMBER(L42))),"",IF(ISNUMBER(G42),G42,0)+IF(ISNUMBER(L42),L42,0)))</f>
+      <c r="N42" s="4" t="str">
+        <f>IF(ISNUMBER(M42),ROUND(M42/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O42" s="5" t="str">
+        <f>IF(入力!$B38="","",IF(AND(NOT(ISNUMBER(G42)),NOT(ISNUMBER(M42))),"",IF(ISNUMBER(G42),G42,0)+IF(ISNUMBER(M42),M42,0)))</f>
+        <v/>
+      </c>
+      <c r="P42" s="4" t="str">
+        <f>IF(入力!$B38="","",IF(AND(NOT(ISNUMBER(H42)),NOT(ISNUMBER(N42))),"",IF(ISNUMBER(H42),H42,0)+IF(ISNUMBER(N42),N42,0)))</f>
         <v/>
       </c>
     </row>
@@ -25001,28 +25379,40 @@
         <f>IF(AND(ISNUMBER(入力!$C39),ISNUMBER(入力!$O39)),MAX(0,入力!$C39-入力!$B$5)*入力!$O39,"")</f>
         <v/>
       </c>
-      <c r="H43" s="5" t="str">
+      <c r="H43" s="4" t="str">
+        <f>IF(ISNUMBER(G43),ROUND(G43/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="5" t="str">
         <f>IF(入力!$B39="","",IF(ISNUMBER(入力!$D39),入力!$D39,""))</f>
         <v/>
       </c>
-      <c r="I43" s="5" t="str">
+      <c r="J43" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D39),MAX(0,入力!$D39-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J43" s="4" t="str">
+      <c r="K43" s="4" t="str">
         <f>IF(入力!$B39="","",IF(ISNUMBER(入力!$P39),入力!$P39,""))</f>
         <v/>
       </c>
-      <c r="K43" s="5" t="str">
+      <c r="L43" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D39),ISNUMBER(入力!$P39)),入力!$D39*入力!$P39,"")</f>
         <v/>
       </c>
-      <c r="L43" s="5" t="str">
+      <c r="M43" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D39),ISNUMBER(入力!$P39)),MAX(0,入力!$D39-入力!$C$5)*入力!$P39,"")</f>
         <v/>
       </c>
-      <c r="M43" s="5" t="str">
-        <f>IF(入力!$B39="","",IF(AND(NOT(ISNUMBER(G43)),NOT(ISNUMBER(L43))),"",IF(ISNUMBER(G43),G43,0)+IF(ISNUMBER(L43),L43,0)))</f>
+      <c r="N43" s="4" t="str">
+        <f>IF(ISNUMBER(M43),ROUND(M43/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O43" s="5" t="str">
+        <f>IF(入力!$B39="","",IF(AND(NOT(ISNUMBER(G43)),NOT(ISNUMBER(M43))),"",IF(ISNUMBER(G43),G43,0)+IF(ISNUMBER(M43),M43,0)))</f>
+        <v/>
+      </c>
+      <c r="P43" s="4" t="str">
+        <f>IF(入力!$B39="","",IF(AND(NOT(ISNUMBER(H43)),NOT(ISNUMBER(N43))),"",IF(ISNUMBER(H43),H43,0)+IF(ISNUMBER(N43),N43,0)))</f>
         <v/>
       </c>
     </row>
@@ -25051,28 +25441,40 @@
         <f>IF(AND(ISNUMBER(入力!$C40),ISNUMBER(入力!$O40)),MAX(0,入力!$C40-入力!$B$5)*入力!$O40,"")</f>
         <v/>
       </c>
-      <c r="H44" s="5" t="str">
+      <c r="H44" s="4" t="str">
+        <f>IF(ISNUMBER(G44),ROUND(G44/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="5" t="str">
         <f>IF(入力!$B40="","",IF(ISNUMBER(入力!$D40),入力!$D40,""))</f>
         <v/>
       </c>
-      <c r="I44" s="5" t="str">
+      <c r="J44" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D40),MAX(0,入力!$D40-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J44" s="4" t="str">
+      <c r="K44" s="4" t="str">
         <f>IF(入力!$B40="","",IF(ISNUMBER(入力!$P40),入力!$P40,""))</f>
         <v/>
       </c>
-      <c r="K44" s="5" t="str">
+      <c r="L44" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D40),ISNUMBER(入力!$P40)),入力!$D40*入力!$P40,"")</f>
         <v/>
       </c>
-      <c r="L44" s="5" t="str">
+      <c r="M44" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D40),ISNUMBER(入力!$P40)),MAX(0,入力!$D40-入力!$C$5)*入力!$P40,"")</f>
         <v/>
       </c>
-      <c r="M44" s="5" t="str">
-        <f>IF(入力!$B40="","",IF(AND(NOT(ISNUMBER(G44)),NOT(ISNUMBER(L44))),"",IF(ISNUMBER(G44),G44,0)+IF(ISNUMBER(L44),L44,0)))</f>
+      <c r="N44" s="4" t="str">
+        <f>IF(ISNUMBER(M44),ROUND(M44/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O44" s="5" t="str">
+        <f>IF(入力!$B40="","",IF(AND(NOT(ISNUMBER(G44)),NOT(ISNUMBER(M44))),"",IF(ISNUMBER(G44),G44,0)+IF(ISNUMBER(M44),M44,0)))</f>
+        <v/>
+      </c>
+      <c r="P44" s="4" t="str">
+        <f>IF(入力!$B40="","",IF(AND(NOT(ISNUMBER(H44)),NOT(ISNUMBER(N44))),"",IF(ISNUMBER(H44),H44,0)+IF(ISNUMBER(N44),N44,0)))</f>
         <v/>
       </c>
     </row>
@@ -25101,28 +25503,40 @@
         <f>IF(AND(ISNUMBER(入力!$C41),ISNUMBER(入力!$O41)),MAX(0,入力!$C41-入力!$B$5)*入力!$O41,"")</f>
         <v/>
       </c>
-      <c r="H45" s="5" t="str">
+      <c r="H45" s="4" t="str">
+        <f>IF(ISNUMBER(G45),ROUND(G45/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="5" t="str">
         <f>IF(入力!$B41="","",IF(ISNUMBER(入力!$D41),入力!$D41,""))</f>
         <v/>
       </c>
-      <c r="I45" s="5" t="str">
+      <c r="J45" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D41),MAX(0,入力!$D41-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J45" s="4" t="str">
+      <c r="K45" s="4" t="str">
         <f>IF(入力!$B41="","",IF(ISNUMBER(入力!$P41),入力!$P41,""))</f>
         <v/>
       </c>
-      <c r="K45" s="5" t="str">
+      <c r="L45" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D41),ISNUMBER(入力!$P41)),入力!$D41*入力!$P41,"")</f>
         <v/>
       </c>
-      <c r="L45" s="5" t="str">
+      <c r="M45" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D41),ISNUMBER(入力!$P41)),MAX(0,入力!$D41-入力!$C$5)*入力!$P41,"")</f>
         <v/>
       </c>
-      <c r="M45" s="5" t="str">
-        <f>IF(入力!$B41="","",IF(AND(NOT(ISNUMBER(G45)),NOT(ISNUMBER(L45))),"",IF(ISNUMBER(G45),G45,0)+IF(ISNUMBER(L45),L45,0)))</f>
+      <c r="N45" s="4" t="str">
+        <f>IF(ISNUMBER(M45),ROUND(M45/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O45" s="5" t="str">
+        <f>IF(入力!$B41="","",IF(AND(NOT(ISNUMBER(G45)),NOT(ISNUMBER(M45))),"",IF(ISNUMBER(G45),G45,0)+IF(ISNUMBER(M45),M45,0)))</f>
+        <v/>
+      </c>
+      <c r="P45" s="4" t="str">
+        <f>IF(入力!$B41="","",IF(AND(NOT(ISNUMBER(H45)),NOT(ISNUMBER(N45))),"",IF(ISNUMBER(H45),H45,0)+IF(ISNUMBER(N45),N45,0)))</f>
         <v/>
       </c>
     </row>
@@ -25151,28 +25565,40 @@
         <f>IF(AND(ISNUMBER(入力!$C42),ISNUMBER(入力!$O42)),MAX(0,入力!$C42-入力!$B$5)*入力!$O42,"")</f>
         <v/>
       </c>
-      <c r="H46" s="5" t="str">
+      <c r="H46" s="4" t="str">
+        <f>IF(ISNUMBER(G46),ROUND(G46/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="5" t="str">
         <f>IF(入力!$B42="","",IF(ISNUMBER(入力!$D42),入力!$D42,""))</f>
         <v/>
       </c>
-      <c r="I46" s="5" t="str">
+      <c r="J46" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D42),MAX(0,入力!$D42-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J46" s="4" t="str">
+      <c r="K46" s="4" t="str">
         <f>IF(入力!$B42="","",IF(ISNUMBER(入力!$P42),入力!$P42,""))</f>
         <v/>
       </c>
-      <c r="K46" s="5" t="str">
+      <c r="L46" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D42),ISNUMBER(入力!$P42)),入力!$D42*入力!$P42,"")</f>
         <v/>
       </c>
-      <c r="L46" s="5" t="str">
+      <c r="M46" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D42),ISNUMBER(入力!$P42)),MAX(0,入力!$D42-入力!$C$5)*入力!$P42,"")</f>
         <v/>
       </c>
-      <c r="M46" s="5" t="str">
-        <f>IF(入力!$B42="","",IF(AND(NOT(ISNUMBER(G46)),NOT(ISNUMBER(L46))),"",IF(ISNUMBER(G46),G46,0)+IF(ISNUMBER(L46),L46,0)))</f>
+      <c r="N46" s="4" t="str">
+        <f>IF(ISNUMBER(M46),ROUND(M46/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O46" s="5" t="str">
+        <f>IF(入力!$B42="","",IF(AND(NOT(ISNUMBER(G46)),NOT(ISNUMBER(M46))),"",IF(ISNUMBER(G46),G46,0)+IF(ISNUMBER(M46),M46,0)))</f>
+        <v/>
+      </c>
+      <c r="P46" s="4" t="str">
+        <f>IF(入力!$B42="","",IF(AND(NOT(ISNUMBER(H46)),NOT(ISNUMBER(N46))),"",IF(ISNUMBER(H46),H46,0)+IF(ISNUMBER(N46),N46,0)))</f>
         <v/>
       </c>
     </row>
@@ -25201,28 +25627,40 @@
         <f>IF(AND(ISNUMBER(入力!$C43),ISNUMBER(入力!$O43)),MAX(0,入力!$C43-入力!$B$5)*入力!$O43,"")</f>
         <v/>
       </c>
-      <c r="H47" s="5" t="str">
+      <c r="H47" s="4" t="str">
+        <f>IF(ISNUMBER(G47),ROUND(G47/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="5" t="str">
         <f>IF(入力!$B43="","",IF(ISNUMBER(入力!$D43),入力!$D43,""))</f>
         <v/>
       </c>
-      <c r="I47" s="5" t="str">
+      <c r="J47" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D43),MAX(0,入力!$D43-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J47" s="4" t="str">
+      <c r="K47" s="4" t="str">
         <f>IF(入力!$B43="","",IF(ISNUMBER(入力!$P43),入力!$P43,""))</f>
         <v/>
       </c>
-      <c r="K47" s="5" t="str">
+      <c r="L47" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D43),ISNUMBER(入力!$P43)),入力!$D43*入力!$P43,"")</f>
         <v/>
       </c>
-      <c r="L47" s="5" t="str">
+      <c r="M47" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D43),ISNUMBER(入力!$P43)),MAX(0,入力!$D43-入力!$C$5)*入力!$P43,"")</f>
         <v/>
       </c>
-      <c r="M47" s="5" t="str">
-        <f>IF(入力!$B43="","",IF(AND(NOT(ISNUMBER(G47)),NOT(ISNUMBER(L47))),"",IF(ISNUMBER(G47),G47,0)+IF(ISNUMBER(L47),L47,0)))</f>
+      <c r="N47" s="4" t="str">
+        <f>IF(ISNUMBER(M47),ROUND(M47/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O47" s="5" t="str">
+        <f>IF(入力!$B43="","",IF(AND(NOT(ISNUMBER(G47)),NOT(ISNUMBER(M47))),"",IF(ISNUMBER(G47),G47,0)+IF(ISNUMBER(M47),M47,0)))</f>
+        <v/>
+      </c>
+      <c r="P47" s="4" t="str">
+        <f>IF(入力!$B43="","",IF(AND(NOT(ISNUMBER(H47)),NOT(ISNUMBER(N47))),"",IF(ISNUMBER(H47),H47,0)+IF(ISNUMBER(N47),N47,0)))</f>
         <v/>
       </c>
     </row>
@@ -25251,28 +25689,40 @@
         <f>IF(AND(ISNUMBER(入力!$C44),ISNUMBER(入力!$O44)),MAX(0,入力!$C44-入力!$B$5)*入力!$O44,"")</f>
         <v/>
       </c>
-      <c r="H48" s="5" t="str">
+      <c r="H48" s="4" t="str">
+        <f>IF(ISNUMBER(G48),ROUND(G48/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="5" t="str">
         <f>IF(入力!$B44="","",IF(ISNUMBER(入力!$D44),入力!$D44,""))</f>
         <v/>
       </c>
-      <c r="I48" s="5" t="str">
+      <c r="J48" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D44),MAX(0,入力!$D44-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J48" s="4" t="str">
+      <c r="K48" s="4" t="str">
         <f>IF(入力!$B44="","",IF(ISNUMBER(入力!$P44),入力!$P44,""))</f>
         <v/>
       </c>
-      <c r="K48" s="5" t="str">
+      <c r="L48" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D44),ISNUMBER(入力!$P44)),入力!$D44*入力!$P44,"")</f>
         <v/>
       </c>
-      <c r="L48" s="5" t="str">
+      <c r="M48" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D44),ISNUMBER(入力!$P44)),MAX(0,入力!$D44-入力!$C$5)*入力!$P44,"")</f>
         <v/>
       </c>
-      <c r="M48" s="5" t="str">
-        <f>IF(入力!$B44="","",IF(AND(NOT(ISNUMBER(G48)),NOT(ISNUMBER(L48))),"",IF(ISNUMBER(G48),G48,0)+IF(ISNUMBER(L48),L48,0)))</f>
+      <c r="N48" s="4" t="str">
+        <f>IF(ISNUMBER(M48),ROUND(M48/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O48" s="5" t="str">
+        <f>IF(入力!$B44="","",IF(AND(NOT(ISNUMBER(G48)),NOT(ISNUMBER(M48))),"",IF(ISNUMBER(G48),G48,0)+IF(ISNUMBER(M48),M48,0)))</f>
+        <v/>
+      </c>
+      <c r="P48" s="4" t="str">
+        <f>IF(入力!$B44="","",IF(AND(NOT(ISNUMBER(H48)),NOT(ISNUMBER(N48))),"",IF(ISNUMBER(H48),H48,0)+IF(ISNUMBER(N48),N48,0)))</f>
         <v/>
       </c>
     </row>
@@ -25301,28 +25751,40 @@
         <f>IF(AND(ISNUMBER(入力!$C45),ISNUMBER(入力!$O45)),MAX(0,入力!$C45-入力!$B$5)*入力!$O45,"")</f>
         <v/>
       </c>
-      <c r="H49" s="5" t="str">
+      <c r="H49" s="4" t="str">
+        <f>IF(ISNUMBER(G49),ROUND(G49/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="5" t="str">
         <f>IF(入力!$B45="","",IF(ISNUMBER(入力!$D45),入力!$D45,""))</f>
         <v/>
       </c>
-      <c r="I49" s="5" t="str">
+      <c r="J49" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D45),MAX(0,入力!$D45-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J49" s="4" t="str">
+      <c r="K49" s="4" t="str">
         <f>IF(入力!$B45="","",IF(ISNUMBER(入力!$P45),入力!$P45,""))</f>
         <v/>
       </c>
-      <c r="K49" s="5" t="str">
+      <c r="L49" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D45),ISNUMBER(入力!$P45)),入力!$D45*入力!$P45,"")</f>
         <v/>
       </c>
-      <c r="L49" s="5" t="str">
+      <c r="M49" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D45),ISNUMBER(入力!$P45)),MAX(0,入力!$D45-入力!$C$5)*入力!$P45,"")</f>
         <v/>
       </c>
-      <c r="M49" s="5" t="str">
-        <f>IF(入力!$B45="","",IF(AND(NOT(ISNUMBER(G49)),NOT(ISNUMBER(L49))),"",IF(ISNUMBER(G49),G49,0)+IF(ISNUMBER(L49),L49,0)))</f>
+      <c r="N49" s="4" t="str">
+        <f>IF(ISNUMBER(M49),ROUND(M49/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O49" s="5" t="str">
+        <f>IF(入力!$B45="","",IF(AND(NOT(ISNUMBER(G49)),NOT(ISNUMBER(M49))),"",IF(ISNUMBER(G49),G49,0)+IF(ISNUMBER(M49),M49,0)))</f>
+        <v/>
+      </c>
+      <c r="P49" s="4" t="str">
+        <f>IF(入力!$B45="","",IF(AND(NOT(ISNUMBER(H49)),NOT(ISNUMBER(N49))),"",IF(ISNUMBER(H49),H49,0)+IF(ISNUMBER(N49),N49,0)))</f>
         <v/>
       </c>
     </row>
@@ -25351,28 +25813,40 @@
         <f>IF(AND(ISNUMBER(入力!$C46),ISNUMBER(入力!$O46)),MAX(0,入力!$C46-入力!$B$5)*入力!$O46,"")</f>
         <v/>
       </c>
-      <c r="H50" s="5" t="str">
+      <c r="H50" s="4" t="str">
+        <f>IF(ISNUMBER(G50),ROUND(G50/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="5" t="str">
         <f>IF(入力!$B46="","",IF(ISNUMBER(入力!$D46),入力!$D46,""))</f>
         <v/>
       </c>
-      <c r="I50" s="5" t="str">
+      <c r="J50" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D46),MAX(0,入力!$D46-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J50" s="4" t="str">
+      <c r="K50" s="4" t="str">
         <f>IF(入力!$B46="","",IF(ISNUMBER(入力!$P46),入力!$P46,""))</f>
         <v/>
       </c>
-      <c r="K50" s="5" t="str">
+      <c r="L50" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D46),ISNUMBER(入力!$P46)),入力!$D46*入力!$P46,"")</f>
         <v/>
       </c>
-      <c r="L50" s="5" t="str">
+      <c r="M50" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D46),ISNUMBER(入力!$P46)),MAX(0,入力!$D46-入力!$C$5)*入力!$P46,"")</f>
         <v/>
       </c>
-      <c r="M50" s="5" t="str">
-        <f>IF(入力!$B46="","",IF(AND(NOT(ISNUMBER(G50)),NOT(ISNUMBER(L50))),"",IF(ISNUMBER(G50),G50,0)+IF(ISNUMBER(L50),L50,0)))</f>
+      <c r="N50" s="4" t="str">
+        <f>IF(ISNUMBER(M50),ROUND(M50/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O50" s="5" t="str">
+        <f>IF(入力!$B46="","",IF(AND(NOT(ISNUMBER(G50)),NOT(ISNUMBER(M50))),"",IF(ISNUMBER(G50),G50,0)+IF(ISNUMBER(M50),M50,0)))</f>
+        <v/>
+      </c>
+      <c r="P50" s="4" t="str">
+        <f>IF(入力!$B46="","",IF(AND(NOT(ISNUMBER(H50)),NOT(ISNUMBER(N50))),"",IF(ISNUMBER(H50),H50,0)+IF(ISNUMBER(N50),N50,0)))</f>
         <v/>
       </c>
     </row>
@@ -25401,28 +25875,40 @@
         <f>IF(AND(ISNUMBER(入力!$C47),ISNUMBER(入力!$O47)),MAX(0,入力!$C47-入力!$B$5)*入力!$O47,"")</f>
         <v/>
       </c>
-      <c r="H51" s="5" t="str">
+      <c r="H51" s="4" t="str">
+        <f>IF(ISNUMBER(G51),ROUND(G51/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="5" t="str">
         <f>IF(入力!$B47="","",IF(ISNUMBER(入力!$D47),入力!$D47,""))</f>
         <v/>
       </c>
-      <c r="I51" s="5" t="str">
+      <c r="J51" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D47),MAX(0,入力!$D47-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J51" s="4" t="str">
+      <c r="K51" s="4" t="str">
         <f>IF(入力!$B47="","",IF(ISNUMBER(入力!$P47),入力!$P47,""))</f>
         <v/>
       </c>
-      <c r="K51" s="5" t="str">
+      <c r="L51" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D47),ISNUMBER(入力!$P47)),入力!$D47*入力!$P47,"")</f>
         <v/>
       </c>
-      <c r="L51" s="5" t="str">
+      <c r="M51" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D47),ISNUMBER(入力!$P47)),MAX(0,入力!$D47-入力!$C$5)*入力!$P47,"")</f>
         <v/>
       </c>
-      <c r="M51" s="5" t="str">
-        <f>IF(入力!$B47="","",IF(AND(NOT(ISNUMBER(G51)),NOT(ISNUMBER(L51))),"",IF(ISNUMBER(G51),G51,0)+IF(ISNUMBER(L51),L51,0)))</f>
+      <c r="N51" s="4" t="str">
+        <f>IF(ISNUMBER(M51),ROUND(M51/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O51" s="5" t="str">
+        <f>IF(入力!$B47="","",IF(AND(NOT(ISNUMBER(G51)),NOT(ISNUMBER(M51))),"",IF(ISNUMBER(G51),G51,0)+IF(ISNUMBER(M51),M51,0)))</f>
+        <v/>
+      </c>
+      <c r="P51" s="4" t="str">
+        <f>IF(入力!$B47="","",IF(AND(NOT(ISNUMBER(H51)),NOT(ISNUMBER(N51))),"",IF(ISNUMBER(H51),H51,0)+IF(ISNUMBER(N51),N51,0)))</f>
         <v/>
       </c>
     </row>
@@ -25451,28 +25937,40 @@
         <f>IF(AND(ISNUMBER(入力!$C48),ISNUMBER(入力!$O48)),MAX(0,入力!$C48-入力!$B$5)*入力!$O48,"")</f>
         <v/>
       </c>
-      <c r="H52" s="5" t="str">
+      <c r="H52" s="4" t="str">
+        <f>IF(ISNUMBER(G52),ROUND(G52/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I52" s="5" t="str">
         <f>IF(入力!$B48="","",IF(ISNUMBER(入力!$D48),入力!$D48,""))</f>
         <v/>
       </c>
-      <c r="I52" s="5" t="str">
+      <c r="J52" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D48),MAX(0,入力!$D48-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J52" s="4" t="str">
+      <c r="K52" s="4" t="str">
         <f>IF(入力!$B48="","",IF(ISNUMBER(入力!$P48),入力!$P48,""))</f>
         <v/>
       </c>
-      <c r="K52" s="5" t="str">
+      <c r="L52" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D48),ISNUMBER(入力!$P48)),入力!$D48*入力!$P48,"")</f>
         <v/>
       </c>
-      <c r="L52" s="5" t="str">
+      <c r="M52" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D48),ISNUMBER(入力!$P48)),MAX(0,入力!$D48-入力!$C$5)*入力!$P48,"")</f>
         <v/>
       </c>
-      <c r="M52" s="5" t="str">
-        <f>IF(入力!$B48="","",IF(AND(NOT(ISNUMBER(G52)),NOT(ISNUMBER(L52))),"",IF(ISNUMBER(G52),G52,0)+IF(ISNUMBER(L52),L52,0)))</f>
+      <c r="N52" s="4" t="str">
+        <f>IF(ISNUMBER(M52),ROUND(M52/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O52" s="5" t="str">
+        <f>IF(入力!$B48="","",IF(AND(NOT(ISNUMBER(G52)),NOT(ISNUMBER(M52))),"",IF(ISNUMBER(G52),G52,0)+IF(ISNUMBER(M52),M52,0)))</f>
+        <v/>
+      </c>
+      <c r="P52" s="4" t="str">
+        <f>IF(入力!$B48="","",IF(AND(NOT(ISNUMBER(H52)),NOT(ISNUMBER(N52))),"",IF(ISNUMBER(H52),H52,0)+IF(ISNUMBER(N52),N52,0)))</f>
         <v/>
       </c>
     </row>
@@ -25501,28 +25999,40 @@
         <f>IF(AND(ISNUMBER(入力!$C49),ISNUMBER(入力!$O49)),MAX(0,入力!$C49-入力!$B$5)*入力!$O49,"")</f>
         <v/>
       </c>
-      <c r="H53" s="5" t="str">
+      <c r="H53" s="4" t="str">
+        <f>IF(ISNUMBER(G53),ROUND(G53/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I53" s="5" t="str">
         <f>IF(入力!$B49="","",IF(ISNUMBER(入力!$D49),入力!$D49,""))</f>
         <v/>
       </c>
-      <c r="I53" s="5" t="str">
+      <c r="J53" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D49),MAX(0,入力!$D49-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J53" s="4" t="str">
+      <c r="K53" s="4" t="str">
         <f>IF(入力!$B49="","",IF(ISNUMBER(入力!$P49),入力!$P49,""))</f>
         <v/>
       </c>
-      <c r="K53" s="5" t="str">
+      <c r="L53" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D49),ISNUMBER(入力!$P49)),入力!$D49*入力!$P49,"")</f>
         <v/>
       </c>
-      <c r="L53" s="5" t="str">
+      <c r="M53" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D49),ISNUMBER(入力!$P49)),MAX(0,入力!$D49-入力!$C$5)*入力!$P49,"")</f>
         <v/>
       </c>
-      <c r="M53" s="5" t="str">
-        <f>IF(入力!$B49="","",IF(AND(NOT(ISNUMBER(G53)),NOT(ISNUMBER(L53))),"",IF(ISNUMBER(G53),G53,0)+IF(ISNUMBER(L53),L53,0)))</f>
+      <c r="N53" s="4" t="str">
+        <f>IF(ISNUMBER(M53),ROUND(M53/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O53" s="5" t="str">
+        <f>IF(入力!$B49="","",IF(AND(NOT(ISNUMBER(G53)),NOT(ISNUMBER(M53))),"",IF(ISNUMBER(G53),G53,0)+IF(ISNUMBER(M53),M53,0)))</f>
+        <v/>
+      </c>
+      <c r="P53" s="4" t="str">
+        <f>IF(入力!$B49="","",IF(AND(NOT(ISNUMBER(H53)),NOT(ISNUMBER(N53))),"",IF(ISNUMBER(H53),H53,0)+IF(ISNUMBER(N53),N53,0)))</f>
         <v/>
       </c>
     </row>
@@ -25551,28 +26061,40 @@
         <f>IF(AND(ISNUMBER(入力!$C50),ISNUMBER(入力!$O50)),MAX(0,入力!$C50-入力!$B$5)*入力!$O50,"")</f>
         <v/>
       </c>
-      <c r="H54" s="5" t="str">
+      <c r="H54" s="4" t="str">
+        <f>IF(ISNUMBER(G54),ROUND(G54/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I54" s="5" t="str">
         <f>IF(入力!$B50="","",IF(ISNUMBER(入力!$D50),入力!$D50,""))</f>
         <v/>
       </c>
-      <c r="I54" s="5" t="str">
+      <c r="J54" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D50),MAX(0,入力!$D50-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J54" s="4" t="str">
+      <c r="K54" s="4" t="str">
         <f>IF(入力!$B50="","",IF(ISNUMBER(入力!$P50),入力!$P50,""))</f>
         <v/>
       </c>
-      <c r="K54" s="5" t="str">
+      <c r="L54" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D50),ISNUMBER(入力!$P50)),入力!$D50*入力!$P50,"")</f>
         <v/>
       </c>
-      <c r="L54" s="5" t="str">
+      <c r="M54" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D50),ISNUMBER(入力!$P50)),MAX(0,入力!$D50-入力!$C$5)*入力!$P50,"")</f>
         <v/>
       </c>
-      <c r="M54" s="5" t="str">
-        <f>IF(入力!$B50="","",IF(AND(NOT(ISNUMBER(G54)),NOT(ISNUMBER(L54))),"",IF(ISNUMBER(G54),G54,0)+IF(ISNUMBER(L54),L54,0)))</f>
+      <c r="N54" s="4" t="str">
+        <f>IF(ISNUMBER(M54),ROUND(M54/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O54" s="5" t="str">
+        <f>IF(入力!$B50="","",IF(AND(NOT(ISNUMBER(G54)),NOT(ISNUMBER(M54))),"",IF(ISNUMBER(G54),G54,0)+IF(ISNUMBER(M54),M54,0)))</f>
+        <v/>
+      </c>
+      <c r="P54" s="4" t="str">
+        <f>IF(入力!$B50="","",IF(AND(NOT(ISNUMBER(H54)),NOT(ISNUMBER(N54))),"",IF(ISNUMBER(H54),H54,0)+IF(ISNUMBER(N54),N54,0)))</f>
         <v/>
       </c>
     </row>
@@ -25601,28 +26123,40 @@
         <f>IF(AND(ISNUMBER(入力!$C51),ISNUMBER(入力!$O51)),MAX(0,入力!$C51-入力!$B$5)*入力!$O51,"")</f>
         <v/>
       </c>
-      <c r="H55" s="5" t="str">
+      <c r="H55" s="4" t="str">
+        <f>IF(ISNUMBER(G55),ROUND(G55/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I55" s="5" t="str">
         <f>IF(入力!$B51="","",IF(ISNUMBER(入力!$D51),入力!$D51,""))</f>
         <v/>
       </c>
-      <c r="I55" s="5" t="str">
+      <c r="J55" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D51),MAX(0,入力!$D51-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J55" s="4" t="str">
+      <c r="K55" s="4" t="str">
         <f>IF(入力!$B51="","",IF(ISNUMBER(入力!$P51),入力!$P51,""))</f>
         <v/>
       </c>
-      <c r="K55" s="5" t="str">
+      <c r="L55" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D51),ISNUMBER(入力!$P51)),入力!$D51*入力!$P51,"")</f>
         <v/>
       </c>
-      <c r="L55" s="5" t="str">
+      <c r="M55" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D51),ISNUMBER(入力!$P51)),MAX(0,入力!$D51-入力!$C$5)*入力!$P51,"")</f>
         <v/>
       </c>
-      <c r="M55" s="5" t="str">
-        <f>IF(入力!$B51="","",IF(AND(NOT(ISNUMBER(G55)),NOT(ISNUMBER(L55))),"",IF(ISNUMBER(G55),G55,0)+IF(ISNUMBER(L55),L55,0)))</f>
+      <c r="N55" s="4" t="str">
+        <f>IF(ISNUMBER(M55),ROUND(M55/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O55" s="5" t="str">
+        <f>IF(入力!$B51="","",IF(AND(NOT(ISNUMBER(G55)),NOT(ISNUMBER(M55))),"",IF(ISNUMBER(G55),G55,0)+IF(ISNUMBER(M55),M55,0)))</f>
+        <v/>
+      </c>
+      <c r="P55" s="4" t="str">
+        <f>IF(入力!$B51="","",IF(AND(NOT(ISNUMBER(H55)),NOT(ISNUMBER(N55))),"",IF(ISNUMBER(H55),H55,0)+IF(ISNUMBER(N55),N55,0)))</f>
         <v/>
       </c>
     </row>
@@ -25651,28 +26185,40 @@
         <f>IF(AND(ISNUMBER(入力!$C52),ISNUMBER(入力!$O52)),MAX(0,入力!$C52-入力!$B$5)*入力!$O52,"")</f>
         <v/>
       </c>
-      <c r="H56" s="5" t="str">
+      <c r="H56" s="4" t="str">
+        <f>IF(ISNUMBER(G56),ROUND(G56/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I56" s="5" t="str">
         <f>IF(入力!$B52="","",IF(ISNUMBER(入力!$D52),入力!$D52,""))</f>
         <v/>
       </c>
-      <c r="I56" s="5" t="str">
+      <c r="J56" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D52),MAX(0,入力!$D52-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J56" s="4" t="str">
+      <c r="K56" s="4" t="str">
         <f>IF(入力!$B52="","",IF(ISNUMBER(入力!$P52),入力!$P52,""))</f>
         <v/>
       </c>
-      <c r="K56" s="5" t="str">
+      <c r="L56" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D52),ISNUMBER(入力!$P52)),入力!$D52*入力!$P52,"")</f>
         <v/>
       </c>
-      <c r="L56" s="5" t="str">
+      <c r="M56" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D52),ISNUMBER(入力!$P52)),MAX(0,入力!$D52-入力!$C$5)*入力!$P52,"")</f>
         <v/>
       </c>
-      <c r="M56" s="5" t="str">
-        <f>IF(入力!$B52="","",IF(AND(NOT(ISNUMBER(G56)),NOT(ISNUMBER(L56))),"",IF(ISNUMBER(G56),G56,0)+IF(ISNUMBER(L56),L56,0)))</f>
+      <c r="N56" s="4" t="str">
+        <f>IF(ISNUMBER(M56),ROUND(M56/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O56" s="5" t="str">
+        <f>IF(入力!$B52="","",IF(AND(NOT(ISNUMBER(G56)),NOT(ISNUMBER(M56))),"",IF(ISNUMBER(G56),G56,0)+IF(ISNUMBER(M56),M56,0)))</f>
+        <v/>
+      </c>
+      <c r="P56" s="4" t="str">
+        <f>IF(入力!$B52="","",IF(AND(NOT(ISNUMBER(H56)),NOT(ISNUMBER(N56))),"",IF(ISNUMBER(H56),H56,0)+IF(ISNUMBER(N56),N56,0)))</f>
         <v/>
       </c>
     </row>
@@ -25701,28 +26247,40 @@
         <f>IF(AND(ISNUMBER(入力!$C53),ISNUMBER(入力!$O53)),MAX(0,入力!$C53-入力!$B$5)*入力!$O53,"")</f>
         <v/>
       </c>
-      <c r="H57" s="5" t="str">
+      <c r="H57" s="4" t="str">
+        <f>IF(ISNUMBER(G57),ROUND(G57/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I57" s="5" t="str">
         <f>IF(入力!$B53="","",IF(ISNUMBER(入力!$D53),入力!$D53,""))</f>
         <v/>
       </c>
-      <c r="I57" s="5" t="str">
+      <c r="J57" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D53),MAX(0,入力!$D53-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J57" s="4" t="str">
+      <c r="K57" s="4" t="str">
         <f>IF(入力!$B53="","",IF(ISNUMBER(入力!$P53),入力!$P53,""))</f>
         <v/>
       </c>
-      <c r="K57" s="5" t="str">
+      <c r="L57" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D53),ISNUMBER(入力!$P53)),入力!$D53*入力!$P53,"")</f>
         <v/>
       </c>
-      <c r="L57" s="5" t="str">
+      <c r="M57" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D53),ISNUMBER(入力!$P53)),MAX(0,入力!$D53-入力!$C$5)*入力!$P53,"")</f>
         <v/>
       </c>
-      <c r="M57" s="5" t="str">
-        <f>IF(入力!$B53="","",IF(AND(NOT(ISNUMBER(G57)),NOT(ISNUMBER(L57))),"",IF(ISNUMBER(G57),G57,0)+IF(ISNUMBER(L57),L57,0)))</f>
+      <c r="N57" s="4" t="str">
+        <f>IF(ISNUMBER(M57),ROUND(M57/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O57" s="5" t="str">
+        <f>IF(入力!$B53="","",IF(AND(NOT(ISNUMBER(G57)),NOT(ISNUMBER(M57))),"",IF(ISNUMBER(G57),G57,0)+IF(ISNUMBER(M57),M57,0)))</f>
+        <v/>
+      </c>
+      <c r="P57" s="4" t="str">
+        <f>IF(入力!$B53="","",IF(AND(NOT(ISNUMBER(H57)),NOT(ISNUMBER(N57))),"",IF(ISNUMBER(H57),H57,0)+IF(ISNUMBER(N57),N57,0)))</f>
         <v/>
       </c>
     </row>
@@ -25751,28 +26309,40 @@
         <f>IF(AND(ISNUMBER(入力!$C54),ISNUMBER(入力!$O54)),MAX(0,入力!$C54-入力!$B$5)*入力!$O54,"")</f>
         <v/>
       </c>
-      <c r="H58" s="5" t="str">
+      <c r="H58" s="4" t="str">
+        <f>IF(ISNUMBER(G58),ROUND(G58/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I58" s="5" t="str">
         <f>IF(入力!$B54="","",IF(ISNUMBER(入力!$D54),入力!$D54,""))</f>
         <v/>
       </c>
-      <c r="I58" s="5" t="str">
+      <c r="J58" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D54),MAX(0,入力!$D54-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J58" s="4" t="str">
+      <c r="K58" s="4" t="str">
         <f>IF(入力!$B54="","",IF(ISNUMBER(入力!$P54),入力!$P54,""))</f>
         <v/>
       </c>
-      <c r="K58" s="5" t="str">
+      <c r="L58" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D54),ISNUMBER(入力!$P54)),入力!$D54*入力!$P54,"")</f>
         <v/>
       </c>
-      <c r="L58" s="5" t="str">
+      <c r="M58" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D54),ISNUMBER(入力!$P54)),MAX(0,入力!$D54-入力!$C$5)*入力!$P54,"")</f>
         <v/>
       </c>
-      <c r="M58" s="5" t="str">
-        <f>IF(入力!$B54="","",IF(AND(NOT(ISNUMBER(G58)),NOT(ISNUMBER(L58))),"",IF(ISNUMBER(G58),G58,0)+IF(ISNUMBER(L58),L58,0)))</f>
+      <c r="N58" s="4" t="str">
+        <f>IF(ISNUMBER(M58),ROUND(M58/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O58" s="5" t="str">
+        <f>IF(入力!$B54="","",IF(AND(NOT(ISNUMBER(G58)),NOT(ISNUMBER(M58))),"",IF(ISNUMBER(G58),G58,0)+IF(ISNUMBER(M58),M58,0)))</f>
+        <v/>
+      </c>
+      <c r="P58" s="4" t="str">
+        <f>IF(入力!$B54="","",IF(AND(NOT(ISNUMBER(H58)),NOT(ISNUMBER(N58))),"",IF(ISNUMBER(H58),H58,0)+IF(ISNUMBER(N58),N58,0)))</f>
         <v/>
       </c>
     </row>
@@ -25801,28 +26371,40 @@
         <f>IF(AND(ISNUMBER(入力!$C55),ISNUMBER(入力!$O55)),MAX(0,入力!$C55-入力!$B$5)*入力!$O55,"")</f>
         <v/>
       </c>
-      <c r="H59" s="5" t="str">
+      <c r="H59" s="4" t="str">
+        <f>IF(ISNUMBER(G59),ROUND(G59/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I59" s="5" t="str">
         <f>IF(入力!$B55="","",IF(ISNUMBER(入力!$D55),入力!$D55,""))</f>
         <v/>
       </c>
-      <c r="I59" s="5" t="str">
+      <c r="J59" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D55),MAX(0,入力!$D55-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J59" s="4" t="str">
+      <c r="K59" s="4" t="str">
         <f>IF(入力!$B55="","",IF(ISNUMBER(入力!$P55),入力!$P55,""))</f>
         <v/>
       </c>
-      <c r="K59" s="5" t="str">
+      <c r="L59" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D55),ISNUMBER(入力!$P55)),入力!$D55*入力!$P55,"")</f>
         <v/>
       </c>
-      <c r="L59" s="5" t="str">
+      <c r="M59" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D55),ISNUMBER(入力!$P55)),MAX(0,入力!$D55-入力!$C$5)*入力!$P55,"")</f>
         <v/>
       </c>
-      <c r="M59" s="5" t="str">
-        <f>IF(入力!$B55="","",IF(AND(NOT(ISNUMBER(G59)),NOT(ISNUMBER(L59))),"",IF(ISNUMBER(G59),G59,0)+IF(ISNUMBER(L59),L59,0)))</f>
+      <c r="N59" s="4" t="str">
+        <f>IF(ISNUMBER(M59),ROUND(M59/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O59" s="5" t="str">
+        <f>IF(入力!$B55="","",IF(AND(NOT(ISNUMBER(G59)),NOT(ISNUMBER(M59))),"",IF(ISNUMBER(G59),G59,0)+IF(ISNUMBER(M59),M59,0)))</f>
+        <v/>
+      </c>
+      <c r="P59" s="4" t="str">
+        <f>IF(入力!$B55="","",IF(AND(NOT(ISNUMBER(H59)),NOT(ISNUMBER(N59))),"",IF(ISNUMBER(H59),H59,0)+IF(ISNUMBER(N59),N59,0)))</f>
         <v/>
       </c>
     </row>
@@ -25851,28 +26433,40 @@
         <f>IF(AND(ISNUMBER(入力!$C56),ISNUMBER(入力!$O56)),MAX(0,入力!$C56-入力!$B$5)*入力!$O56,"")</f>
         <v/>
       </c>
-      <c r="H60" s="5" t="str">
+      <c r="H60" s="4" t="str">
+        <f>IF(ISNUMBER(G60),ROUND(G60/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I60" s="5" t="str">
         <f>IF(入力!$B56="","",IF(ISNUMBER(入力!$D56),入力!$D56,""))</f>
         <v/>
       </c>
-      <c r="I60" s="5" t="str">
+      <c r="J60" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D56),MAX(0,入力!$D56-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J60" s="4" t="str">
+      <c r="K60" s="4" t="str">
         <f>IF(入力!$B56="","",IF(ISNUMBER(入力!$P56),入力!$P56,""))</f>
         <v/>
       </c>
-      <c r="K60" s="5" t="str">
+      <c r="L60" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D56),ISNUMBER(入力!$P56)),入力!$D56*入力!$P56,"")</f>
         <v/>
       </c>
-      <c r="L60" s="5" t="str">
+      <c r="M60" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D56),ISNUMBER(入力!$P56)),MAX(0,入力!$D56-入力!$C$5)*入力!$P56,"")</f>
         <v/>
       </c>
-      <c r="M60" s="5" t="str">
-        <f>IF(入力!$B56="","",IF(AND(NOT(ISNUMBER(G60)),NOT(ISNUMBER(L60))),"",IF(ISNUMBER(G60),G60,0)+IF(ISNUMBER(L60),L60,0)))</f>
+      <c r="N60" s="4" t="str">
+        <f>IF(ISNUMBER(M60),ROUND(M60/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O60" s="5" t="str">
+        <f>IF(入力!$B56="","",IF(AND(NOT(ISNUMBER(G60)),NOT(ISNUMBER(M60))),"",IF(ISNUMBER(G60),G60,0)+IF(ISNUMBER(M60),M60,0)))</f>
+        <v/>
+      </c>
+      <c r="P60" s="4" t="str">
+        <f>IF(入力!$B56="","",IF(AND(NOT(ISNUMBER(H60)),NOT(ISNUMBER(N60))),"",IF(ISNUMBER(H60),H60,0)+IF(ISNUMBER(N60),N60,0)))</f>
         <v/>
       </c>
     </row>
@@ -25901,28 +26495,40 @@
         <f>IF(AND(ISNUMBER(入力!$C57),ISNUMBER(入力!$O57)),MAX(0,入力!$C57-入力!$B$5)*入力!$O57,"")</f>
         <v/>
       </c>
-      <c r="H61" s="5" t="str">
+      <c r="H61" s="4" t="str">
+        <f>IF(ISNUMBER(G61),ROUND(G61/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I61" s="5" t="str">
         <f>IF(入力!$B57="","",IF(ISNUMBER(入力!$D57),入力!$D57,""))</f>
         <v/>
       </c>
-      <c r="I61" s="5" t="str">
+      <c r="J61" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D57),MAX(0,入力!$D57-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J61" s="4" t="str">
+      <c r="K61" s="4" t="str">
         <f>IF(入力!$B57="","",IF(ISNUMBER(入力!$P57),入力!$P57,""))</f>
         <v/>
       </c>
-      <c r="K61" s="5" t="str">
+      <c r="L61" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D57),ISNUMBER(入力!$P57)),入力!$D57*入力!$P57,"")</f>
         <v/>
       </c>
-      <c r="L61" s="5" t="str">
+      <c r="M61" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D57),ISNUMBER(入力!$P57)),MAX(0,入力!$D57-入力!$C$5)*入力!$P57,"")</f>
         <v/>
       </c>
-      <c r="M61" s="5" t="str">
-        <f>IF(入力!$B57="","",IF(AND(NOT(ISNUMBER(G61)),NOT(ISNUMBER(L61))),"",IF(ISNUMBER(G61),G61,0)+IF(ISNUMBER(L61),L61,0)))</f>
+      <c r="N61" s="4" t="str">
+        <f>IF(ISNUMBER(M61),ROUND(M61/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O61" s="5" t="str">
+        <f>IF(入力!$B57="","",IF(AND(NOT(ISNUMBER(G61)),NOT(ISNUMBER(M61))),"",IF(ISNUMBER(G61),G61,0)+IF(ISNUMBER(M61),M61,0)))</f>
+        <v/>
+      </c>
+      <c r="P61" s="4" t="str">
+        <f>IF(入力!$B57="","",IF(AND(NOT(ISNUMBER(H61)),NOT(ISNUMBER(N61))),"",IF(ISNUMBER(H61),H61,0)+IF(ISNUMBER(N61),N61,0)))</f>
         <v/>
       </c>
     </row>
@@ -25951,28 +26557,40 @@
         <f>IF(AND(ISNUMBER(入力!$C58),ISNUMBER(入力!$O58)),MAX(0,入力!$C58-入力!$B$5)*入力!$O58,"")</f>
         <v/>
       </c>
-      <c r="H62" s="5" t="str">
+      <c r="H62" s="4" t="str">
+        <f>IF(ISNUMBER(G62),ROUND(G62/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I62" s="5" t="str">
         <f>IF(入力!$B58="","",IF(ISNUMBER(入力!$D58),入力!$D58,""))</f>
         <v/>
       </c>
-      <c r="I62" s="5" t="str">
+      <c r="J62" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D58),MAX(0,入力!$D58-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="J62" s="4" t="str">
+      <c r="K62" s="4" t="str">
         <f>IF(入力!$B58="","",IF(ISNUMBER(入力!$P58),入力!$P58,""))</f>
         <v/>
       </c>
-      <c r="K62" s="5" t="str">
+      <c r="L62" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D58),ISNUMBER(入力!$P58)),入力!$D58*入力!$P58,"")</f>
         <v/>
       </c>
-      <c r="L62" s="5" t="str">
+      <c r="M62" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D58),ISNUMBER(入力!$P58)),MAX(0,入力!$D58-入力!$C$5)*入力!$P58,"")</f>
         <v/>
       </c>
-      <c r="M62" s="5" t="str">
-        <f>IF(入力!$B58="","",IF(AND(NOT(ISNUMBER(G62)),NOT(ISNUMBER(L62))),"",IF(ISNUMBER(G62),G62,0)+IF(ISNUMBER(L62),L62,0)))</f>
+      <c r="N62" s="4" t="str">
+        <f>IF(ISNUMBER(M62),ROUND(M62/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O62" s="5" t="str">
+        <f>IF(入力!$B58="","",IF(AND(NOT(ISNUMBER(G62)),NOT(ISNUMBER(M62))),"",IF(ISNUMBER(G62),G62,0)+IF(ISNUMBER(M62),M62,0)))</f>
+        <v/>
+      </c>
+      <c r="P62" s="4" t="str">
+        <f>IF(入力!$B58="","",IF(AND(NOT(ISNUMBER(H62)),NOT(ISNUMBER(N62))),"",IF(ISNUMBER(H62),H62,0)+IF(ISNUMBER(N62),N62,0)))</f>
         <v/>
       </c>
     </row>
@@ -26002,47 +26620,60 @@
         <f>SUM(G13:G62)</f>
         <v>1577</v>
       </c>
-      <c r="H63" s="5">
-        <f>IF(SUM(J13:J62)=0,"",SUM(K13:K62)/SUM(J13:J62))</f>
+      <c r="H63" s="4">
+        <f>SUM(H13:H62)</f>
+        <v>985</v>
+      </c>
+      <c r="I63" s="5">
+        <f>IF(SUM(K13:K62)=0,"",SUM(L13:L62)/SUM(K13:K62))</f>
         <v>1.472862</v>
       </c>
-      <c r="I63" s="5">
-        <f>IF(H63="","",MAX(0,H63-入力!$C$5))</f>
+      <c r="J63" s="5">
+        <f>IF(I63="","",MAX(0,I63-入力!$C$5))</f>
         <v>0</v>
       </c>
-      <c r="J63" s="4">
-        <f>SUM(J13:J62)</f>
+      <c r="K63" s="4">
+        <f>SUM(K13:K62)</f>
         <v>20116</v>
-      </c>
-      <c r="K63" s="5">
-        <f>SUM(K13:K62)</f>
-        <v>29628.1</v>
       </c>
       <c r="L63" s="5">
         <f>SUM(L13:L62)</f>
-        <v>2961.2</v>
+        <v>29628.1</v>
       </c>
       <c r="M63" s="5">
         <f>SUM(M13:M62)</f>
+        <v>2961.2</v>
+      </c>
+      <c r="N63" s="4">
+        <f>SUM(N13:N62)</f>
+        <v>1850</v>
+      </c>
+      <c r="O63" s="5">
+        <f>SUM(O13:O62)</f>
         <v>4538.2</v>
+      </c>
+      <c r="P63" s="4">
+        <f>SUM(P13:P62)</f>
+        <v>2835</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">※ 加重平均＝件数で重み付けした平均速度（＝現状総時間合計÷件数合計）。全体が目標1.6分/個に到達するには、加重平均を1.6まで下げる必要がある。短縮効果合計＝全員が目標達成した場合に削減できる総作業時間（分）。</t>
+          <t xml:space="preserve">※ 加重平均＝件数で重み付けした平均速度。追加可能件数＝短縮効果(分)÷目標1.6分/個＝全員が目標達成した場合、浮いた時間で追加処理できる件数の目安（0.5未満は四捨五入）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="B2:M2"/>
+  <mergeCells count="8">
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B10:P10"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:L11"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="B10:M10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="I11:N11"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P11:P12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/個人別作業達成度と改善分析_2026.4_目標到達分析.xlsx
+++ b/個人別作業達成度と改善分析_2026.4_目標到達分析.xlsx
@@ -23286,11 +23286,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:P65"/>
+  <dimension ref="B1:P74"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="16" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -23311,7 +23311,7 @@
     <row r="4">
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数の統計</t>
+          <t xml:space="preserve">① 件数の統計</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
@@ -23385,758 +23385,332 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="B10" s="35" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">▼ 担当者別：目標(1.6分/個)到達に必要な 1個あたり短縮・短縮効果(分)、および短縮効果で追加処理できる件数</t>
+          <t xml:space="preserve">② 全体サマリー（目標到達）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
+          <t xml:space="preserve">項目</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ピッキング</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">梱包</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">総件数</t>
+        </is>
+      </c>
+      <c r="C12" s="4">
+        <f>SUM(E22:E71)</f>
+        <v>19739</v>
+      </c>
+      <c r="D12" s="4">
+        <f>SUM(K22:K71)</f>
+        <v>20116</v>
+      </c>
+      <c r="E12" s="4">
+        <f>C12+D12</f>
+        <v>39855</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">加重平均速度（分/個）</t>
+        </is>
+      </c>
+      <c r="C13" s="5">
+        <f>IF(SUM(E22:E71)=0,"",SUM(F22:F71)/SUM(E22:E71))</f>
+        <v>1.501798</v>
+      </c>
+      <c r="D13" s="5">
+        <f>IF(SUM(K22:K71)=0,"",SUM(L22:L71)/SUM(K22:K71))</f>
+        <v>1.472862</v>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目標との差（分/個）</t>
+        </is>
+      </c>
+      <c r="C14" s="5">
+        <f>IF(C13="","",MAX(0,C13-入力!$B$5))</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <f>IF(D13="","",MAX(0,D13-入力!$C$5))</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">総短縮効果（分）</t>
+        </is>
+      </c>
+      <c r="C15" s="5">
+        <f>SUM(G22:G71)</f>
+        <v>1577</v>
+      </c>
+      <c r="D15" s="5">
+        <f>SUM(M22:M71)</f>
+        <v>2961.2</v>
+      </c>
+      <c r="E15" s="5">
+        <f>C15+D15</f>
+        <v>4538.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">総追加可能件数</t>
+        </is>
+      </c>
+      <c r="C16" s="4">
+        <f>SUM(H22:H71)</f>
+        <v>985</v>
+      </c>
+      <c r="D16" s="4">
+        <f>SUM(N22:N71)</f>
+        <v>1850</v>
+      </c>
+      <c r="E16" s="4">
+        <f>C16+D16</f>
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="25" t="str">
+        <f>="◎ 全員が目標(1.6分/個)に到達すると、同じ稼働時間で 合計 "&amp;TEXT(E16,"#,##0")&amp;" アイテム多く処理可能（削減できる総作業時間 "&amp;TEXT(E15,"#,##0")&amp;" 分 ≒ "&amp;TEXT(E15/60,"0.0")&amp;" 時間）"</f>
+        <v>◎ 全員が目標(1.6分/個)に到達すると、同じ稼働時間で 合計 2,835 アイテム多く処理可能（削減できる総作業時間 4,538 分 ≒ 75.6 時間）</v>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 担当者別 明細：目標到達に必要な1個あたり短縮・短縮効果(分)・追加可能件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="25" t="inlineStr">
+        <is>
           <t xml:space="preserve">担当者</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">ピッキング（目標 1.6 分/個）</t>
         </is>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">梱包（目標 1.6 分/個）</t>
         </is>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25" t="inlineStr">
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">合計短縮効果(分)</t>
         </is>
       </c>
-      <c r="P11" s="25" t="inlineStr">
+      <c r="P20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">合計追加可能件数</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="25"/>
-      <c r="C12" s="25" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="25"/>
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">現状(分/個)</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">必要短縮(分/個)</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">件数</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">現状総時間(分)</t>
         </is>
       </c>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="G21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">短縮効果(分)</t>
         </is>
       </c>
-      <c r="H12" s="25" t="inlineStr">
+      <c r="H21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">追加可能件数</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">現状(分/個)</t>
         </is>
       </c>
-      <c r="J12" s="25" t="inlineStr">
+      <c r="J21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">必要短縮(分/個)</t>
         </is>
       </c>
-      <c r="K12" s="25" t="inlineStr">
+      <c r="K21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">件数</t>
         </is>
       </c>
-      <c r="L12" s="25" t="inlineStr">
+      <c r="L21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">現状総時間(分)</t>
         </is>
       </c>
-      <c r="M12" s="25" t="inlineStr">
+      <c r="M21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">短縮効果(分)</t>
         </is>
       </c>
-      <c r="N12" s="25" t="inlineStr">
+      <c r="N21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">追加可能件数</t>
         </is>
       </c>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="7" t="str">
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="7" t="str">
         <f>IF(入力!$B9="","",入力!$B9)</f>
         <v>佐藤　辰成</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C22" s="5">
         <f>IF(入力!$B9="","",IF(ISNUMBER(入力!$C9),入力!$C9,""))</f>
         <v>1</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D22" s="5">
         <f>IF(ISNUMBER(入力!$C9),MAX(0,入力!$C9-入力!$B$5),"")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E22" s="4">
         <f>IF(入力!$B9="","",IF(ISNUMBER(入力!$O9),入力!$O9,""))</f>
         <v>732</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F22" s="5">
         <f>IF(AND(ISNUMBER(入力!$C9),ISNUMBER(入力!$O9)),入力!$C9*入力!$O9,"")</f>
         <v>732</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G22" s="5">
         <f>IF(AND(ISNUMBER(入力!$C9),ISNUMBER(入力!$O9)),MAX(0,入力!$C9-入力!$B$5)*入力!$O9,"")</f>
         <v>0</v>
       </c>
-      <c r="H13" s="4">
-        <f>IF(ISNUMBER(G13),ROUND(G13/入力!$B$5,0),"")</f>
+      <c r="H22" s="4">
+        <f>IF(ISNUMBER(G22),ROUND(G22/入力!$B$5,0),"")</f>
         <v>0</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I22" s="5">
         <f>IF(入力!$B9="","",IF(ISNUMBER(入力!$D9),入力!$D9,""))</f>
         <v>0.5</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J22" s="5">
         <f>IF(ISNUMBER(入力!$D9),MAX(0,入力!$D9-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K22" s="4">
         <f>IF(入力!$B9="","",IF(ISNUMBER(入力!$P9),入力!$P9,""))</f>
         <v>505</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L22" s="5">
         <f>IF(AND(ISNUMBER(入力!$D9),ISNUMBER(入力!$P9)),入力!$D9*入力!$P9,"")</f>
         <v>252.5</v>
       </c>
-      <c r="M13" s="5">
+      <c r="M22" s="5">
         <f>IF(AND(ISNUMBER(入力!$D9),ISNUMBER(入力!$P9)),MAX(0,入力!$D9-入力!$C$5)*入力!$P9,"")</f>
         <v>0</v>
       </c>
-      <c r="N13" s="4">
-        <f>IF(ISNUMBER(M13),ROUND(M13/入力!$C$5,0),"")</f>
+      <c r="N22" s="4">
+        <f>IF(ISNUMBER(M22),ROUND(M22/入力!$C$5,0),"")</f>
         <v>0</v>
       </c>
-      <c r="O13" s="5">
-        <f>IF(入力!$B9="","",IF(AND(NOT(ISNUMBER(G13)),NOT(ISNUMBER(M13))),"",IF(ISNUMBER(G13),G13,0)+IF(ISNUMBER(M13),M13,0)))</f>
+      <c r="O22" s="5">
+        <f>IF(入力!$B9="","",IF(AND(NOT(ISNUMBER(G22)),NOT(ISNUMBER(M22))),"",IF(ISNUMBER(G22),G22,0)+IF(ISNUMBER(M22),M22,0)))</f>
         <v>0</v>
       </c>
-      <c r="P13" s="4">
-        <f>IF(入力!$B9="","",IF(AND(NOT(ISNUMBER(H13)),NOT(ISNUMBER(N13))),"",IF(ISNUMBER(H13),H13,0)+IF(ISNUMBER(N13),N13,0)))</f>
+      <c r="P22" s="4">
+        <f>IF(入力!$B9="","",IF(AND(NOT(ISNUMBER(H22)),NOT(ISNUMBER(N22))),"",IF(ISNUMBER(H22),H22,0)+IF(ISNUMBER(N22),N22,0)))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="7" t="str">
+    <row r="23">
+      <c r="B23" s="7" t="str">
         <f>IF(入力!$B10="","",入力!$B10)</f>
         <v>河野　忠</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C23" s="5">
         <f>IF(入力!$B10="","",IF(ISNUMBER(入力!$C10),入力!$C10,""))</f>
         <v>1.2</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D23" s="5">
         <f>IF(ISNUMBER(入力!$C10),MAX(0,入力!$C10-入力!$B$5),"")</f>
         <v>0</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E23" s="4">
         <f>IF(入力!$B10="","",IF(ISNUMBER(入力!$O10),入力!$O10,""))</f>
         <v>365</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F23" s="5">
         <f>IF(AND(ISNUMBER(入力!$C10),ISNUMBER(入力!$O10)),入力!$C10*入力!$O10,"")</f>
         <v>438</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G23" s="5">
         <f>IF(AND(ISNUMBER(入力!$C10),ISNUMBER(入力!$O10)),MAX(0,入力!$C10-入力!$B$5)*入力!$O10,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="4">
-        <f>IF(ISNUMBER(G14),ROUND(G14/入力!$B$5,0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="5">
-        <f>IF(入力!$B10="","",IF(ISNUMBER(入力!$D10),入力!$D10,""))</f>
-        <v>1</v>
-      </c>
-      <c r="J14" s="5">
-        <f>IF(ISNUMBER(入力!$D10),MAX(0,入力!$D10-入力!$C$5),"")</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="4">
-        <f>IF(入力!$B10="","",IF(ISNUMBER(入力!$P10),入力!$P10,""))</f>
-        <v>656</v>
-      </c>
-      <c r="L14" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D10),ISNUMBER(入力!$P10)),入力!$D10*入力!$P10,"")</f>
-        <v>656</v>
-      </c>
-      <c r="M14" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D10),ISNUMBER(入力!$P10)),MAX(0,入力!$D10-入力!$C$5)*入力!$P10,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="4">
-        <f>IF(ISNUMBER(M14),ROUND(M14/入力!$C$5,0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="5">
-        <f>IF(入力!$B10="","",IF(AND(NOT(ISNUMBER(G14)),NOT(ISNUMBER(M14))),"",IF(ISNUMBER(G14),G14,0)+IF(ISNUMBER(M14),M14,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="4">
-        <f>IF(入力!$B10="","",IF(AND(NOT(ISNUMBER(H14)),NOT(ISNUMBER(N14))),"",IF(ISNUMBER(H14),H14,0)+IF(ISNUMBER(N14),N14,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="str">
-        <f>IF(入力!$B11="","",入力!$B11)</f>
-        <v>中納　沙織</v>
-      </c>
-      <c r="C15" s="5">
-        <f>IF(入力!$B11="","",IF(ISNUMBER(入力!$C11),入力!$C11,""))</f>
-        <v>1.3</v>
-      </c>
-      <c r="D15" s="5">
-        <f>IF(ISNUMBER(入力!$C11),MAX(0,入力!$C11-入力!$B$5),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="4">
-        <f>IF(入力!$B11="","",IF(ISNUMBER(入力!$O11),入力!$O11,""))</f>
-        <v>1143</v>
-      </c>
-      <c r="F15" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C11),ISNUMBER(入力!$O11)),入力!$C11*入力!$O11,"")</f>
-        <v>1485.9</v>
-      </c>
-      <c r="G15" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C11),ISNUMBER(入力!$O11)),MAX(0,入力!$C11-入力!$B$5)*入力!$O11,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="4">
-        <f>IF(ISNUMBER(G15),ROUND(G15/入力!$B$5,0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="5">
-        <f>IF(入力!$B11="","",IF(ISNUMBER(入力!$D11),入力!$D11,""))</f>
-        <v>2.1</v>
-      </c>
-      <c r="J15" s="5">
-        <f>IF(ISNUMBER(入力!$D11),MAX(0,入力!$D11-入力!$C$5),"")</f>
-        <v>0.5</v>
-      </c>
-      <c r="K15" s="4">
-        <f>IF(入力!$B11="","",IF(ISNUMBER(入力!$P11),入力!$P11,""))</f>
-        <v>224</v>
-      </c>
-      <c r="L15" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D11),ISNUMBER(入力!$P11)),入力!$D11*入力!$P11,"")</f>
-        <v>470.4</v>
-      </c>
-      <c r="M15" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D11),ISNUMBER(入力!$P11)),MAX(0,入力!$D11-入力!$C$5)*入力!$P11,"")</f>
-        <v>112</v>
-      </c>
-      <c r="N15" s="4">
-        <f>IF(ISNUMBER(M15),ROUND(M15/入力!$C$5,0),"")</f>
-        <v>70</v>
-      </c>
-      <c r="O15" s="5">
-        <f>IF(入力!$B11="","",IF(AND(NOT(ISNUMBER(G15)),NOT(ISNUMBER(M15))),"",IF(ISNUMBER(G15),G15,0)+IF(ISNUMBER(M15),M15,0)))</f>
-        <v>112</v>
-      </c>
-      <c r="P15" s="4">
-        <f>IF(入力!$B11="","",IF(AND(NOT(ISNUMBER(H15)),NOT(ISNUMBER(N15))),"",IF(ISNUMBER(H15),H15,0)+IF(ISNUMBER(N15),N15,0)))</f>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="7" t="str">
-        <f>IF(入力!$B12="","",入力!$B12)</f>
-        <v>澤田　凌</v>
-      </c>
-      <c r="C16" s="5">
-        <f>IF(入力!$B12="","",IF(ISNUMBER(入力!$C12),入力!$C12,""))</f>
-        <v>1.6</v>
-      </c>
-      <c r="D16" s="5">
-        <f>IF(ISNUMBER(入力!$C12),MAX(0,入力!$C12-入力!$B$5),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
-        <f>IF(入力!$B12="","",IF(ISNUMBER(入力!$O12),入力!$O12,""))</f>
-        <v>847</v>
-      </c>
-      <c r="F16" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C12),ISNUMBER(入力!$O12)),入力!$C12*入力!$O12,"")</f>
-        <v>1355.2</v>
-      </c>
-      <c r="G16" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C12),ISNUMBER(入力!$O12)),MAX(0,入力!$C12-入力!$B$5)*入力!$O12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="4">
-        <f>IF(ISNUMBER(G16),ROUND(G16/入力!$B$5,0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="5">
-        <f>IF(入力!$B12="","",IF(ISNUMBER(入力!$D12),入力!$D12,""))</f>
-        <v>1.6</v>
-      </c>
-      <c r="J16" s="5">
-        <f>IF(ISNUMBER(入力!$D12),MAX(0,入力!$D12-入力!$C$5),"")</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="4">
-        <f>IF(入力!$B12="","",IF(ISNUMBER(入力!$P12),入力!$P12,""))</f>
-        <v>939</v>
-      </c>
-      <c r="L16" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D12),ISNUMBER(入力!$P12)),入力!$D12*入力!$P12,"")</f>
-        <v>1502.4</v>
-      </c>
-      <c r="M16" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D12),ISNUMBER(入力!$P12)),MAX(0,入力!$D12-入力!$C$5)*入力!$P12,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="4">
-        <f>IF(ISNUMBER(M16),ROUND(M16/入力!$C$5,0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O16" s="5">
-        <f>IF(入力!$B12="","",IF(AND(NOT(ISNUMBER(G16)),NOT(ISNUMBER(M16))),"",IF(ISNUMBER(G16),G16,0)+IF(ISNUMBER(M16),M16,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="4">
-        <f>IF(入力!$B12="","",IF(AND(NOT(ISNUMBER(H16)),NOT(ISNUMBER(N16))),"",IF(ISNUMBER(H16),H16,0)+IF(ISNUMBER(N16),N16,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="7" t="str">
-        <f>IF(入力!$B13="","",入力!$B13)</f>
-        <v>佐々木　千恵</v>
-      </c>
-      <c r="C17" s="5">
-        <f>IF(入力!$B13="","",IF(ISNUMBER(入力!$C13),入力!$C13,""))</f>
-        <v>1.7</v>
-      </c>
-      <c r="D17" s="5">
-        <f>IF(ISNUMBER(入力!$C13),MAX(0,入力!$C13-入力!$B$5),"")</f>
-        <v>0.1</v>
-      </c>
-      <c r="E17" s="4">
-        <f>IF(入力!$B13="","",IF(ISNUMBER(入力!$O13),入力!$O13,""))</f>
-        <v>681</v>
-      </c>
-      <c r="F17" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C13),ISNUMBER(入力!$O13)),入力!$C13*入力!$O13,"")</f>
-        <v>1157.7</v>
-      </c>
-      <c r="G17" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C13),ISNUMBER(入力!$O13)),MAX(0,入力!$C13-入力!$B$5)*入力!$O13,"")</f>
-        <v>68.1</v>
-      </c>
-      <c r="H17" s="4">
-        <f>IF(ISNUMBER(G17),ROUND(G17/入力!$B$5,0),"")</f>
-        <v>43</v>
-      </c>
-      <c r="I17" s="5">
-        <f>IF(入力!$B13="","",IF(ISNUMBER(入力!$D13),入力!$D13,""))</f>
-        <v>0.6</v>
-      </c>
-      <c r="J17" s="5">
-        <f>IF(ISNUMBER(入力!$D13),MAX(0,入力!$D13-入力!$C$5),"")</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="4">
-        <f>IF(入力!$B13="","",IF(ISNUMBER(入力!$P13),入力!$P13,""))</f>
-        <v>1223</v>
-      </c>
-      <c r="L17" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D13),ISNUMBER(入力!$P13)),入力!$D13*入力!$P13,"")</f>
-        <v>733.8</v>
-      </c>
-      <c r="M17" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D13),ISNUMBER(入力!$P13)),MAX(0,入力!$D13-入力!$C$5)*入力!$P13,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="4">
-        <f>IF(ISNUMBER(M17),ROUND(M17/入力!$C$5,0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O17" s="5">
-        <f>IF(入力!$B13="","",IF(AND(NOT(ISNUMBER(G17)),NOT(ISNUMBER(M17))),"",IF(ISNUMBER(G17),G17,0)+IF(ISNUMBER(M17),M17,0)))</f>
-        <v>68.1</v>
-      </c>
-      <c r="P17" s="4">
-        <f>IF(入力!$B13="","",IF(AND(NOT(ISNUMBER(H17)),NOT(ISNUMBER(N17))),"",IF(ISNUMBER(H17),H17,0)+IF(ISNUMBER(N17),N17,0)))</f>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="7" t="str">
-        <f>IF(入力!$B14="","",入力!$B14)</f>
-        <v>片岡　達也</v>
-      </c>
-      <c r="C18" s="5">
-        <f>IF(入力!$B14="","",IF(ISNUMBER(入力!$C14),入力!$C14,""))</f>
-        <v>3.1</v>
-      </c>
-      <c r="D18" s="5">
-        <f>IF(ISNUMBER(入力!$C14),MAX(0,入力!$C14-入力!$B$5),"")</f>
-        <v>1.5</v>
-      </c>
-      <c r="E18" s="4">
-        <f>IF(入力!$B14="","",IF(ISNUMBER(入力!$O14),入力!$O14,""))</f>
-        <v>66</v>
-      </c>
-      <c r="F18" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C14),ISNUMBER(入力!$O14)),入力!$C14*入力!$O14,"")</f>
-        <v>204.6</v>
-      </c>
-      <c r="G18" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C14),ISNUMBER(入力!$O14)),MAX(0,入力!$C14-入力!$B$5)*入力!$O14,"")</f>
-        <v>99</v>
-      </c>
-      <c r="H18" s="4">
-        <f>IF(ISNUMBER(G18),ROUND(G18/入力!$B$5,0),"")</f>
-        <v>62</v>
-      </c>
-      <c r="I18" s="5">
-        <f>IF(入力!$B14="","",IF(ISNUMBER(入力!$D14),入力!$D14,""))</f>
-        <v>0.6</v>
-      </c>
-      <c r="J18" s="5">
-        <f>IF(ISNUMBER(入力!$D14),MAX(0,入力!$D14-入力!$C$5),"")</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="4">
-        <f>IF(入力!$B14="","",IF(ISNUMBER(入力!$P14),入力!$P14,""))</f>
-        <v>16</v>
-      </c>
-      <c r="L18" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D14),ISNUMBER(入力!$P14)),入力!$D14*入力!$P14,"")</f>
-        <v>9.6</v>
-      </c>
-      <c r="M18" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D14),ISNUMBER(入力!$P14)),MAX(0,入力!$D14-入力!$C$5)*入力!$P14,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="4">
-        <f>IF(ISNUMBER(M18),ROUND(M18/入力!$C$5,0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O18" s="5">
-        <f>IF(入力!$B14="","",IF(AND(NOT(ISNUMBER(G18)),NOT(ISNUMBER(M18))),"",IF(ISNUMBER(G18),G18,0)+IF(ISNUMBER(M18),M18,0)))</f>
-        <v>99</v>
-      </c>
-      <c r="P18" s="4">
-        <f>IF(入力!$B14="","",IF(AND(NOT(ISNUMBER(H18)),NOT(ISNUMBER(N18))),"",IF(ISNUMBER(H18),H18,0)+IF(ISNUMBER(N18),N18,0)))</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="7" t="str">
-        <f>IF(入力!$B15="","",入力!$B15)</f>
-        <v>後藤　克行</v>
-      </c>
-      <c r="C19" s="5">
-        <f>IF(入力!$B15="","",IF(ISNUMBER(入力!$C15),入力!$C15,""))</f>
-        <v>1.5</v>
-      </c>
-      <c r="D19" s="5">
-        <f>IF(ISNUMBER(入力!$C15),MAX(0,入力!$C15-入力!$B$5),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="4">
-        <f>IF(入力!$B15="","",IF(ISNUMBER(入力!$O15),入力!$O15,""))</f>
-        <v>2007</v>
-      </c>
-      <c r="F19" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C15),ISNUMBER(入力!$O15)),入力!$C15*入力!$O15,"")</f>
-        <v>3010.5</v>
-      </c>
-      <c r="G19" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C15),ISNUMBER(入力!$O15)),MAX(0,入力!$C15-入力!$B$5)*入力!$O15,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="4">
-        <f>IF(ISNUMBER(G19),ROUND(G19/入力!$B$5,0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="5">
-        <f>IF(入力!$B15="","",IF(ISNUMBER(入力!$D15),入力!$D15,""))</f>
-        <v>1.9</v>
-      </c>
-      <c r="J19" s="5">
-        <f>IF(ISNUMBER(入力!$D15),MAX(0,入力!$D15-入力!$C$5),"")</f>
-        <v>0.3</v>
-      </c>
-      <c r="K19" s="4">
-        <f>IF(入力!$B15="","",IF(ISNUMBER(入力!$P15),入力!$P15,""))</f>
-        <v>1421</v>
-      </c>
-      <c r="L19" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D15),ISNUMBER(入力!$P15)),入力!$D15*入力!$P15,"")</f>
-        <v>2699.9</v>
-      </c>
-      <c r="M19" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D15),ISNUMBER(入力!$P15)),MAX(0,入力!$D15-入力!$C$5)*入力!$P15,"")</f>
-        <v>426.3</v>
-      </c>
-      <c r="N19" s="4">
-        <f>IF(ISNUMBER(M19),ROUND(M19/入力!$C$5,0),"")</f>
-        <v>266</v>
-      </c>
-      <c r="O19" s="5">
-        <f>IF(入力!$B15="","",IF(AND(NOT(ISNUMBER(G19)),NOT(ISNUMBER(M19))),"",IF(ISNUMBER(G19),G19,0)+IF(ISNUMBER(M19),M19,0)))</f>
-        <v>426.3</v>
-      </c>
-      <c r="P19" s="4">
-        <f>IF(入力!$B15="","",IF(AND(NOT(ISNUMBER(H19)),NOT(ISNUMBER(N19))),"",IF(ISNUMBER(H19),H19,0)+IF(ISNUMBER(N19),N19,0)))</f>
-        <v>266</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="7" t="str">
-        <f>IF(入力!$B16="","",入力!$B16)</f>
-        <v>山本　祥吉</v>
-      </c>
-      <c r="C20" s="5">
-        <f>IF(入力!$B16="","",IF(ISNUMBER(入力!$C16),入力!$C16,""))</f>
-        <v>1.4</v>
-      </c>
-      <c r="D20" s="5">
-        <f>IF(ISNUMBER(入力!$C16),MAX(0,入力!$C16-入力!$B$5),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="4">
-        <f>IF(入力!$B16="","",IF(ISNUMBER(入力!$O16),入力!$O16,""))</f>
-        <v>2129</v>
-      </c>
-      <c r="F20" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C16),ISNUMBER(入力!$O16)),入力!$C16*入力!$O16,"")</f>
-        <v>2980.6</v>
-      </c>
-      <c r="G20" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C16),ISNUMBER(入力!$O16)),MAX(0,入力!$C16-入力!$B$5)*入力!$O16,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="4">
-        <f>IF(ISNUMBER(G20),ROUND(G20/入力!$B$5,0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="5">
-        <f>IF(入力!$B16="","",IF(ISNUMBER(入力!$D16),入力!$D16,""))</f>
-        <v>1.8</v>
-      </c>
-      <c r="J20" s="5">
-        <f>IF(ISNUMBER(入力!$D16),MAX(0,入力!$D16-入力!$C$5),"")</f>
-        <v>0.2</v>
-      </c>
-      <c r="K20" s="4">
-        <f>IF(入力!$B16="","",IF(ISNUMBER(入力!$P16),入力!$P16,""))</f>
-        <v>1548</v>
-      </c>
-      <c r="L20" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D16),ISNUMBER(入力!$P16)),入力!$D16*入力!$P16,"")</f>
-        <v>2786.4</v>
-      </c>
-      <c r="M20" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D16),ISNUMBER(入力!$P16)),MAX(0,入力!$D16-入力!$C$5)*入力!$P16,"")</f>
-        <v>309.6</v>
-      </c>
-      <c r="N20" s="4">
-        <f>IF(ISNUMBER(M20),ROUND(M20/入力!$C$5,0),"")</f>
-        <v>193</v>
-      </c>
-      <c r="O20" s="5">
-        <f>IF(入力!$B16="","",IF(AND(NOT(ISNUMBER(G20)),NOT(ISNUMBER(M20))),"",IF(ISNUMBER(G20),G20,0)+IF(ISNUMBER(M20),M20,0)))</f>
-        <v>309.6</v>
-      </c>
-      <c r="P20" s="4">
-        <f>IF(入力!$B16="","",IF(AND(NOT(ISNUMBER(H20)),NOT(ISNUMBER(N20))),"",IF(ISNUMBER(H20),H20,0)+IF(ISNUMBER(N20),N20,0)))</f>
-        <v>193</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="7" t="str">
-        <f>IF(入力!$B17="","",入力!$B17)</f>
-        <v>本吉　有美子</v>
-      </c>
-      <c r="C21" s="5">
-        <f>IF(入力!$B17="","",IF(ISNUMBER(入力!$C17),入力!$C17,""))</f>
-        <v>1.1</v>
-      </c>
-      <c r="D21" s="5">
-        <f>IF(ISNUMBER(入力!$C17),MAX(0,入力!$C17-入力!$B$5),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="4">
-        <f>IF(入力!$B17="","",IF(ISNUMBER(入力!$O17),入力!$O17,""))</f>
-        <v>1454</v>
-      </c>
-      <c r="F21" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C17),ISNUMBER(入力!$O17)),入力!$C17*入力!$O17,"")</f>
-        <v>1599.4</v>
-      </c>
-      <c r="G21" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C17),ISNUMBER(入力!$O17)),MAX(0,入力!$C17-入力!$B$5)*入力!$O17,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="4">
-        <f>IF(ISNUMBER(G21),ROUND(G21/入力!$B$5,0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="5">
-        <f>IF(入力!$B17="","",IF(ISNUMBER(入力!$D17),入力!$D17,""))</f>
-        <v>1</v>
-      </c>
-      <c r="J21" s="5">
-        <f>IF(ISNUMBER(入力!$D17),MAX(0,入力!$D17-入力!$C$5),"")</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="4">
-        <f>IF(入力!$B17="","",IF(ISNUMBER(入力!$P17),入力!$P17,""))</f>
-        <v>2493</v>
-      </c>
-      <c r="L21" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D17),ISNUMBER(入力!$P17)),入力!$D17*入力!$P17,"")</f>
-        <v>2493</v>
-      </c>
-      <c r="M21" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D17),ISNUMBER(入力!$P17)),MAX(0,入力!$D17-入力!$C$5)*入力!$P17,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N21" s="4">
-        <f>IF(ISNUMBER(M21),ROUND(M21/入力!$C$5,0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O21" s="5">
-        <f>IF(入力!$B17="","",IF(AND(NOT(ISNUMBER(G21)),NOT(ISNUMBER(M21))),"",IF(ISNUMBER(G21),G21,0)+IF(ISNUMBER(M21),M21,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="P21" s="4">
-        <f>IF(入力!$B17="","",IF(AND(NOT(ISNUMBER(H21)),NOT(ISNUMBER(N21))),"",IF(ISNUMBER(H21),H21,0)+IF(ISNUMBER(N21),N21,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="7" t="str">
-        <f>IF(入力!$B18="","",入力!$B18)</f>
-        <v>屋宮　敬子</v>
-      </c>
-      <c r="C22" s="5" t="str">
-        <f>IF(入力!$B18="","",IF(ISNUMBER(入力!$C18),入力!$C18,""))</f>
-        <v/>
-      </c>
-      <c r="D22" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C18),MAX(0,入力!$C18-入力!$B$5),"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="4" t="str">
-        <f>IF(入力!$B18="","",IF(ISNUMBER(入力!$O18),入力!$O18,""))</f>
-        <v/>
-      </c>
-      <c r="F22" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C18),ISNUMBER(入力!$O18)),入力!$C18*入力!$O18,"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C18),ISNUMBER(入力!$O18)),MAX(0,入力!$C18-入力!$B$5)*入力!$O18,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="str">
-        <f>IF(ISNUMBER(G22),ROUND(G22/入力!$B$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="5" t="str">
-        <f>IF(入力!$B18="","",IF(ISNUMBER(入力!$D18),入力!$D18,""))</f>
-        <v/>
-      </c>
-      <c r="J22" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D18),MAX(0,入力!$D18-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K22" s="4" t="str">
-        <f>IF(入力!$B18="","",IF(ISNUMBER(入力!$P18),入力!$P18,""))</f>
-        <v/>
-      </c>
-      <c r="L22" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D18),ISNUMBER(入力!$P18)),入力!$D18*入力!$P18,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D18),ISNUMBER(入力!$P18)),MAX(0,入力!$D18-入力!$C$5)*入力!$P18,"")</f>
-        <v/>
-      </c>
-      <c r="N22" s="4" t="str">
-        <f>IF(ISNUMBER(M22),ROUND(M22/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O22" s="5" t="str">
-        <f>IF(入力!$B18="","",IF(AND(NOT(ISNUMBER(G22)),NOT(ISNUMBER(M22))),"",IF(ISNUMBER(G22),G22,0)+IF(ISNUMBER(M22),M22,0)))</f>
-        <v/>
-      </c>
-      <c r="P22" s="4" t="str">
-        <f>IF(入力!$B18="","",IF(AND(NOT(ISNUMBER(H22)),NOT(ISNUMBER(N22))),"",IF(ISNUMBER(H22),H22,0)+IF(ISNUMBER(N22),N22,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="7" t="str">
-        <f>IF(入力!$B19="","",入力!$B19)</f>
-        <v>大江　美記子</v>
-      </c>
-      <c r="C23" s="5">
-        <f>IF(入力!$B19="","",IF(ISNUMBER(入力!$C19),入力!$C19,""))</f>
-        <v>1.2</v>
-      </c>
-      <c r="D23" s="5">
-        <f>IF(ISNUMBER(入力!$C19),MAX(0,入力!$C19-入力!$B$5),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
-        <f>IF(入力!$B19="","",IF(ISNUMBER(入力!$O19),入力!$O19,""))</f>
-        <v>1053</v>
-      </c>
-      <c r="F23" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C19),ISNUMBER(入力!$O19)),入力!$C19*入力!$O19,"")</f>
-        <v>1263.6</v>
-      </c>
-      <c r="G23" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C19),ISNUMBER(入力!$O19)),MAX(0,入力!$C19-入力!$B$5)*入力!$O19,"")</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
@@ -24144,23 +23718,23 @@
         <v>0</v>
       </c>
       <c r="I23" s="5">
-        <f>IF(入力!$B19="","",IF(ISNUMBER(入力!$D19),入力!$D19,""))</f>
-        <v>1.2</v>
+        <f>IF(入力!$B10="","",IF(ISNUMBER(入力!$D10),入力!$D10,""))</f>
+        <v>1</v>
       </c>
       <c r="J23" s="5">
-        <f>IF(ISNUMBER(入力!$D19),MAX(0,入力!$D19-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D10),MAX(0,入力!$D10-入力!$C$5),"")</f>
         <v>0</v>
       </c>
       <c r="K23" s="4">
-        <f>IF(入力!$B19="","",IF(ISNUMBER(入力!$P19),入力!$P19,""))</f>
-        <v>2616</v>
+        <f>IF(入力!$B10="","",IF(ISNUMBER(入力!$P10),入力!$P10,""))</f>
+        <v>656</v>
       </c>
       <c r="L23" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D19),ISNUMBER(入力!$P19)),入力!$D19*入力!$P19,"")</f>
-        <v>3139.2</v>
+        <f>IF(AND(ISNUMBER(入力!$D10),ISNUMBER(入力!$P10)),入力!$D10*入力!$P10,"")</f>
+        <v>656</v>
       </c>
       <c r="M23" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D19),ISNUMBER(入力!$P19)),MAX(0,入力!$D19-入力!$C$5)*入力!$P19,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D10),ISNUMBER(入力!$P10)),MAX(0,入力!$D10-入力!$C$5)*入力!$P10,"")</f>
         <v>0</v>
       </c>
       <c r="N23" s="4">
@@ -24168,99 +23742,99 @@
         <v>0</v>
       </c>
       <c r="O23" s="5">
-        <f>IF(入力!$B19="","",IF(AND(NOT(ISNUMBER(G23)),NOT(ISNUMBER(M23))),"",IF(ISNUMBER(G23),G23,0)+IF(ISNUMBER(M23),M23,0)))</f>
+        <f>IF(入力!$B10="","",IF(AND(NOT(ISNUMBER(G23)),NOT(ISNUMBER(M23))),"",IF(ISNUMBER(G23),G23,0)+IF(ISNUMBER(M23),M23,0)))</f>
         <v>0</v>
       </c>
       <c r="P23" s="4">
-        <f>IF(入力!$B19="","",IF(AND(NOT(ISNUMBER(H23)),NOT(ISNUMBER(N23))),"",IF(ISNUMBER(H23),H23,0)+IF(ISNUMBER(N23),N23,0)))</f>
+        <f>IF(入力!$B10="","",IF(AND(NOT(ISNUMBER(H23)),NOT(ISNUMBER(N23))),"",IF(ISNUMBER(H23),H23,0)+IF(ISNUMBER(N23),N23,0)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="7" t="str">
-        <f>IF(入力!$B20="","",入力!$B20)</f>
-        <v>木村　千鶴</v>
+        <f>IF(入力!$B11="","",入力!$B11)</f>
+        <v>中納　沙織</v>
       </c>
       <c r="C24" s="5">
-        <f>IF(入力!$B20="","",IF(ISNUMBER(入力!$C20),入力!$C20,""))</f>
-        <v>1.7</v>
+        <f>IF(入力!$B11="","",IF(ISNUMBER(入力!$C11),入力!$C11,""))</f>
+        <v>1.3</v>
       </c>
       <c r="D24" s="5">
-        <f>IF(ISNUMBER(入力!$C20),MAX(0,入力!$C20-入力!$B$5),"")</f>
-        <v>0.1</v>
+        <f>IF(ISNUMBER(入力!$C11),MAX(0,入力!$C11-入力!$B$5),"")</f>
+        <v>0</v>
       </c>
       <c r="E24" s="4">
-        <f>IF(入力!$B20="","",IF(ISNUMBER(入力!$O20),入力!$O20,""))</f>
-        <v>691</v>
+        <f>IF(入力!$B11="","",IF(ISNUMBER(入力!$O11),入力!$O11,""))</f>
+        <v>1143</v>
       </c>
       <c r="F24" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C20),ISNUMBER(入力!$O20)),入力!$C20*入力!$O20,"")</f>
-        <v>1174.7</v>
+        <f>IF(AND(ISNUMBER(入力!$C11),ISNUMBER(入力!$O11)),入力!$C11*入力!$O11,"")</f>
+        <v>1485.9</v>
       </c>
       <c r="G24" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C20),ISNUMBER(入力!$O20)),MAX(0,入力!$C20-入力!$B$5)*入力!$O20,"")</f>
-        <v>69.1</v>
+        <f>IF(AND(ISNUMBER(入力!$C11),ISNUMBER(入力!$O11)),MAX(0,入力!$C11-入力!$B$5)*入力!$O11,"")</f>
+        <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>IF(ISNUMBER(G24),ROUND(G24/入力!$B$5,0),"")</f>
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I24" s="5">
-        <f>IF(入力!$B20="","",IF(ISNUMBER(入力!$D20),入力!$D20,""))</f>
-        <v>2.2</v>
+        <f>IF(入力!$B11="","",IF(ISNUMBER(入力!$D11),入力!$D11,""))</f>
+        <v>2.1</v>
       </c>
       <c r="J24" s="5">
-        <f>IF(ISNUMBER(入力!$D20),MAX(0,入力!$D20-入力!$C$5),"")</f>
-        <v>0.6</v>
+        <f>IF(ISNUMBER(入力!$D11),MAX(0,入力!$D11-入力!$C$5),"")</f>
+        <v>0.5</v>
       </c>
       <c r="K24" s="4">
-        <f>IF(入力!$B20="","",IF(ISNUMBER(入力!$P20),入力!$P20,""))</f>
-        <v>1750</v>
+        <f>IF(入力!$B11="","",IF(ISNUMBER(入力!$P11),入力!$P11,""))</f>
+        <v>224</v>
       </c>
       <c r="L24" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D20),ISNUMBER(入力!$P20)),入力!$D20*入力!$P20,"")</f>
-        <v>3850</v>
+        <f>IF(AND(ISNUMBER(入力!$D11),ISNUMBER(入力!$P11)),入力!$D11*入力!$P11,"")</f>
+        <v>470.4</v>
       </c>
       <c r="M24" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D20),ISNUMBER(入力!$P20)),MAX(0,入力!$D20-入力!$C$5)*入力!$P20,"")</f>
-        <v>1050</v>
+        <f>IF(AND(ISNUMBER(入力!$D11),ISNUMBER(入力!$P11)),MAX(0,入力!$D11-入力!$C$5)*入力!$P11,"")</f>
+        <v>112</v>
       </c>
       <c r="N24" s="4">
         <f>IF(ISNUMBER(M24),ROUND(M24/入力!$C$5,0),"")</f>
-        <v>656</v>
+        <v>70</v>
       </c>
       <c r="O24" s="5">
-        <f>IF(入力!$B20="","",IF(AND(NOT(ISNUMBER(G24)),NOT(ISNUMBER(M24))),"",IF(ISNUMBER(G24),G24,0)+IF(ISNUMBER(M24),M24,0)))</f>
-        <v>1119.1</v>
+        <f>IF(入力!$B11="","",IF(AND(NOT(ISNUMBER(G24)),NOT(ISNUMBER(M24))),"",IF(ISNUMBER(G24),G24,0)+IF(ISNUMBER(M24),M24,0)))</f>
+        <v>112</v>
       </c>
       <c r="P24" s="4">
-        <f>IF(入力!$B20="","",IF(AND(NOT(ISNUMBER(H24)),NOT(ISNUMBER(N24))),"",IF(ISNUMBER(H24),H24,0)+IF(ISNUMBER(N24),N24,0)))</f>
-        <v>699</v>
+        <f>IF(入力!$B11="","",IF(AND(NOT(ISNUMBER(H24)),NOT(ISNUMBER(N24))),"",IF(ISNUMBER(H24),H24,0)+IF(ISNUMBER(N24),N24,0)))</f>
+        <v>70</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="7" t="str">
-        <f>IF(入力!$B21="","",入力!$B21)</f>
-        <v>晩田　恵美</v>
+        <f>IF(入力!$B12="","",入力!$B12)</f>
+        <v>澤田　凌</v>
       </c>
       <c r="C25" s="5">
-        <f>IF(入力!$B21="","",IF(ISNUMBER(入力!$C21),入力!$C21,""))</f>
-        <v>1.1</v>
+        <f>IF(入力!$B12="","",IF(ISNUMBER(入力!$C12),入力!$C12,""))</f>
+        <v>1.6</v>
       </c>
       <c r="D25" s="5">
-        <f>IF(ISNUMBER(入力!$C21),MAX(0,入力!$C21-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C12),MAX(0,入力!$C12-入力!$B$5),"")</f>
         <v>0</v>
       </c>
       <c r="E25" s="4">
-        <f>IF(入力!$B21="","",IF(ISNUMBER(入力!$O21),入力!$O21,""))</f>
-        <v>877</v>
+        <f>IF(入力!$B12="","",IF(ISNUMBER(入力!$O12),入力!$O12,""))</f>
+        <v>847</v>
       </c>
       <c r="F25" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C21),ISNUMBER(入力!$O21)),入力!$C21*入力!$O21,"")</f>
-        <v>964.7</v>
+        <f>IF(AND(ISNUMBER(入力!$C12),ISNUMBER(入力!$O12)),入力!$C12*入力!$O12,"")</f>
+        <v>1355.2</v>
       </c>
       <c r="G25" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C21),ISNUMBER(入力!$O21)),MAX(0,入力!$C21-入力!$B$5)*入力!$O21,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C12),ISNUMBER(入力!$O12)),MAX(0,入力!$C12-入力!$B$5)*入力!$O12,"")</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
@@ -24268,23 +23842,23 @@
         <v>0</v>
       </c>
       <c r="I25" s="5">
-        <f>IF(入力!$B21="","",IF(ISNUMBER(入力!$D21),入力!$D21,""))</f>
-        <v>1.4</v>
+        <f>IF(入力!$B12="","",IF(ISNUMBER(入力!$D12),入力!$D12,""))</f>
+        <v>1.6</v>
       </c>
       <c r="J25" s="5">
-        <f>IF(ISNUMBER(入力!$D21),MAX(0,入力!$D21-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D12),MAX(0,入力!$D12-入力!$C$5),"")</f>
         <v>0</v>
       </c>
       <c r="K25" s="4">
-        <f>IF(入力!$B21="","",IF(ISNUMBER(入力!$P21),入力!$P21,""))</f>
-        <v>2881</v>
+        <f>IF(入力!$B12="","",IF(ISNUMBER(入力!$P12),入力!$P12,""))</f>
+        <v>939</v>
       </c>
       <c r="L25" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D21),ISNUMBER(入力!$P21)),入力!$D21*入力!$P21,"")</f>
-        <v>4033.4</v>
+        <f>IF(AND(ISNUMBER(入力!$D12),ISNUMBER(入力!$P12)),入力!$D12*入力!$P12,"")</f>
+        <v>1502.4</v>
       </c>
       <c r="M25" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D21),ISNUMBER(入力!$P21)),MAX(0,入力!$D21-入力!$C$5)*入力!$P21,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D12),ISNUMBER(入力!$P12)),MAX(0,入力!$D12-入力!$C$5)*入力!$P12,"")</f>
         <v>0</v>
       </c>
       <c r="N25" s="4">
@@ -24292,123 +23866,123 @@
         <v>0</v>
       </c>
       <c r="O25" s="5">
-        <f>IF(入力!$B21="","",IF(AND(NOT(ISNUMBER(G25)),NOT(ISNUMBER(M25))),"",IF(ISNUMBER(G25),G25,0)+IF(ISNUMBER(M25),M25,0)))</f>
+        <f>IF(入力!$B12="","",IF(AND(NOT(ISNUMBER(G25)),NOT(ISNUMBER(M25))),"",IF(ISNUMBER(G25),G25,0)+IF(ISNUMBER(M25),M25,0)))</f>
         <v>0</v>
       </c>
       <c r="P25" s="4">
-        <f>IF(入力!$B21="","",IF(AND(NOT(ISNUMBER(H25)),NOT(ISNUMBER(N25))),"",IF(ISNUMBER(H25),H25,0)+IF(ISNUMBER(N25),N25,0)))</f>
+        <f>IF(入力!$B12="","",IF(AND(NOT(ISNUMBER(H25)),NOT(ISNUMBER(N25))),"",IF(ISNUMBER(H25),H25,0)+IF(ISNUMBER(N25),N25,0)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="7" t="str">
-        <f>IF(入力!$B22="","",入力!$B22)</f>
-        <v>森田　美加</v>
+        <f>IF(入力!$B13="","",入力!$B13)</f>
+        <v>佐々木　千恵</v>
       </c>
       <c r="C26" s="5">
-        <f>IF(入力!$B22="","",IF(ISNUMBER(入力!$C22),入力!$C22,""))</f>
-        <v>1.1</v>
+        <f>IF(入力!$B13="","",IF(ISNUMBER(入力!$C13),入力!$C13,""))</f>
+        <v>1.7</v>
       </c>
       <c r="D26" s="5">
-        <f>IF(ISNUMBER(入力!$C22),MAX(0,入力!$C22-入力!$B$5),"")</f>
-        <v>0</v>
+        <f>IF(ISNUMBER(入力!$C13),MAX(0,入力!$C13-入力!$B$5),"")</f>
+        <v>0.1</v>
       </c>
       <c r="E26" s="4">
-        <f>IF(入力!$B22="","",IF(ISNUMBER(入力!$O22),入力!$O22,""))</f>
-        <v>233</v>
+        <f>IF(入力!$B13="","",IF(ISNUMBER(入力!$O13),入力!$O13,""))</f>
+        <v>681</v>
       </c>
       <c r="F26" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C22),ISNUMBER(入力!$O22)),入力!$C22*入力!$O22,"")</f>
-        <v>256.3</v>
+        <f>IF(AND(ISNUMBER(入力!$C13),ISNUMBER(入力!$O13)),入力!$C13*入力!$O13,"")</f>
+        <v>1157.7</v>
       </c>
       <c r="G26" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C22),ISNUMBER(入力!$O22)),MAX(0,入力!$C22-入力!$B$5)*入力!$O22,"")</f>
-        <v>0</v>
+        <f>IF(AND(ISNUMBER(入力!$C13),ISNUMBER(入力!$O13)),MAX(0,入力!$C13-入力!$B$5)*入力!$O13,"")</f>
+        <v>68.1</v>
       </c>
       <c r="H26" s="4">
         <f>IF(ISNUMBER(G26),ROUND(G26/入力!$B$5,0),"")</f>
+        <v>43</v>
+      </c>
+      <c r="I26" s="5">
+        <f>IF(入力!$B13="","",IF(ISNUMBER(入力!$D13),入力!$D13,""))</f>
+        <v>0.6</v>
+      </c>
+      <c r="J26" s="5">
+        <f>IF(ISNUMBER(入力!$D13),MAX(0,入力!$D13-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="I26" s="5">
-        <f>IF(入力!$B22="","",IF(ISNUMBER(入力!$D22),入力!$D22,""))</f>
-        <v>3.1</v>
-      </c>
-      <c r="J26" s="5">
-        <f>IF(ISNUMBER(入力!$D22),MAX(0,入力!$D22-入力!$C$5),"")</f>
-        <v>1.5</v>
-      </c>
       <c r="K26" s="4">
-        <f>IF(入力!$B22="","",IF(ISNUMBER(入力!$P22),入力!$P22,""))</f>
-        <v>630</v>
+        <f>IF(入力!$B13="","",IF(ISNUMBER(入力!$P13),入力!$P13,""))</f>
+        <v>1223</v>
       </c>
       <c r="L26" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D22),ISNUMBER(入力!$P22)),入力!$D22*入力!$P22,"")</f>
-        <v>1953</v>
+        <f>IF(AND(ISNUMBER(入力!$D13),ISNUMBER(入力!$P13)),入力!$D13*入力!$P13,"")</f>
+        <v>733.8</v>
       </c>
       <c r="M26" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D22),ISNUMBER(入力!$P22)),MAX(0,入力!$D22-入力!$C$5)*入力!$P22,"")</f>
-        <v>945</v>
+        <f>IF(AND(ISNUMBER(入力!$D13),ISNUMBER(入力!$P13)),MAX(0,入力!$D13-入力!$C$5)*入力!$P13,"")</f>
+        <v>0</v>
       </c>
       <c r="N26" s="4">
         <f>IF(ISNUMBER(M26),ROUND(M26/入力!$C$5,0),"")</f>
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="O26" s="5">
-        <f>IF(入力!$B22="","",IF(AND(NOT(ISNUMBER(G26)),NOT(ISNUMBER(M26))),"",IF(ISNUMBER(G26),G26,0)+IF(ISNUMBER(M26),M26,0)))</f>
-        <v>945</v>
+        <f>IF(入力!$B13="","",IF(AND(NOT(ISNUMBER(G26)),NOT(ISNUMBER(M26))),"",IF(ISNUMBER(G26),G26,0)+IF(ISNUMBER(M26),M26,0)))</f>
+        <v>68.1</v>
       </c>
       <c r="P26" s="4">
-        <f>IF(入力!$B22="","",IF(AND(NOT(ISNUMBER(H26)),NOT(ISNUMBER(N26))),"",IF(ISNUMBER(H26),H26,0)+IF(ISNUMBER(N26),N26,0)))</f>
-        <v>591</v>
+        <f>IF(入力!$B13="","",IF(AND(NOT(ISNUMBER(H26)),NOT(ISNUMBER(N26))),"",IF(ISNUMBER(H26),H26,0)+IF(ISNUMBER(N26),N26,0)))</f>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="7" t="str">
-        <f>IF(入力!$B23="","",入力!$B23)</f>
-        <v>飯田　由加里</v>
+        <f>IF(入力!$B14="","",入力!$B14)</f>
+        <v>片岡　達也</v>
       </c>
       <c r="C27" s="5">
-        <f>IF(入力!$B23="","",IF(ISNUMBER(入力!$C23),入力!$C23,""))</f>
-        <v>1.8</v>
+        <f>IF(入力!$B14="","",IF(ISNUMBER(入力!$C14),入力!$C14,""))</f>
+        <v>3.1</v>
       </c>
       <c r="D27" s="5">
-        <f>IF(ISNUMBER(入力!$C23),MAX(0,入力!$C23-入力!$B$5),"")</f>
-        <v>0.2</v>
+        <f>IF(ISNUMBER(入力!$C14),MAX(0,入力!$C14-入力!$B$5),"")</f>
+        <v>1.5</v>
       </c>
       <c r="E27" s="4">
-        <f>IF(入力!$B23="","",IF(ISNUMBER(入力!$O23),入力!$O23,""))</f>
-        <v>271</v>
+        <f>IF(入力!$B14="","",IF(ISNUMBER(入力!$O14),入力!$O14,""))</f>
+        <v>66</v>
       </c>
       <c r="F27" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C23),ISNUMBER(入力!$O23)),入力!$C23*入力!$O23,"")</f>
-        <v>487.8</v>
+        <f>IF(AND(ISNUMBER(入力!$C14),ISNUMBER(入力!$O14)),入力!$C14*入力!$O14,"")</f>
+        <v>204.6</v>
       </c>
       <c r="G27" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C23),ISNUMBER(入力!$O23)),MAX(0,入力!$C23-入力!$B$5)*入力!$O23,"")</f>
-        <v>54.2</v>
+        <f>IF(AND(ISNUMBER(入力!$C14),ISNUMBER(入力!$O14)),MAX(0,入力!$C14-入力!$B$5)*入力!$O14,"")</f>
+        <v>99</v>
       </c>
       <c r="H27" s="4">
         <f>IF(ISNUMBER(G27),ROUND(G27/入力!$B$5,0),"")</f>
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="I27" s="5">
-        <f>IF(入力!$B23="","",IF(ISNUMBER(入力!$D23),入力!$D23,""))</f>
-        <v>1.4</v>
+        <f>IF(入力!$B14="","",IF(ISNUMBER(入力!$D14),入力!$D14,""))</f>
+        <v>0.6</v>
       </c>
       <c r="J27" s="5">
-        <f>IF(ISNUMBER(入力!$D23),MAX(0,入力!$D23-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D14),MAX(0,入力!$D14-入力!$C$5),"")</f>
         <v>0</v>
       </c>
       <c r="K27" s="4">
-        <f>IF(入力!$B23="","",IF(ISNUMBER(入力!$P23),入力!$P23,""))</f>
-        <v>1061</v>
+        <f>IF(入力!$B14="","",IF(ISNUMBER(入力!$P14),入力!$P14,""))</f>
+        <v>16</v>
       </c>
       <c r="L27" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D23),ISNUMBER(入力!$P23)),入力!$D23*入力!$P23,"")</f>
-        <v>1485.4</v>
+        <f>IF(AND(ISNUMBER(入力!$D14),ISNUMBER(入力!$P14)),入力!$D14*入力!$P14,"")</f>
+        <v>9.6</v>
       </c>
       <c r="M27" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D23),ISNUMBER(入力!$P23)),MAX(0,入力!$D23-入力!$C$5)*入力!$P23,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D14),ISNUMBER(入力!$P14)),MAX(0,入力!$D14-入力!$C$5)*入力!$P14,"")</f>
         <v>0</v>
       </c>
       <c r="N27" s="4">
@@ -24416,37 +23990,37 @@
         <v>0</v>
       </c>
       <c r="O27" s="5">
-        <f>IF(入力!$B23="","",IF(AND(NOT(ISNUMBER(G27)),NOT(ISNUMBER(M27))),"",IF(ISNUMBER(G27),G27,0)+IF(ISNUMBER(M27),M27,0)))</f>
-        <v>54.2</v>
+        <f>IF(入力!$B14="","",IF(AND(NOT(ISNUMBER(G27)),NOT(ISNUMBER(M27))),"",IF(ISNUMBER(G27),G27,0)+IF(ISNUMBER(M27),M27,0)))</f>
+        <v>99</v>
       </c>
       <c r="P27" s="4">
-        <f>IF(入力!$B23="","",IF(AND(NOT(ISNUMBER(H27)),NOT(ISNUMBER(N27))),"",IF(ISNUMBER(H27),H27,0)+IF(ISNUMBER(N27),N27,0)))</f>
-        <v>34</v>
+        <f>IF(入力!$B14="","",IF(AND(NOT(ISNUMBER(H27)),NOT(ISNUMBER(N27))),"",IF(ISNUMBER(H27),H27,0)+IF(ISNUMBER(N27),N27,0)))</f>
+        <v>62</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="7" t="str">
-        <f>IF(入力!$B24="","",入力!$B24)</f>
-        <v>森本　久美</v>
+        <f>IF(入力!$B15="","",入力!$B15)</f>
+        <v>後藤　克行</v>
       </c>
       <c r="C28" s="5">
-        <f>IF(入力!$B24="","",IF(ISNUMBER(入力!$C24),入力!$C24,""))</f>
-        <v>1.4</v>
+        <f>IF(入力!$B15="","",IF(ISNUMBER(入力!$C15),入力!$C15,""))</f>
+        <v>1.5</v>
       </c>
       <c r="D28" s="5">
-        <f>IF(ISNUMBER(入力!$C24),MAX(0,入力!$C24-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C15),MAX(0,入力!$C15-入力!$B$5),"")</f>
         <v>0</v>
       </c>
       <c r="E28" s="4">
-        <f>IF(入力!$B24="","",IF(ISNUMBER(入力!$O24),入力!$O24,""))</f>
-        <v>335</v>
+        <f>IF(入力!$B15="","",IF(ISNUMBER(入力!$O15),入力!$O15,""))</f>
+        <v>2007</v>
       </c>
       <c r="F28" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C24),ISNUMBER(入力!$O24)),入力!$C24*入力!$O24,"")</f>
-        <v>469</v>
+        <f>IF(AND(ISNUMBER(入力!$C15),ISNUMBER(入力!$O15)),入力!$C15*入力!$O15,"")</f>
+        <v>3010.5</v>
       </c>
       <c r="G28" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C24),ISNUMBER(入力!$O24)),MAX(0,入力!$C24-入力!$B$5)*入力!$O24,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C15),ISNUMBER(入力!$O15)),MAX(0,入力!$C15-入力!$B$5)*入力!$O15,"")</f>
         <v>0</v>
       </c>
       <c r="H28" s="4">
@@ -24454,123 +24028,123 @@
         <v>0</v>
       </c>
       <c r="I28" s="5">
-        <f>IF(入力!$B24="","",IF(ISNUMBER(入力!$D24),入力!$D24,""))</f>
-        <v>1.6</v>
+        <f>IF(入力!$B15="","",IF(ISNUMBER(入力!$D15),入力!$D15,""))</f>
+        <v>1.9</v>
       </c>
       <c r="J28" s="5">
-        <f>IF(ISNUMBER(入力!$D24),MAX(0,入力!$D24-入力!$C$5),"")</f>
-        <v>0</v>
+        <f>IF(ISNUMBER(入力!$D15),MAX(0,入力!$D15-入力!$C$5),"")</f>
+        <v>0.3</v>
       </c>
       <c r="K28" s="4">
-        <f>IF(入力!$B24="","",IF(ISNUMBER(入力!$P24),入力!$P24,""))</f>
-        <v>970</v>
+        <f>IF(入力!$B15="","",IF(ISNUMBER(入力!$P15),入力!$P15,""))</f>
+        <v>1421</v>
       </c>
       <c r="L28" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D24),ISNUMBER(入力!$P24)),入力!$D24*入力!$P24,"")</f>
-        <v>1552</v>
+        <f>IF(AND(ISNUMBER(入力!$D15),ISNUMBER(入力!$P15)),入力!$D15*入力!$P15,"")</f>
+        <v>2699.9</v>
       </c>
       <c r="M28" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D24),ISNUMBER(入力!$P24)),MAX(0,入力!$D24-入力!$C$5)*入力!$P24,"")</f>
-        <v>0</v>
+        <f>IF(AND(ISNUMBER(入力!$D15),ISNUMBER(入力!$P15)),MAX(0,入力!$D15-入力!$C$5)*入力!$P15,"")</f>
+        <v>426.3</v>
       </c>
       <c r="N28" s="4">
         <f>IF(ISNUMBER(M28),ROUND(M28/入力!$C$5,0),"")</f>
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="O28" s="5">
-        <f>IF(入力!$B24="","",IF(AND(NOT(ISNUMBER(G28)),NOT(ISNUMBER(M28))),"",IF(ISNUMBER(G28),G28,0)+IF(ISNUMBER(M28),M28,0)))</f>
-        <v>0</v>
+        <f>IF(入力!$B15="","",IF(AND(NOT(ISNUMBER(G28)),NOT(ISNUMBER(M28))),"",IF(ISNUMBER(G28),G28,0)+IF(ISNUMBER(M28),M28,0)))</f>
+        <v>426.3</v>
       </c>
       <c r="P28" s="4">
-        <f>IF(入力!$B24="","",IF(AND(NOT(ISNUMBER(H28)),NOT(ISNUMBER(N28))),"",IF(ISNUMBER(H28),H28,0)+IF(ISNUMBER(N28),N28,0)))</f>
-        <v>0</v>
+        <f>IF(入力!$B15="","",IF(AND(NOT(ISNUMBER(H28)),NOT(ISNUMBER(N28))),"",IF(ISNUMBER(H28),H28,0)+IF(ISNUMBER(N28),N28,0)))</f>
+        <v>266</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="7" t="str">
-        <f>IF(入力!$B25="","",入力!$B25)</f>
-        <v>高橋　佐織</v>
+        <f>IF(入力!$B16="","",入力!$B16)</f>
+        <v>山本　祥吉</v>
       </c>
       <c r="C29" s="5">
-        <f>IF(入力!$B25="","",IF(ISNUMBER(入力!$C25),入力!$C25,""))</f>
-        <v>1.8</v>
+        <f>IF(入力!$B16="","",IF(ISNUMBER(入力!$C16),入力!$C16,""))</f>
+        <v>1.4</v>
       </c>
       <c r="D29" s="5">
-        <f>IF(ISNUMBER(入力!$C25),MAX(0,入力!$C25-入力!$B$5),"")</f>
-        <v>0.2</v>
+        <f>IF(ISNUMBER(入力!$C16),MAX(0,入力!$C16-入力!$B$5),"")</f>
+        <v>0</v>
       </c>
       <c r="E29" s="4">
-        <f>IF(入力!$B25="","",IF(ISNUMBER(入力!$O25),入力!$O25,""))</f>
-        <v>941</v>
+        <f>IF(入力!$B16="","",IF(ISNUMBER(入力!$O16),入力!$O16,""))</f>
+        <v>2129</v>
       </c>
       <c r="F29" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C25),ISNUMBER(入力!$O25)),入力!$C25*入力!$O25,"")</f>
-        <v>1693.8</v>
+        <f>IF(AND(ISNUMBER(入力!$C16),ISNUMBER(入力!$O16)),入力!$C16*入力!$O16,"")</f>
+        <v>2980.6</v>
       </c>
       <c r="G29" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C25),ISNUMBER(入力!$O25)),MAX(0,入力!$C25-入力!$B$5)*入力!$O25,"")</f>
-        <v>188.2</v>
+        <f>IF(AND(ISNUMBER(入力!$C16),ISNUMBER(入力!$O16)),MAX(0,入力!$C16-入力!$B$5)*入力!$O16,"")</f>
+        <v>0</v>
       </c>
       <c r="H29" s="4">
         <f>IF(ISNUMBER(G29),ROUND(G29/入力!$B$5,0),"")</f>
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="I29" s="5">
-        <f>IF(入力!$B25="","",IF(ISNUMBER(入力!$D25),入力!$D25,""))</f>
-        <v>1.7</v>
+        <f>IF(入力!$B16="","",IF(ISNUMBER(入力!$D16),入力!$D16,""))</f>
+        <v>1.8</v>
       </c>
       <c r="J29" s="5">
-        <f>IF(ISNUMBER(入力!$D25),MAX(0,入力!$D25-入力!$C$5),"")</f>
-        <v>0.1</v>
+        <f>IF(ISNUMBER(入力!$D16),MAX(0,入力!$D16-入力!$C$5),"")</f>
+        <v>0.2</v>
       </c>
       <c r="K29" s="4">
-        <f>IF(入力!$B25="","",IF(ISNUMBER(入力!$P25),入力!$P25,""))</f>
-        <v>1183</v>
+        <f>IF(入力!$B16="","",IF(ISNUMBER(入力!$P16),入力!$P16,""))</f>
+        <v>1548</v>
       </c>
       <c r="L29" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D25),ISNUMBER(入力!$P25)),入力!$D25*入力!$P25,"")</f>
-        <v>2011.1</v>
+        <f>IF(AND(ISNUMBER(入力!$D16),ISNUMBER(入力!$P16)),入力!$D16*入力!$P16,"")</f>
+        <v>2786.4</v>
       </c>
       <c r="M29" s="5">
-        <f>IF(AND(ISNUMBER(入力!$D25),ISNUMBER(入力!$P25)),MAX(0,入力!$D25-入力!$C$5)*入力!$P25,"")</f>
-        <v>118.3</v>
+        <f>IF(AND(ISNUMBER(入力!$D16),ISNUMBER(入力!$P16)),MAX(0,入力!$D16-入力!$C$5)*入力!$P16,"")</f>
+        <v>309.6</v>
       </c>
       <c r="N29" s="4">
         <f>IF(ISNUMBER(M29),ROUND(M29/入力!$C$5,0),"")</f>
-        <v>74</v>
+        <v>193</v>
       </c>
       <c r="O29" s="5">
-        <f>IF(入力!$B25="","",IF(AND(NOT(ISNUMBER(G29)),NOT(ISNUMBER(M29))),"",IF(ISNUMBER(G29),G29,0)+IF(ISNUMBER(M29),M29,0)))</f>
-        <v>306.5</v>
+        <f>IF(入力!$B16="","",IF(AND(NOT(ISNUMBER(G29)),NOT(ISNUMBER(M29))),"",IF(ISNUMBER(G29),G29,0)+IF(ISNUMBER(M29),M29,0)))</f>
+        <v>309.6</v>
       </c>
       <c r="P29" s="4">
-        <f>IF(入力!$B25="","",IF(AND(NOT(ISNUMBER(H29)),NOT(ISNUMBER(N29))),"",IF(ISNUMBER(H29),H29,0)+IF(ISNUMBER(N29),N29,0)))</f>
-        <v>192</v>
+        <f>IF(入力!$B16="","",IF(AND(NOT(ISNUMBER(H29)),NOT(ISNUMBER(N29))),"",IF(ISNUMBER(H29),H29,0)+IF(ISNUMBER(N29),N29,0)))</f>
+        <v>193</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="7" t="str">
-        <f>IF(入力!$B26="","",入力!$B26)</f>
-        <v>北田　倫子</v>
+        <f>IF(入力!$B17="","",入力!$B17)</f>
+        <v>本吉　有美子</v>
       </c>
       <c r="C30" s="5">
-        <f>IF(入力!$B26="","",IF(ISNUMBER(入力!$C26),入力!$C26,""))</f>
-        <v>1.6</v>
+        <f>IF(入力!$B17="","",IF(ISNUMBER(入力!$C17),入力!$C17,""))</f>
+        <v>1.1</v>
       </c>
       <c r="D30" s="5">
-        <f>IF(ISNUMBER(入力!$C26),MAX(0,入力!$C26-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C17),MAX(0,入力!$C17-入力!$B$5),"")</f>
         <v>0</v>
       </c>
       <c r="E30" s="4">
-        <f>IF(入力!$B26="","",IF(ISNUMBER(入力!$O26),入力!$O26,""))</f>
-        <v>468</v>
+        <f>IF(入力!$B17="","",IF(ISNUMBER(入力!$O17),入力!$O17,""))</f>
+        <v>1454</v>
       </c>
       <c r="F30" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C26),ISNUMBER(入力!$O26)),入力!$C26*入力!$O26,"")</f>
-        <v>748.8</v>
+        <f>IF(AND(ISNUMBER(入力!$C17),ISNUMBER(入力!$O17)),入力!$C17*入力!$O17,"")</f>
+        <v>1599.4</v>
       </c>
       <c r="G30" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C26),ISNUMBER(入力!$O26)),MAX(0,入力!$C26-入力!$B$5)*入力!$O26,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C17),ISNUMBER(入力!$O17)),MAX(0,入力!$C17-入力!$B$5)*入力!$O17,"")</f>
         <v>0</v>
       </c>
       <c r="H30" s="4">
@@ -24578,1177 +24152,1177 @@
         <v>0</v>
       </c>
       <c r="I30" s="5">
-        <f>IF(入力!$B26="","",IF(ISNUMBER(入力!$D26),入力!$D26,""))</f>
-        <v>1.2</v>
+        <f>IF(入力!$B17="","",IF(ISNUMBER(入力!$D17),入力!$D17,""))</f>
+        <v>1</v>
       </c>
       <c r="J30" s="5">
-        <f>IF(ISNUMBER(入力!$D26),MAX(0,入力!$D26-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D17),MAX(0,入力!$D17-入力!$C$5),"")</f>
         <v>0</v>
       </c>
-      <c r="K30" s="4" t="str">
-        <f>IF(入力!$B26="","",IF(ISNUMBER(入力!$P26),入力!$P26,""))</f>
-        <v/>
-      </c>
-      <c r="L30" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D26),ISNUMBER(入力!$P26)),入力!$D26*入力!$P26,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D26),ISNUMBER(入力!$P26)),MAX(0,入力!$D26-入力!$C$5)*入力!$P26,"")</f>
-        <v/>
-      </c>
-      <c r="N30" s="4" t="str">
+      <c r="K30" s="4">
+        <f>IF(入力!$B17="","",IF(ISNUMBER(入力!$P17),入力!$P17,""))</f>
+        <v>2493</v>
+      </c>
+      <c r="L30" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D17),ISNUMBER(入力!$P17)),入力!$D17*入力!$P17,"")</f>
+        <v>2493</v>
+      </c>
+      <c r="M30" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D17),ISNUMBER(入力!$P17)),MAX(0,入力!$D17-入力!$C$5)*入力!$P17,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="4">
         <f>IF(ISNUMBER(M30),ROUND(M30/入力!$C$5,0),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O30" s="5">
-        <f>IF(入力!$B26="","",IF(AND(NOT(ISNUMBER(G30)),NOT(ISNUMBER(M30))),"",IF(ISNUMBER(G30),G30,0)+IF(ISNUMBER(M30),M30,0)))</f>
+        <f>IF(入力!$B17="","",IF(AND(NOT(ISNUMBER(G30)),NOT(ISNUMBER(M30))),"",IF(ISNUMBER(G30),G30,0)+IF(ISNUMBER(M30),M30,0)))</f>
         <v>0</v>
       </c>
       <c r="P30" s="4">
-        <f>IF(入力!$B26="","",IF(AND(NOT(ISNUMBER(H30)),NOT(ISNUMBER(N30))),"",IF(ISNUMBER(H30),H30,0)+IF(ISNUMBER(N30),N30,0)))</f>
+        <f>IF(入力!$B17="","",IF(AND(NOT(ISNUMBER(H30)),NOT(ISNUMBER(N30))),"",IF(ISNUMBER(H30),H30,0)+IF(ISNUMBER(N30),N30,0)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="7" t="str">
-        <f>IF(入力!$B27="","",入力!$B27)</f>
-        <v>鈴木　香織</v>
-      </c>
-      <c r="C31" s="5">
-        <f>IF(入力!$B27="","",IF(ISNUMBER(入力!$C27),入力!$C27,""))</f>
-        <v>1.2</v>
-      </c>
-      <c r="D31" s="5">
-        <f>IF(ISNUMBER(入力!$C27),MAX(0,入力!$C27-入力!$B$5),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="4">
-        <f>IF(入力!$B27="","",IF(ISNUMBER(入力!$O27),入力!$O27,""))</f>
-        <v>260</v>
-      </c>
-      <c r="F31" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C27),ISNUMBER(入力!$O27)),入力!$C27*入力!$O27,"")</f>
-        <v>312</v>
-      </c>
-      <c r="G31" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C27),ISNUMBER(入力!$O27)),MAX(0,入力!$C27-入力!$B$5)*入力!$O27,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="4">
+        <f>IF(入力!$B18="","",入力!$B18)</f>
+        <v>屋宮　敬子</v>
+      </c>
+      <c r="C31" s="5" t="str">
+        <f>IF(入力!$B18="","",IF(ISNUMBER(入力!$C18),入力!$C18,""))</f>
+        <v/>
+      </c>
+      <c r="D31" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$C18),MAX(0,入力!$C18-入力!$B$5),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="4" t="str">
+        <f>IF(入力!$B18="","",IF(ISNUMBER(入力!$O18),入力!$O18,""))</f>
+        <v/>
+      </c>
+      <c r="F31" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C18),ISNUMBER(入力!$O18)),入力!$C18*入力!$O18,"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C18),ISNUMBER(入力!$O18)),MAX(0,入力!$C18-入力!$B$5)*入力!$O18,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="4" t="str">
         <f>IF(ISNUMBER(G31),ROUND(G31/入力!$B$5,0),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="5">
-        <f>IF(入力!$B27="","",IF(ISNUMBER(入力!$D27),入力!$D27,""))</f>
-        <v>1.8</v>
-      </c>
-      <c r="J31" s="5">
-        <f>IF(ISNUMBER(入力!$D27),MAX(0,入力!$D27-入力!$C$5),"")</f>
-        <v>0.2</v>
+        <v/>
+      </c>
+      <c r="I31" s="5" t="str">
+        <f>IF(入力!$B18="","",IF(ISNUMBER(入力!$D18),入力!$D18,""))</f>
+        <v/>
+      </c>
+      <c r="J31" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D18),MAX(0,入力!$D18-入力!$C$5),"")</f>
+        <v/>
       </c>
       <c r="K31" s="4" t="str">
-        <f>IF(入力!$B27="","",IF(ISNUMBER(入力!$P27),入力!$P27,""))</f>
+        <f>IF(入力!$B18="","",IF(ISNUMBER(入力!$P18),入力!$P18,""))</f>
         <v/>
       </c>
       <c r="L31" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D27),ISNUMBER(入力!$P27)),入力!$D27*入力!$P27,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D18),ISNUMBER(入力!$P18)),入力!$D18*入力!$P18,"")</f>
         <v/>
       </c>
       <c r="M31" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D27),ISNUMBER(入力!$P27)),MAX(0,入力!$D27-入力!$C$5)*入力!$P27,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D18),ISNUMBER(入力!$P18)),MAX(0,入力!$D18-入力!$C$5)*入力!$P18,"")</f>
         <v/>
       </c>
       <c r="N31" s="4" t="str">
         <f>IF(ISNUMBER(M31),ROUND(M31/入力!$C$5,0),"")</f>
         <v/>
       </c>
-      <c r="O31" s="5">
-        <f>IF(入力!$B27="","",IF(AND(NOT(ISNUMBER(G31)),NOT(ISNUMBER(M31))),"",IF(ISNUMBER(G31),G31,0)+IF(ISNUMBER(M31),M31,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="P31" s="4">
-        <f>IF(入力!$B27="","",IF(AND(NOT(ISNUMBER(H31)),NOT(ISNUMBER(N31))),"",IF(ISNUMBER(H31),H31,0)+IF(ISNUMBER(N31),N31,0)))</f>
-        <v>0</v>
+      <c r="O31" s="5" t="str">
+        <f>IF(入力!$B18="","",IF(AND(NOT(ISNUMBER(G31)),NOT(ISNUMBER(M31))),"",IF(ISNUMBER(G31),G31,0)+IF(ISNUMBER(M31),M31,0)))</f>
+        <v/>
+      </c>
+      <c r="P31" s="4" t="str">
+        <f>IF(入力!$B18="","",IF(AND(NOT(ISNUMBER(H31)),NOT(ISNUMBER(N31))),"",IF(ISNUMBER(H31),H31,0)+IF(ISNUMBER(N31),N31,0)))</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="7" t="str">
-        <f>IF(入力!$B28="","",入力!$B28)</f>
-        <v>菊池　敬</v>
+        <f>IF(入力!$B19="","",入力!$B19)</f>
+        <v>大江　美記子</v>
       </c>
       <c r="C32" s="5">
-        <f>IF(入力!$B28="","",IF(ISNUMBER(入力!$C28),入力!$C28,""))</f>
-        <v>1.7</v>
+        <f>IF(入力!$B19="","",IF(ISNUMBER(入力!$C19),入力!$C19,""))</f>
+        <v>1.2</v>
       </c>
       <c r="D32" s="5">
-        <f>IF(ISNUMBER(入力!$C28),MAX(0,入力!$C28-入力!$B$5),"")</f>
-        <v>0.1</v>
+        <f>IF(ISNUMBER(入力!$C19),MAX(0,入力!$C19-入力!$B$5),"")</f>
+        <v>0</v>
       </c>
       <c r="E32" s="4">
-        <f>IF(入力!$B28="","",IF(ISNUMBER(入力!$O28),入力!$O28,""))</f>
-        <v>422</v>
+        <f>IF(入力!$B19="","",IF(ISNUMBER(入力!$O19),入力!$O19,""))</f>
+        <v>1053</v>
       </c>
       <c r="F32" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C28),ISNUMBER(入力!$O28)),入力!$C28*入力!$O28,"")</f>
-        <v>717.4</v>
+        <f>IF(AND(ISNUMBER(入力!$C19),ISNUMBER(入力!$O19)),入力!$C19*入力!$O19,"")</f>
+        <v>1263.6</v>
       </c>
       <c r="G32" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C28),ISNUMBER(入力!$O28)),MAX(0,入力!$C28-入力!$B$5)*入力!$O28,"")</f>
-        <v>42.2</v>
+        <f>IF(AND(ISNUMBER(入力!$C19),ISNUMBER(入力!$O19)),MAX(0,入力!$C19-入力!$B$5)*入力!$O19,"")</f>
+        <v>0</v>
       </c>
       <c r="H32" s="4">
         <f>IF(ISNUMBER(G32),ROUND(G32/入力!$B$5,0),"")</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I32" s="5">
-        <f>IF(入力!$B28="","",IF(ISNUMBER(入力!$D28),入力!$D28,""))</f>
-        <v>2.5</v>
+        <f>IF(入力!$B19="","",IF(ISNUMBER(入力!$D19),入力!$D19,""))</f>
+        <v>1.2</v>
       </c>
       <c r="J32" s="5">
-        <f>IF(ISNUMBER(入力!$D28),MAX(0,入力!$D28-入力!$C$5),"")</f>
-        <v>0.9</v>
-      </c>
-      <c r="K32" s="4" t="str">
-        <f>IF(入力!$B28="","",IF(ISNUMBER(入力!$P28),入力!$P28,""))</f>
-        <v/>
-      </c>
-      <c r="L32" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D28),ISNUMBER(入力!$P28)),入力!$D28*入力!$P28,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D28),ISNUMBER(入力!$P28)),MAX(0,入力!$D28-入力!$C$5)*入力!$P28,"")</f>
-        <v/>
-      </c>
-      <c r="N32" s="4" t="str">
+        <f>IF(ISNUMBER(入力!$D19),MAX(0,入力!$D19-入力!$C$5),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="4">
+        <f>IF(入力!$B19="","",IF(ISNUMBER(入力!$P19),入力!$P19,""))</f>
+        <v>2616</v>
+      </c>
+      <c r="L32" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D19),ISNUMBER(入力!$P19)),入力!$D19*入力!$P19,"")</f>
+        <v>3139.2</v>
+      </c>
+      <c r="M32" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D19),ISNUMBER(入力!$P19)),MAX(0,入力!$D19-入力!$C$5)*入力!$P19,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="4">
         <f>IF(ISNUMBER(M32),ROUND(M32/入力!$C$5,0),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O32" s="5">
-        <f>IF(入力!$B28="","",IF(AND(NOT(ISNUMBER(G32)),NOT(ISNUMBER(M32))),"",IF(ISNUMBER(G32),G32,0)+IF(ISNUMBER(M32),M32,0)))</f>
-        <v>42.2</v>
+        <f>IF(入力!$B19="","",IF(AND(NOT(ISNUMBER(G32)),NOT(ISNUMBER(M32))),"",IF(ISNUMBER(G32),G32,0)+IF(ISNUMBER(M32),M32,0)))</f>
+        <v>0</v>
       </c>
       <c r="P32" s="4">
-        <f>IF(入力!$B28="","",IF(AND(NOT(ISNUMBER(H32)),NOT(ISNUMBER(N32))),"",IF(ISNUMBER(H32),H32,0)+IF(ISNUMBER(N32),N32,0)))</f>
-        <v>26</v>
+        <f>IF(入力!$B19="","",IF(AND(NOT(ISNUMBER(H32)),NOT(ISNUMBER(N32))),"",IF(ISNUMBER(H32),H32,0)+IF(ISNUMBER(N32),N32,0)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="7" t="str">
-        <f>IF(入力!$B29="","",入力!$B29)</f>
-        <v>上村　和恵</v>
+        <f>IF(入力!$B20="","",入力!$B20)</f>
+        <v>木村　千鶴</v>
       </c>
       <c r="C33" s="5">
-        <f>IF(入力!$B29="","",IF(ISNUMBER(入力!$C29),入力!$C29,""))</f>
-        <v>1.8</v>
+        <f>IF(入力!$B20="","",IF(ISNUMBER(入力!$C20),入力!$C20,""))</f>
+        <v>1.7</v>
       </c>
       <c r="D33" s="5">
-        <f>IF(ISNUMBER(入力!$C29),MAX(0,入力!$C29-入力!$B$5),"")</f>
-        <v>0.2</v>
+        <f>IF(ISNUMBER(入力!$C20),MAX(0,入力!$C20-入力!$B$5),"")</f>
+        <v>0.1</v>
       </c>
       <c r="E33" s="4">
-        <f>IF(入力!$B29="","",IF(ISNUMBER(入力!$O29),入力!$O29,""))</f>
-        <v>1112</v>
+        <f>IF(入力!$B20="","",IF(ISNUMBER(入力!$O20),入力!$O20,""))</f>
+        <v>691</v>
       </c>
       <c r="F33" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C29),ISNUMBER(入力!$O29)),入力!$C29*入力!$O29,"")</f>
-        <v>2001.6</v>
+        <f>IF(AND(ISNUMBER(入力!$C20),ISNUMBER(入力!$O20)),入力!$C20*入力!$O20,"")</f>
+        <v>1174.7</v>
       </c>
       <c r="G33" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C29),ISNUMBER(入力!$O29)),MAX(0,入力!$C29-入力!$B$5)*入力!$O29,"")</f>
-        <v>222.4</v>
+        <f>IF(AND(ISNUMBER(入力!$C20),ISNUMBER(入力!$O20)),MAX(0,入力!$C20-入力!$B$5)*入力!$O20,"")</f>
+        <v>69.1</v>
       </c>
       <c r="H33" s="4">
         <f>IF(ISNUMBER(G33),ROUND(G33/入力!$B$5,0),"")</f>
-        <v>139</v>
-      </c>
-      <c r="I33" s="5" t="str">
-        <f>IF(入力!$B29="","",IF(ISNUMBER(入力!$D29),入力!$D29,""))</f>
-        <v/>
-      </c>
-      <c r="J33" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D29),MAX(0,入力!$D29-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="4" t="str">
-        <f>IF(入力!$B29="","",IF(ISNUMBER(入力!$P29),入力!$P29,""))</f>
-        <v/>
-      </c>
-      <c r="L33" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D29),ISNUMBER(入力!$P29)),入力!$D29*入力!$P29,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D29),ISNUMBER(入力!$P29)),MAX(0,入力!$D29-入力!$C$5)*入力!$P29,"")</f>
-        <v/>
-      </c>
-      <c r="N33" s="4" t="str">
+        <v>43</v>
+      </c>
+      <c r="I33" s="5">
+        <f>IF(入力!$B20="","",IF(ISNUMBER(入力!$D20),入力!$D20,""))</f>
+        <v>2.2</v>
+      </c>
+      <c r="J33" s="5">
+        <f>IF(ISNUMBER(入力!$D20),MAX(0,入力!$D20-入力!$C$5),"")</f>
+        <v>0.6</v>
+      </c>
+      <c r="K33" s="4">
+        <f>IF(入力!$B20="","",IF(ISNUMBER(入力!$P20),入力!$P20,""))</f>
+        <v>1750</v>
+      </c>
+      <c r="L33" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D20),ISNUMBER(入力!$P20)),入力!$D20*入力!$P20,"")</f>
+        <v>3850</v>
+      </c>
+      <c r="M33" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D20),ISNUMBER(入力!$P20)),MAX(0,入力!$D20-入力!$C$5)*入力!$P20,"")</f>
+        <v>1050</v>
+      </c>
+      <c r="N33" s="4">
         <f>IF(ISNUMBER(M33),ROUND(M33/入力!$C$5,0),"")</f>
-        <v/>
+        <v>656</v>
       </c>
       <c r="O33" s="5">
-        <f>IF(入力!$B29="","",IF(AND(NOT(ISNUMBER(G33)),NOT(ISNUMBER(M33))),"",IF(ISNUMBER(G33),G33,0)+IF(ISNUMBER(M33),M33,0)))</f>
-        <v>222.4</v>
+        <f>IF(入力!$B20="","",IF(AND(NOT(ISNUMBER(G33)),NOT(ISNUMBER(M33))),"",IF(ISNUMBER(G33),G33,0)+IF(ISNUMBER(M33),M33,0)))</f>
+        <v>1119.1</v>
       </c>
       <c r="P33" s="4">
-        <f>IF(入力!$B29="","",IF(AND(NOT(ISNUMBER(H33)),NOT(ISNUMBER(N33))),"",IF(ISNUMBER(H33),H33,0)+IF(ISNUMBER(N33),N33,0)))</f>
-        <v>139</v>
+        <f>IF(入力!$B20="","",IF(AND(NOT(ISNUMBER(H33)),NOT(ISNUMBER(N33))),"",IF(ISNUMBER(H33),H33,0)+IF(ISNUMBER(N33),N33,0)))</f>
+        <v>699</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="7" t="str">
-        <f>IF(入力!$B30="","",入力!$B30)</f>
-        <v>秋草　文恵</v>
+        <f>IF(入力!$B21="","",入力!$B21)</f>
+        <v>晩田　恵美</v>
       </c>
       <c r="C34" s="5">
-        <f>IF(入力!$B30="","",IF(ISNUMBER(入力!$C30),入力!$C30,""))</f>
-        <v>1.8</v>
+        <f>IF(入力!$B21="","",IF(ISNUMBER(入力!$C21),入力!$C21,""))</f>
+        <v>1.1</v>
       </c>
       <c r="D34" s="5">
-        <f>IF(ISNUMBER(入力!$C30),MAX(0,入力!$C30-入力!$B$5),"")</f>
-        <v>0.2</v>
+        <f>IF(ISNUMBER(入力!$C21),MAX(0,入力!$C21-入力!$B$5),"")</f>
+        <v>0</v>
       </c>
       <c r="E34" s="4">
-        <f>IF(入力!$B30="","",IF(ISNUMBER(入力!$O30),入力!$O30,""))</f>
-        <v>858</v>
+        <f>IF(入力!$B21="","",IF(ISNUMBER(入力!$O21),入力!$O21,""))</f>
+        <v>877</v>
       </c>
       <c r="F34" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C30),ISNUMBER(入力!$O30)),入力!$C30*入力!$O30,"")</f>
-        <v>1544.4</v>
+        <f>IF(AND(ISNUMBER(入力!$C21),ISNUMBER(入力!$O21)),入力!$C21*入力!$O21,"")</f>
+        <v>964.7</v>
       </c>
       <c r="G34" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C30),ISNUMBER(入力!$O30)),MAX(0,入力!$C30-入力!$B$5)*入力!$O30,"")</f>
-        <v>171.6</v>
+        <f>IF(AND(ISNUMBER(入力!$C21),ISNUMBER(入力!$O21)),MAX(0,入力!$C21-入力!$B$5)*入力!$O21,"")</f>
+        <v>0</v>
       </c>
       <c r="H34" s="4">
         <f>IF(ISNUMBER(G34),ROUND(G34/入力!$B$5,0),"")</f>
-        <v>107</v>
-      </c>
-      <c r="I34" s="5" t="str">
-        <f>IF(入力!$B30="","",IF(ISNUMBER(入力!$D30),入力!$D30,""))</f>
-        <v/>
-      </c>
-      <c r="J34" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D30),MAX(0,入力!$D30-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="4" t="str">
-        <f>IF(入力!$B30="","",IF(ISNUMBER(入力!$P30),入力!$P30,""))</f>
-        <v/>
-      </c>
-      <c r="L34" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D30),ISNUMBER(入力!$P30)),入力!$D30*入力!$P30,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D30),ISNUMBER(入力!$P30)),MAX(0,入力!$D30-入力!$C$5)*入力!$P30,"")</f>
-        <v/>
-      </c>
-      <c r="N34" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5">
+        <f>IF(入力!$B21="","",IF(ISNUMBER(入力!$D21),入力!$D21,""))</f>
+        <v>1.4</v>
+      </c>
+      <c r="J34" s="5">
+        <f>IF(ISNUMBER(入力!$D21),MAX(0,入力!$D21-入力!$C$5),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="4">
+        <f>IF(入力!$B21="","",IF(ISNUMBER(入力!$P21),入力!$P21,""))</f>
+        <v>2881</v>
+      </c>
+      <c r="L34" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D21),ISNUMBER(入力!$P21)),入力!$D21*入力!$P21,"")</f>
+        <v>4033.4</v>
+      </c>
+      <c r="M34" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D21),ISNUMBER(入力!$P21)),MAX(0,入力!$D21-入力!$C$5)*入力!$P21,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="4">
         <f>IF(ISNUMBER(M34),ROUND(M34/入力!$C$5,0),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O34" s="5">
-        <f>IF(入力!$B30="","",IF(AND(NOT(ISNUMBER(G34)),NOT(ISNUMBER(M34))),"",IF(ISNUMBER(G34),G34,0)+IF(ISNUMBER(M34),M34,0)))</f>
-        <v>171.6</v>
+        <f>IF(入力!$B21="","",IF(AND(NOT(ISNUMBER(G34)),NOT(ISNUMBER(M34))),"",IF(ISNUMBER(G34),G34,0)+IF(ISNUMBER(M34),M34,0)))</f>
+        <v>0</v>
       </c>
       <c r="P34" s="4">
-        <f>IF(入力!$B30="","",IF(AND(NOT(ISNUMBER(H34)),NOT(ISNUMBER(N34))),"",IF(ISNUMBER(H34),H34,0)+IF(ISNUMBER(N34),N34,0)))</f>
-        <v>107</v>
+        <f>IF(入力!$B21="","",IF(AND(NOT(ISNUMBER(H34)),NOT(ISNUMBER(N34))),"",IF(ISNUMBER(H34),H34,0)+IF(ISNUMBER(N34),N34,0)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="7" t="str">
-        <f>IF(入力!$B31="","",入力!$B31)</f>
-        <v>向井　ひかり</v>
+        <f>IF(入力!$B22="","",入力!$B22)</f>
+        <v>森田　美加</v>
       </c>
       <c r="C35" s="5">
-        <f>IF(入力!$B31="","",IF(ISNUMBER(入力!$C31),入力!$C31,""))</f>
-        <v>1.5</v>
+        <f>IF(入力!$B22="","",IF(ISNUMBER(入力!$C22),入力!$C22,""))</f>
+        <v>1.1</v>
       </c>
       <c r="D35" s="5">
-        <f>IF(ISNUMBER(入力!$C31),MAX(0,入力!$C31-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C22),MAX(0,入力!$C22-入力!$B$5),"")</f>
         <v>0</v>
       </c>
       <c r="E35" s="4">
-        <f>IF(入力!$B31="","",IF(ISNUMBER(入力!$O31),入力!$O31,""))</f>
-        <v>866</v>
+        <f>IF(入力!$B22="","",IF(ISNUMBER(入力!$O22),入力!$O22,""))</f>
+        <v>233</v>
       </c>
       <c r="F35" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C31),ISNUMBER(入力!$O31)),入力!$C31*入力!$O31,"")</f>
-        <v>1299</v>
+        <f>IF(AND(ISNUMBER(入力!$C22),ISNUMBER(入力!$O22)),入力!$C22*入力!$O22,"")</f>
+        <v>256.3</v>
       </c>
       <c r="G35" s="5">
-        <f>IF(AND(ISNUMBER(入力!$C31),ISNUMBER(入力!$O31)),MAX(0,入力!$C31-入力!$B$5)*入力!$O31,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C22),ISNUMBER(入力!$O22)),MAX(0,入力!$C22-入力!$B$5)*入力!$O22,"")</f>
         <v>0</v>
       </c>
       <c r="H35" s="4">
         <f>IF(ISNUMBER(G35),ROUND(G35/入力!$B$5,0),"")</f>
         <v>0</v>
       </c>
-      <c r="I35" s="5" t="str">
-        <f>IF(入力!$B31="","",IF(ISNUMBER(入力!$D31),入力!$D31,""))</f>
-        <v/>
-      </c>
-      <c r="J35" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D31),MAX(0,入力!$D31-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="4" t="str">
-        <f>IF(入力!$B31="","",IF(ISNUMBER(入力!$P31),入力!$P31,""))</f>
-        <v/>
-      </c>
-      <c r="L35" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D31),ISNUMBER(入力!$P31)),入力!$D31*入力!$P31,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D31),ISNUMBER(入力!$P31)),MAX(0,入力!$D31-入力!$C$5)*入力!$P31,"")</f>
-        <v/>
-      </c>
-      <c r="N35" s="4" t="str">
+      <c r="I35" s="5">
+        <f>IF(入力!$B22="","",IF(ISNUMBER(入力!$D22),入力!$D22,""))</f>
+        <v>3.1</v>
+      </c>
+      <c r="J35" s="5">
+        <f>IF(ISNUMBER(入力!$D22),MAX(0,入力!$D22-入力!$C$5),"")</f>
+        <v>1.5</v>
+      </c>
+      <c r="K35" s="4">
+        <f>IF(入力!$B22="","",IF(ISNUMBER(入力!$P22),入力!$P22,""))</f>
+        <v>630</v>
+      </c>
+      <c r="L35" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D22),ISNUMBER(入力!$P22)),入力!$D22*入力!$P22,"")</f>
+        <v>1953</v>
+      </c>
+      <c r="M35" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D22),ISNUMBER(入力!$P22)),MAX(0,入力!$D22-入力!$C$5)*入力!$P22,"")</f>
+        <v>945</v>
+      </c>
+      <c r="N35" s="4">
         <f>IF(ISNUMBER(M35),ROUND(M35/入力!$C$5,0),"")</f>
-        <v/>
+        <v>591</v>
       </c>
       <c r="O35" s="5">
-        <f>IF(入力!$B31="","",IF(AND(NOT(ISNUMBER(G35)),NOT(ISNUMBER(M35))),"",IF(ISNUMBER(G35),G35,0)+IF(ISNUMBER(M35),M35,0)))</f>
-        <v>0</v>
+        <f>IF(入力!$B22="","",IF(AND(NOT(ISNUMBER(G35)),NOT(ISNUMBER(M35))),"",IF(ISNUMBER(G35),G35,0)+IF(ISNUMBER(M35),M35,0)))</f>
+        <v>945</v>
       </c>
       <c r="P35" s="4">
-        <f>IF(入力!$B31="","",IF(AND(NOT(ISNUMBER(H35)),NOT(ISNUMBER(N35))),"",IF(ISNUMBER(H35),H35,0)+IF(ISNUMBER(N35),N35,0)))</f>
-        <v>0</v>
+        <f>IF(入力!$B22="","",IF(AND(NOT(ISNUMBER(H35)),NOT(ISNUMBER(N35))),"",IF(ISNUMBER(H35),H35,0)+IF(ISNUMBER(N35),N35,0)))</f>
+        <v>591</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="7" t="str">
+        <f>IF(入力!$B23="","",入力!$B23)</f>
+        <v>飯田　由加里</v>
+      </c>
+      <c r="C36" s="5">
+        <f>IF(入力!$B23="","",IF(ISNUMBER(入力!$C23),入力!$C23,""))</f>
+        <v>1.8</v>
+      </c>
+      <c r="D36" s="5">
+        <f>IF(ISNUMBER(入力!$C23),MAX(0,入力!$C23-入力!$B$5),"")</f>
+        <v>0.2</v>
+      </c>
+      <c r="E36" s="4">
+        <f>IF(入力!$B23="","",IF(ISNUMBER(入力!$O23),入力!$O23,""))</f>
+        <v>271</v>
+      </c>
+      <c r="F36" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C23),ISNUMBER(入力!$O23)),入力!$C23*入力!$O23,"")</f>
+        <v>487.8</v>
+      </c>
+      <c r="G36" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C23),ISNUMBER(入力!$O23)),MAX(0,入力!$C23-入力!$B$5)*入力!$O23,"")</f>
+        <v>54.2</v>
+      </c>
+      <c r="H36" s="4">
+        <f>IF(ISNUMBER(G36),ROUND(G36/入力!$B$5,0),"")</f>
+        <v>34</v>
+      </c>
+      <c r="I36" s="5">
+        <f>IF(入力!$B23="","",IF(ISNUMBER(入力!$D23),入力!$D23,""))</f>
+        <v>1.4</v>
+      </c>
+      <c r="J36" s="5">
+        <f>IF(ISNUMBER(入力!$D23),MAX(0,入力!$D23-入力!$C$5),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="4">
+        <f>IF(入力!$B23="","",IF(ISNUMBER(入力!$P23),入力!$P23,""))</f>
+        <v>1061</v>
+      </c>
+      <c r="L36" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D23),ISNUMBER(入力!$P23)),入力!$D23*入力!$P23,"")</f>
+        <v>1485.4</v>
+      </c>
+      <c r="M36" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D23),ISNUMBER(入力!$P23)),MAX(0,入力!$D23-入力!$C$5)*入力!$P23,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="4">
+        <f>IF(ISNUMBER(M36),ROUND(M36/入力!$C$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O36" s="5">
+        <f>IF(入力!$B23="","",IF(AND(NOT(ISNUMBER(G36)),NOT(ISNUMBER(M36))),"",IF(ISNUMBER(G36),G36,0)+IF(ISNUMBER(M36),M36,0)))</f>
+        <v>54.2</v>
+      </c>
+      <c r="P36" s="4">
+        <f>IF(入力!$B23="","",IF(AND(NOT(ISNUMBER(H36)),NOT(ISNUMBER(N36))),"",IF(ISNUMBER(H36),H36,0)+IF(ISNUMBER(N36),N36,0)))</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="7" t="str">
+        <f>IF(入力!$B24="","",入力!$B24)</f>
+        <v>森本　久美</v>
+      </c>
+      <c r="C37" s="5">
+        <f>IF(入力!$B24="","",IF(ISNUMBER(入力!$C24),入力!$C24,""))</f>
+        <v>1.4</v>
+      </c>
+      <c r="D37" s="5">
+        <f>IF(ISNUMBER(入力!$C24),MAX(0,入力!$C24-入力!$B$5),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="4">
+        <f>IF(入力!$B24="","",IF(ISNUMBER(入力!$O24),入力!$O24,""))</f>
+        <v>335</v>
+      </c>
+      <c r="F37" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C24),ISNUMBER(入力!$O24)),入力!$C24*入力!$O24,"")</f>
+        <v>469</v>
+      </c>
+      <c r="G37" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C24),ISNUMBER(入力!$O24)),MAX(0,入力!$C24-入力!$B$5)*入力!$O24,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="4">
+        <f>IF(ISNUMBER(G37),ROUND(G37/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="5">
+        <f>IF(入力!$B24="","",IF(ISNUMBER(入力!$D24),入力!$D24,""))</f>
+        <v>1.6</v>
+      </c>
+      <c r="J37" s="5">
+        <f>IF(ISNUMBER(入力!$D24),MAX(0,入力!$D24-入力!$C$5),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="4">
+        <f>IF(入力!$B24="","",IF(ISNUMBER(入力!$P24),入力!$P24,""))</f>
+        <v>970</v>
+      </c>
+      <c r="L37" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D24),ISNUMBER(入力!$P24)),入力!$D24*入力!$P24,"")</f>
+        <v>1552</v>
+      </c>
+      <c r="M37" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D24),ISNUMBER(入力!$P24)),MAX(0,入力!$D24-入力!$C$5)*入力!$P24,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N37" s="4">
+        <f>IF(ISNUMBER(M37),ROUND(M37/入力!$C$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O37" s="5">
+        <f>IF(入力!$B24="","",IF(AND(NOT(ISNUMBER(G37)),NOT(ISNUMBER(M37))),"",IF(ISNUMBER(G37),G37,0)+IF(ISNUMBER(M37),M37,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P37" s="4">
+        <f>IF(入力!$B24="","",IF(AND(NOT(ISNUMBER(H37)),NOT(ISNUMBER(N37))),"",IF(ISNUMBER(H37),H37,0)+IF(ISNUMBER(N37),N37,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="7" t="str">
+        <f>IF(入力!$B25="","",入力!$B25)</f>
+        <v>高橋　佐織</v>
+      </c>
+      <c r="C38" s="5">
+        <f>IF(入力!$B25="","",IF(ISNUMBER(入力!$C25),入力!$C25,""))</f>
+        <v>1.8</v>
+      </c>
+      <c r="D38" s="5">
+        <f>IF(ISNUMBER(入力!$C25),MAX(0,入力!$C25-入力!$B$5),"")</f>
+        <v>0.2</v>
+      </c>
+      <c r="E38" s="4">
+        <f>IF(入力!$B25="","",IF(ISNUMBER(入力!$O25),入力!$O25,""))</f>
+        <v>941</v>
+      </c>
+      <c r="F38" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C25),ISNUMBER(入力!$O25)),入力!$C25*入力!$O25,"")</f>
+        <v>1693.8</v>
+      </c>
+      <c r="G38" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C25),ISNUMBER(入力!$O25)),MAX(0,入力!$C25-入力!$B$5)*入力!$O25,"")</f>
+        <v>188.2</v>
+      </c>
+      <c r="H38" s="4">
+        <f>IF(ISNUMBER(G38),ROUND(G38/入力!$B$5,0),"")</f>
+        <v>118</v>
+      </c>
+      <c r="I38" s="5">
+        <f>IF(入力!$B25="","",IF(ISNUMBER(入力!$D25),入力!$D25,""))</f>
+        <v>1.7</v>
+      </c>
+      <c r="J38" s="5">
+        <f>IF(ISNUMBER(入力!$D25),MAX(0,入力!$D25-入力!$C$5),"")</f>
+        <v>0.1</v>
+      </c>
+      <c r="K38" s="4">
+        <f>IF(入力!$B25="","",IF(ISNUMBER(入力!$P25),入力!$P25,""))</f>
+        <v>1183</v>
+      </c>
+      <c r="L38" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D25),ISNUMBER(入力!$P25)),入力!$D25*入力!$P25,"")</f>
+        <v>2011.1</v>
+      </c>
+      <c r="M38" s="5">
+        <f>IF(AND(ISNUMBER(入力!$D25),ISNUMBER(入力!$P25)),MAX(0,入力!$D25-入力!$C$5)*入力!$P25,"")</f>
+        <v>118.3</v>
+      </c>
+      <c r="N38" s="4">
+        <f>IF(ISNUMBER(M38),ROUND(M38/入力!$C$5,0),"")</f>
+        <v>74</v>
+      </c>
+      <c r="O38" s="5">
+        <f>IF(入力!$B25="","",IF(AND(NOT(ISNUMBER(G38)),NOT(ISNUMBER(M38))),"",IF(ISNUMBER(G38),G38,0)+IF(ISNUMBER(M38),M38,0)))</f>
+        <v>306.5</v>
+      </c>
+      <c r="P38" s="4">
+        <f>IF(入力!$B25="","",IF(AND(NOT(ISNUMBER(H38)),NOT(ISNUMBER(N38))),"",IF(ISNUMBER(H38),H38,0)+IF(ISNUMBER(N38),N38,0)))</f>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="7" t="str">
+        <f>IF(入力!$B26="","",入力!$B26)</f>
+        <v>北田　倫子</v>
+      </c>
+      <c r="C39" s="5">
+        <f>IF(入力!$B26="","",IF(ISNUMBER(入力!$C26),入力!$C26,""))</f>
+        <v>1.6</v>
+      </c>
+      <c r="D39" s="5">
+        <f>IF(ISNUMBER(入力!$C26),MAX(0,入力!$C26-入力!$B$5),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="4">
+        <f>IF(入力!$B26="","",IF(ISNUMBER(入力!$O26),入力!$O26,""))</f>
+        <v>468</v>
+      </c>
+      <c r="F39" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C26),ISNUMBER(入力!$O26)),入力!$C26*入力!$O26,"")</f>
+        <v>748.8</v>
+      </c>
+      <c r="G39" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C26),ISNUMBER(入力!$O26)),MAX(0,入力!$C26-入力!$B$5)*入力!$O26,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="4">
+        <f>IF(ISNUMBER(G39),ROUND(G39/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="5">
+        <f>IF(入力!$B26="","",IF(ISNUMBER(入力!$D26),入力!$D26,""))</f>
+        <v>1.2</v>
+      </c>
+      <c r="J39" s="5">
+        <f>IF(ISNUMBER(入力!$D26),MAX(0,入力!$D26-入力!$C$5),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="4" t="str">
+        <f>IF(入力!$B26="","",IF(ISNUMBER(入力!$P26),入力!$P26,""))</f>
+        <v/>
+      </c>
+      <c r="L39" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D26),ISNUMBER(入力!$P26)),入力!$D26*入力!$P26,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D26),ISNUMBER(入力!$P26)),MAX(0,入力!$D26-入力!$C$5)*入力!$P26,"")</f>
+        <v/>
+      </c>
+      <c r="N39" s="4" t="str">
+        <f>IF(ISNUMBER(M39),ROUND(M39/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O39" s="5">
+        <f>IF(入力!$B26="","",IF(AND(NOT(ISNUMBER(G39)),NOT(ISNUMBER(M39))),"",IF(ISNUMBER(G39),G39,0)+IF(ISNUMBER(M39),M39,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P39" s="4">
+        <f>IF(入力!$B26="","",IF(AND(NOT(ISNUMBER(H39)),NOT(ISNUMBER(N39))),"",IF(ISNUMBER(H39),H39,0)+IF(ISNUMBER(N39),N39,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="7" t="str">
+        <f>IF(入力!$B27="","",入力!$B27)</f>
+        <v>鈴木　香織</v>
+      </c>
+      <c r="C40" s="5">
+        <f>IF(入力!$B27="","",IF(ISNUMBER(入力!$C27),入力!$C27,""))</f>
+        <v>1.2</v>
+      </c>
+      <c r="D40" s="5">
+        <f>IF(ISNUMBER(入力!$C27),MAX(0,入力!$C27-入力!$B$5),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="4">
+        <f>IF(入力!$B27="","",IF(ISNUMBER(入力!$O27),入力!$O27,""))</f>
+        <v>260</v>
+      </c>
+      <c r="F40" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C27),ISNUMBER(入力!$O27)),入力!$C27*入力!$O27,"")</f>
+        <v>312</v>
+      </c>
+      <c r="G40" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C27),ISNUMBER(入力!$O27)),MAX(0,入力!$C27-入力!$B$5)*入力!$O27,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="4">
+        <f>IF(ISNUMBER(G40),ROUND(G40/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="5">
+        <f>IF(入力!$B27="","",IF(ISNUMBER(入力!$D27),入力!$D27,""))</f>
+        <v>1.8</v>
+      </c>
+      <c r="J40" s="5">
+        <f>IF(ISNUMBER(入力!$D27),MAX(0,入力!$D27-入力!$C$5),"")</f>
+        <v>0.2</v>
+      </c>
+      <c r="K40" s="4" t="str">
+        <f>IF(入力!$B27="","",IF(ISNUMBER(入力!$P27),入力!$P27,""))</f>
+        <v/>
+      </c>
+      <c r="L40" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D27),ISNUMBER(入力!$P27)),入力!$D27*入力!$P27,"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D27),ISNUMBER(入力!$P27)),MAX(0,入力!$D27-入力!$C$5)*入力!$P27,"")</f>
+        <v/>
+      </c>
+      <c r="N40" s="4" t="str">
+        <f>IF(ISNUMBER(M40),ROUND(M40/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O40" s="5">
+        <f>IF(入力!$B27="","",IF(AND(NOT(ISNUMBER(G40)),NOT(ISNUMBER(M40))),"",IF(ISNUMBER(G40),G40,0)+IF(ISNUMBER(M40),M40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P40" s="4">
+        <f>IF(入力!$B27="","",IF(AND(NOT(ISNUMBER(H40)),NOT(ISNUMBER(N40))),"",IF(ISNUMBER(H40),H40,0)+IF(ISNUMBER(N40),N40,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="7" t="str">
+        <f>IF(入力!$B28="","",入力!$B28)</f>
+        <v>菊池　敬</v>
+      </c>
+      <c r="C41" s="5">
+        <f>IF(入力!$B28="","",IF(ISNUMBER(入力!$C28),入力!$C28,""))</f>
+        <v>1.7</v>
+      </c>
+      <c r="D41" s="5">
+        <f>IF(ISNUMBER(入力!$C28),MAX(0,入力!$C28-入力!$B$5),"")</f>
+        <v>0.1</v>
+      </c>
+      <c r="E41" s="4">
+        <f>IF(入力!$B28="","",IF(ISNUMBER(入力!$O28),入力!$O28,""))</f>
+        <v>422</v>
+      </c>
+      <c r="F41" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C28),ISNUMBER(入力!$O28)),入力!$C28*入力!$O28,"")</f>
+        <v>717.4</v>
+      </c>
+      <c r="G41" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C28),ISNUMBER(入力!$O28)),MAX(0,入力!$C28-入力!$B$5)*入力!$O28,"")</f>
+        <v>42.2</v>
+      </c>
+      <c r="H41" s="4">
+        <f>IF(ISNUMBER(G41),ROUND(G41/入力!$B$5,0),"")</f>
+        <v>26</v>
+      </c>
+      <c r="I41" s="5">
+        <f>IF(入力!$B28="","",IF(ISNUMBER(入力!$D28),入力!$D28,""))</f>
+        <v>2.5</v>
+      </c>
+      <c r="J41" s="5">
+        <f>IF(ISNUMBER(入力!$D28),MAX(0,入力!$D28-入力!$C$5),"")</f>
+        <v>0.9</v>
+      </c>
+      <c r="K41" s="4" t="str">
+        <f>IF(入力!$B28="","",IF(ISNUMBER(入力!$P28),入力!$P28,""))</f>
+        <v/>
+      </c>
+      <c r="L41" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D28),ISNUMBER(入力!$P28)),入力!$D28*入力!$P28,"")</f>
+        <v/>
+      </c>
+      <c r="M41" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D28),ISNUMBER(入力!$P28)),MAX(0,入力!$D28-入力!$C$5)*入力!$P28,"")</f>
+        <v/>
+      </c>
+      <c r="N41" s="4" t="str">
+        <f>IF(ISNUMBER(M41),ROUND(M41/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O41" s="5">
+        <f>IF(入力!$B28="","",IF(AND(NOT(ISNUMBER(G41)),NOT(ISNUMBER(M41))),"",IF(ISNUMBER(G41),G41,0)+IF(ISNUMBER(M41),M41,0)))</f>
+        <v>42.2</v>
+      </c>
+      <c r="P41" s="4">
+        <f>IF(入力!$B28="","",IF(AND(NOT(ISNUMBER(H41)),NOT(ISNUMBER(N41))),"",IF(ISNUMBER(H41),H41,0)+IF(ISNUMBER(N41),N41,0)))</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="7" t="str">
+        <f>IF(入力!$B29="","",入力!$B29)</f>
+        <v>上村　和恵</v>
+      </c>
+      <c r="C42" s="5">
+        <f>IF(入力!$B29="","",IF(ISNUMBER(入力!$C29),入力!$C29,""))</f>
+        <v>1.8</v>
+      </c>
+      <c r="D42" s="5">
+        <f>IF(ISNUMBER(入力!$C29),MAX(0,入力!$C29-入力!$B$5),"")</f>
+        <v>0.2</v>
+      </c>
+      <c r="E42" s="4">
+        <f>IF(入力!$B29="","",IF(ISNUMBER(入力!$O29),入力!$O29,""))</f>
+        <v>1112</v>
+      </c>
+      <c r="F42" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C29),ISNUMBER(入力!$O29)),入力!$C29*入力!$O29,"")</f>
+        <v>2001.6</v>
+      </c>
+      <c r="G42" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C29),ISNUMBER(入力!$O29)),MAX(0,入力!$C29-入力!$B$5)*入力!$O29,"")</f>
+        <v>222.4</v>
+      </c>
+      <c r="H42" s="4">
+        <f>IF(ISNUMBER(G42),ROUND(G42/入力!$B$5,0),"")</f>
+        <v>139</v>
+      </c>
+      <c r="I42" s="5" t="str">
+        <f>IF(入力!$B29="","",IF(ISNUMBER(入力!$D29),入力!$D29,""))</f>
+        <v/>
+      </c>
+      <c r="J42" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D29),MAX(0,入力!$D29-入力!$C$5),"")</f>
+        <v/>
+      </c>
+      <c r="K42" s="4" t="str">
+        <f>IF(入力!$B29="","",IF(ISNUMBER(入力!$P29),入力!$P29,""))</f>
+        <v/>
+      </c>
+      <c r="L42" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D29),ISNUMBER(入力!$P29)),入力!$D29*入力!$P29,"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D29),ISNUMBER(入力!$P29)),MAX(0,入力!$D29-入力!$C$5)*入力!$P29,"")</f>
+        <v/>
+      </c>
+      <c r="N42" s="4" t="str">
+        <f>IF(ISNUMBER(M42),ROUND(M42/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O42" s="5">
+        <f>IF(入力!$B29="","",IF(AND(NOT(ISNUMBER(G42)),NOT(ISNUMBER(M42))),"",IF(ISNUMBER(G42),G42,0)+IF(ISNUMBER(M42),M42,0)))</f>
+        <v>222.4</v>
+      </c>
+      <c r="P42" s="4">
+        <f>IF(入力!$B29="","",IF(AND(NOT(ISNUMBER(H42)),NOT(ISNUMBER(N42))),"",IF(ISNUMBER(H42),H42,0)+IF(ISNUMBER(N42),N42,0)))</f>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="7" t="str">
+        <f>IF(入力!$B30="","",入力!$B30)</f>
+        <v>秋草　文恵</v>
+      </c>
+      <c r="C43" s="5">
+        <f>IF(入力!$B30="","",IF(ISNUMBER(入力!$C30),入力!$C30,""))</f>
+        <v>1.8</v>
+      </c>
+      <c r="D43" s="5">
+        <f>IF(ISNUMBER(入力!$C30),MAX(0,入力!$C30-入力!$B$5),"")</f>
+        <v>0.2</v>
+      </c>
+      <c r="E43" s="4">
+        <f>IF(入力!$B30="","",IF(ISNUMBER(入力!$O30),入力!$O30,""))</f>
+        <v>858</v>
+      </c>
+      <c r="F43" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C30),ISNUMBER(入力!$O30)),入力!$C30*入力!$O30,"")</f>
+        <v>1544.4</v>
+      </c>
+      <c r="G43" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C30),ISNUMBER(入力!$O30)),MAX(0,入力!$C30-入力!$B$5)*入力!$O30,"")</f>
+        <v>171.6</v>
+      </c>
+      <c r="H43" s="4">
+        <f>IF(ISNUMBER(G43),ROUND(G43/入力!$B$5,0),"")</f>
+        <v>107</v>
+      </c>
+      <c r="I43" s="5" t="str">
+        <f>IF(入力!$B30="","",IF(ISNUMBER(入力!$D30),入力!$D30,""))</f>
+        <v/>
+      </c>
+      <c r="J43" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D30),MAX(0,入力!$D30-入力!$C$5),"")</f>
+        <v/>
+      </c>
+      <c r="K43" s="4" t="str">
+        <f>IF(入力!$B30="","",IF(ISNUMBER(入力!$P30),入力!$P30,""))</f>
+        <v/>
+      </c>
+      <c r="L43" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D30),ISNUMBER(入力!$P30)),入力!$D30*入力!$P30,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D30),ISNUMBER(入力!$P30)),MAX(0,入力!$D30-入力!$C$5)*入力!$P30,"")</f>
+        <v/>
+      </c>
+      <c r="N43" s="4" t="str">
+        <f>IF(ISNUMBER(M43),ROUND(M43/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O43" s="5">
+        <f>IF(入力!$B30="","",IF(AND(NOT(ISNUMBER(G43)),NOT(ISNUMBER(M43))),"",IF(ISNUMBER(G43),G43,0)+IF(ISNUMBER(M43),M43,0)))</f>
+        <v>171.6</v>
+      </c>
+      <c r="P43" s="4">
+        <f>IF(入力!$B30="","",IF(AND(NOT(ISNUMBER(H43)),NOT(ISNUMBER(N43))),"",IF(ISNUMBER(H43),H43,0)+IF(ISNUMBER(N43),N43,0)))</f>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="7" t="str">
+        <f>IF(入力!$B31="","",入力!$B31)</f>
+        <v>向井　ひかり</v>
+      </c>
+      <c r="C44" s="5">
+        <f>IF(入力!$B31="","",IF(ISNUMBER(入力!$C31),入力!$C31,""))</f>
+        <v>1.5</v>
+      </c>
+      <c r="D44" s="5">
+        <f>IF(ISNUMBER(入力!$C31),MAX(0,入力!$C31-入力!$B$5),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="4">
+        <f>IF(入力!$B31="","",IF(ISNUMBER(入力!$O31),入力!$O31,""))</f>
+        <v>866</v>
+      </c>
+      <c r="F44" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C31),ISNUMBER(入力!$O31)),入力!$C31*入力!$O31,"")</f>
+        <v>1299</v>
+      </c>
+      <c r="G44" s="5">
+        <f>IF(AND(ISNUMBER(入力!$C31),ISNUMBER(入力!$O31)),MAX(0,入力!$C31-入力!$B$5)*入力!$O31,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="4">
+        <f>IF(ISNUMBER(G44),ROUND(G44/入力!$B$5,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="str">
+        <f>IF(入力!$B31="","",IF(ISNUMBER(入力!$D31),入力!$D31,""))</f>
+        <v/>
+      </c>
+      <c r="J44" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D31),MAX(0,入力!$D31-入力!$C$5),"")</f>
+        <v/>
+      </c>
+      <c r="K44" s="4" t="str">
+        <f>IF(入力!$B31="","",IF(ISNUMBER(入力!$P31),入力!$P31,""))</f>
+        <v/>
+      </c>
+      <c r="L44" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D31),ISNUMBER(入力!$P31)),入力!$D31*入力!$P31,"")</f>
+        <v/>
+      </c>
+      <c r="M44" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D31),ISNUMBER(入力!$P31)),MAX(0,入力!$D31-入力!$C$5)*入力!$P31,"")</f>
+        <v/>
+      </c>
+      <c r="N44" s="4" t="str">
+        <f>IF(ISNUMBER(M44),ROUND(M44/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O44" s="5">
+        <f>IF(入力!$B31="","",IF(AND(NOT(ISNUMBER(G44)),NOT(ISNUMBER(M44))),"",IF(ISNUMBER(G44),G44,0)+IF(ISNUMBER(M44),M44,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="P44" s="4">
+        <f>IF(入力!$B31="","",IF(AND(NOT(ISNUMBER(H44)),NOT(ISNUMBER(N44))),"",IF(ISNUMBER(H44),H44,0)+IF(ISNUMBER(N44),N44,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="7" t="str">
         <f>IF(入力!$B32="","",入力!$B32)</f>
         <v>高橋　正美</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C45" s="5">
         <f>IF(入力!$B32="","",IF(ISNUMBER(入力!$C32),入力!$C32,""))</f>
         <v>1.9</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D45" s="5">
         <f>IF(ISNUMBER(入力!$C32),MAX(0,入力!$C32-入力!$B$5),"")</f>
         <v>0.3</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E45" s="4">
         <f>IF(入力!$B32="","",IF(ISNUMBER(入力!$O32),入力!$O32,""))</f>
         <v>1090</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F45" s="5">
         <f>IF(AND(ISNUMBER(入力!$C32),ISNUMBER(入力!$O32)),入力!$C32*入力!$O32,"")</f>
         <v>2071</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G45" s="5">
         <f>IF(AND(ISNUMBER(入力!$C32),ISNUMBER(入力!$O32)),MAX(0,入力!$C32-入力!$B$5)*入力!$O32,"")</f>
         <v>327</v>
       </c>
-      <c r="H36" s="4">
-        <f>IF(ISNUMBER(G36),ROUND(G36/入力!$B$5,0),"")</f>
+      <c r="H45" s="4">
+        <f>IF(ISNUMBER(G45),ROUND(G45/入力!$B$5,0),"")</f>
         <v>204</v>
       </c>
-      <c r="I36" s="5" t="str">
+      <c r="I45" s="5" t="str">
         <f>IF(入力!$B32="","",IF(ISNUMBER(入力!$D32),入力!$D32,""))</f>
         <v/>
       </c>
-      <c r="J36" s="5" t="str">
+      <c r="J45" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D32),MAX(0,入力!$D32-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="K36" s="4" t="str">
+      <c r="K45" s="4" t="str">
         <f>IF(入力!$B32="","",IF(ISNUMBER(入力!$P32),入力!$P32,""))</f>
         <v/>
       </c>
-      <c r="L36" s="5" t="str">
+      <c r="L45" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D32),ISNUMBER(入力!$P32)),入力!$D32*入力!$P32,"")</f>
         <v/>
       </c>
-      <c r="M36" s="5" t="str">
+      <c r="M45" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D32),ISNUMBER(入力!$P32)),MAX(0,入力!$D32-入力!$C$5)*入力!$P32,"")</f>
         <v/>
       </c>
-      <c r="N36" s="4" t="str">
-        <f>IF(ISNUMBER(M36),ROUND(M36/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O36" s="5">
-        <f>IF(入力!$B32="","",IF(AND(NOT(ISNUMBER(G36)),NOT(ISNUMBER(M36))),"",IF(ISNUMBER(G36),G36,0)+IF(ISNUMBER(M36),M36,0)))</f>
+      <c r="N45" s="4" t="str">
+        <f>IF(ISNUMBER(M45),ROUND(M45/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O45" s="5">
+        <f>IF(入力!$B32="","",IF(AND(NOT(ISNUMBER(G45)),NOT(ISNUMBER(M45))),"",IF(ISNUMBER(G45),G45,0)+IF(ISNUMBER(M45),M45,0)))</f>
         <v>327</v>
       </c>
-      <c r="P36" s="4">
-        <f>IF(入力!$B32="","",IF(AND(NOT(ISNUMBER(H36)),NOT(ISNUMBER(N36))),"",IF(ISNUMBER(H36),H36,0)+IF(ISNUMBER(N36),N36,0)))</f>
+      <c r="P45" s="4">
+        <f>IF(入力!$B32="","",IF(AND(NOT(ISNUMBER(H45)),NOT(ISNUMBER(N45))),"",IF(ISNUMBER(H45),H45,0)+IF(ISNUMBER(N45),N45,0)))</f>
         <v>204</v>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="7" t="str">
+    <row r="46">
+      <c r="B46" s="7" t="str">
         <f>IF(入力!$B33="","",入力!$B33)</f>
         <v>廣瀬　こずえ</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C46" s="5">
         <f>IF(入力!$B33="","",IF(ISNUMBER(入力!$C33),入力!$C33,""))</f>
         <v>2</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D46" s="5">
         <f>IF(ISNUMBER(入力!$C33),MAX(0,入力!$C33-入力!$B$5),"")</f>
         <v>0.4</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E46" s="4">
         <f>IF(入力!$B33="","",IF(ISNUMBER(入力!$O33),入力!$O33,""))</f>
         <v>838</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F46" s="5">
         <f>IF(AND(ISNUMBER(入力!$C33),ISNUMBER(入力!$O33)),入力!$C33*入力!$O33,"")</f>
         <v>1676</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G46" s="5">
         <f>IF(AND(ISNUMBER(入力!$C33),ISNUMBER(入力!$O33)),MAX(0,入力!$C33-入力!$B$5)*入力!$O33,"")</f>
         <v>335.2</v>
       </c>
-      <c r="H37" s="4">
-        <f>IF(ISNUMBER(G37),ROUND(G37/入力!$B$5,0),"")</f>
+      <c r="H46" s="4">
+        <f>IF(ISNUMBER(G46),ROUND(G46/入力!$B$5,0),"")</f>
         <v>209</v>
       </c>
-      <c r="I37" s="5" t="str">
+      <c r="I46" s="5" t="str">
         <f>IF(入力!$B33="","",IF(ISNUMBER(入力!$D33),入力!$D33,""))</f>
         <v/>
       </c>
-      <c r="J37" s="5" t="str">
+      <c r="J46" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D33),MAX(0,入力!$D33-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="K37" s="4" t="str">
+      <c r="K46" s="4" t="str">
         <f>IF(入力!$B33="","",IF(ISNUMBER(入力!$P33),入力!$P33,""))</f>
         <v/>
       </c>
-      <c r="L37" s="5" t="str">
+      <c r="L46" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D33),ISNUMBER(入力!$P33)),入力!$D33*入力!$P33,"")</f>
         <v/>
       </c>
-      <c r="M37" s="5" t="str">
+      <c r="M46" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D33),ISNUMBER(入力!$P33)),MAX(0,入力!$D33-入力!$C$5)*入力!$P33,"")</f>
         <v/>
       </c>
-      <c r="N37" s="4" t="str">
-        <f>IF(ISNUMBER(M37),ROUND(M37/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O37" s="5">
-        <f>IF(入力!$B33="","",IF(AND(NOT(ISNUMBER(G37)),NOT(ISNUMBER(M37))),"",IF(ISNUMBER(G37),G37,0)+IF(ISNUMBER(M37),M37,0)))</f>
+      <c r="N46" s="4" t="str">
+        <f>IF(ISNUMBER(M46),ROUND(M46/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O46" s="5">
+        <f>IF(入力!$B33="","",IF(AND(NOT(ISNUMBER(G46)),NOT(ISNUMBER(M46))),"",IF(ISNUMBER(G46),G46,0)+IF(ISNUMBER(M46),M46,0)))</f>
         <v>335.2</v>
       </c>
-      <c r="P37" s="4">
-        <f>IF(入力!$B33="","",IF(AND(NOT(ISNUMBER(H37)),NOT(ISNUMBER(N37))),"",IF(ISNUMBER(H37),H37,0)+IF(ISNUMBER(N37),N37,0)))</f>
+      <c r="P46" s="4">
+        <f>IF(入力!$B33="","",IF(AND(NOT(ISNUMBER(H46)),NOT(ISNUMBER(N46))),"",IF(ISNUMBER(H46),H46,0)+IF(ISNUMBER(N46),N46,0)))</f>
         <v>209</v>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="7" t="str">
+    <row r="47">
+      <c r="B47" s="7" t="str">
         <f>IF(入力!$B34="","",入力!$B34)</f>
         <v>石戸谷　亜子</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C47" s="5">
         <f>IF(入力!$B34="","",IF(ISNUMBER(入力!$C34),入力!$C34,""))</f>
         <v>1.3</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D47" s="5">
         <f>IF(ISNUMBER(入力!$C34),MAX(0,入力!$C34-入力!$B$5),"")</f>
         <v>0</v>
       </c>
-      <c r="E38" s="4" t="str">
+      <c r="E47" s="4" t="str">
         <f>IF(入力!$B34="","",IF(ISNUMBER(入力!$O34),入力!$O34,""))</f>
         <v/>
       </c>
-      <c r="F38" s="5" t="str">
+      <c r="F47" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$C34),ISNUMBER(入力!$O34)),入力!$C34*入力!$O34,"")</f>
         <v/>
       </c>
-      <c r="G38" s="5" t="str">
+      <c r="G47" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$C34),ISNUMBER(入力!$O34)),MAX(0,入力!$C34-入力!$B$5)*入力!$O34,"")</f>
         <v/>
       </c>
-      <c r="H38" s="4" t="str">
-        <f>IF(ISNUMBER(G38),ROUND(G38/入力!$B$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="5" t="str">
+      <c r="H47" s="4" t="str">
+        <f>IF(ISNUMBER(G47),ROUND(G47/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="5" t="str">
         <f>IF(入力!$B34="","",IF(ISNUMBER(入力!$D34),入力!$D34,""))</f>
         <v/>
       </c>
-      <c r="J38" s="5" t="str">
+      <c r="J47" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D34),MAX(0,入力!$D34-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="K38" s="4" t="str">
+      <c r="K47" s="4" t="str">
         <f>IF(入力!$B34="","",IF(ISNUMBER(入力!$P34),入力!$P34,""))</f>
         <v/>
       </c>
-      <c r="L38" s="5" t="str">
+      <c r="L47" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D34),ISNUMBER(入力!$P34)),入力!$D34*入力!$P34,"")</f>
         <v/>
       </c>
-      <c r="M38" s="5" t="str">
+      <c r="M47" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D34),ISNUMBER(入力!$P34)),MAX(0,入力!$D34-入力!$C$5)*入力!$P34,"")</f>
         <v/>
       </c>
-      <c r="N38" s="4" t="str">
-        <f>IF(ISNUMBER(M38),ROUND(M38/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O38" s="5" t="str">
-        <f>IF(入力!$B34="","",IF(AND(NOT(ISNUMBER(G38)),NOT(ISNUMBER(M38))),"",IF(ISNUMBER(G38),G38,0)+IF(ISNUMBER(M38),M38,0)))</f>
-        <v/>
-      </c>
-      <c r="P38" s="4" t="str">
-        <f>IF(入力!$B34="","",IF(AND(NOT(ISNUMBER(H38)),NOT(ISNUMBER(N38))),"",IF(ISNUMBER(H38),H38,0)+IF(ISNUMBER(N38),N38,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="7" t="str">
+      <c r="N47" s="4" t="str">
+        <f>IF(ISNUMBER(M47),ROUND(M47/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O47" s="5" t="str">
+        <f>IF(入力!$B34="","",IF(AND(NOT(ISNUMBER(G47)),NOT(ISNUMBER(M47))),"",IF(ISNUMBER(G47),G47,0)+IF(ISNUMBER(M47),M47,0)))</f>
+        <v/>
+      </c>
+      <c r="P47" s="4" t="str">
+        <f>IF(入力!$B34="","",IF(AND(NOT(ISNUMBER(H47)),NOT(ISNUMBER(N47))),"",IF(ISNUMBER(H47),H47,0)+IF(ISNUMBER(N47),N47,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="7" t="str">
         <f>IF(入力!$B35="","",入力!$B35)</f>
         <v>奥野　愛海</v>
       </c>
-      <c r="C39" s="5" t="str">
+      <c r="C48" s="5" t="str">
         <f>IF(入力!$B35="","",IF(ISNUMBER(入力!$C35),入力!$C35,""))</f>
         <v/>
       </c>
-      <c r="D39" s="5" t="str">
+      <c r="D48" s="5" t="str">
         <f>IF(ISNUMBER(入力!$C35),MAX(0,入力!$C35-入力!$B$5),"")</f>
         <v/>
       </c>
-      <c r="E39" s="4" t="str">
+      <c r="E48" s="4" t="str">
         <f>IF(入力!$B35="","",IF(ISNUMBER(入力!$O35),入力!$O35,""))</f>
         <v/>
       </c>
-      <c r="F39" s="5" t="str">
+      <c r="F48" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$C35),ISNUMBER(入力!$O35)),入力!$C35*入力!$O35,"")</f>
         <v/>
       </c>
-      <c r="G39" s="5" t="str">
+      <c r="G48" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$C35),ISNUMBER(入力!$O35)),MAX(0,入力!$C35-入力!$B$5)*入力!$O35,"")</f>
         <v/>
       </c>
-      <c r="H39" s="4" t="str">
-        <f>IF(ISNUMBER(G39),ROUND(G39/入力!$B$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="5" t="str">
+      <c r="H48" s="4" t="str">
+        <f>IF(ISNUMBER(G48),ROUND(G48/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="5" t="str">
         <f>IF(入力!$B35="","",IF(ISNUMBER(入力!$D35),入力!$D35,""))</f>
         <v/>
       </c>
-      <c r="J39" s="5" t="str">
+      <c r="J48" s="5" t="str">
         <f>IF(ISNUMBER(入力!$D35),MAX(0,入力!$D35-入力!$C$5),"")</f>
         <v/>
       </c>
-      <c r="K39" s="4" t="str">
+      <c r="K48" s="4" t="str">
         <f>IF(入力!$B35="","",IF(ISNUMBER(入力!$P35),入力!$P35,""))</f>
         <v/>
       </c>
-      <c r="L39" s="5" t="str">
+      <c r="L48" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D35),ISNUMBER(入力!$P35)),入力!$D35*入力!$P35,"")</f>
         <v/>
       </c>
-      <c r="M39" s="5" t="str">
+      <c r="M48" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$D35),ISNUMBER(入力!$P35)),MAX(0,入力!$D35-入力!$C$5)*入力!$P35,"")</f>
         <v/>
       </c>
-      <c r="N39" s="4" t="str">
-        <f>IF(ISNUMBER(M39),ROUND(M39/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O39" s="5" t="str">
-        <f>IF(入力!$B35="","",IF(AND(NOT(ISNUMBER(G39)),NOT(ISNUMBER(M39))),"",IF(ISNUMBER(G39),G39,0)+IF(ISNUMBER(M39),M39,0)))</f>
-        <v/>
-      </c>
-      <c r="P39" s="4" t="str">
-        <f>IF(入力!$B35="","",IF(AND(NOT(ISNUMBER(H39)),NOT(ISNUMBER(N39))),"",IF(ISNUMBER(H39),H39,0)+IF(ISNUMBER(N39),N39,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="7" t="str">
+      <c r="N48" s="4" t="str">
+        <f>IF(ISNUMBER(M48),ROUND(M48/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O48" s="5" t="str">
+        <f>IF(入力!$B35="","",IF(AND(NOT(ISNUMBER(G48)),NOT(ISNUMBER(M48))),"",IF(ISNUMBER(G48),G48,0)+IF(ISNUMBER(M48),M48,0)))</f>
+        <v/>
+      </c>
+      <c r="P48" s="4" t="str">
+        <f>IF(入力!$B35="","",IF(AND(NOT(ISNUMBER(H48)),NOT(ISNUMBER(N48))),"",IF(ISNUMBER(H48),H48,0)+IF(ISNUMBER(N48),N48,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="7" t="str">
         <f>IF(入力!$B36="","",入力!$B36)</f>
         <v>平田　学</v>
       </c>
-      <c r="C40" s="5" t="str">
+      <c r="C49" s="5" t="str">
         <f>IF(入力!$B36="","",IF(ISNUMBER(入力!$C36),入力!$C36,""))</f>
         <v/>
       </c>
-      <c r="D40" s="5" t="str">
+      <c r="D49" s="5" t="str">
         <f>IF(ISNUMBER(入力!$C36),MAX(0,入力!$C36-入力!$B$5),"")</f>
         <v/>
       </c>
-      <c r="E40" s="4" t="str">
+      <c r="E49" s="4" t="str">
         <f>IF(入力!$B36="","",IF(ISNUMBER(入力!$O36),入力!$O36,""))</f>
         <v/>
       </c>
-      <c r="F40" s="5" t="str">
+      <c r="F49" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$C36),ISNUMBER(入力!$O36)),入力!$C36*入力!$O36,"")</f>
         <v/>
       </c>
-      <c r="G40" s="5" t="str">
+      <c r="G49" s="5" t="str">
         <f>IF(AND(ISNUMBER(入力!$C36),ISNUMBER(入力!$O36)),MAX(0,入力!$C36-入力!$B$5)*入力!$O36,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="4" t="str">
-        <f>IF(ISNUMBER(G40),ROUND(G40/入力!$B$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="5" t="str">
-        <f>IF(入力!$B36="","",IF(ISNUMBER(入力!$D36),入力!$D36,""))</f>
-        <v/>
-      </c>
-      <c r="J40" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D36),MAX(0,入力!$D36-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K40" s="4" t="str">
-        <f>IF(入力!$B36="","",IF(ISNUMBER(入力!$P36),入力!$P36,""))</f>
-        <v/>
-      </c>
-      <c r="L40" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D36),ISNUMBER(入力!$P36)),入力!$D36*入力!$P36,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D36),ISNUMBER(入力!$P36)),MAX(0,入力!$D36-入力!$C$5)*入力!$P36,"")</f>
-        <v/>
-      </c>
-      <c r="N40" s="4" t="str">
-        <f>IF(ISNUMBER(M40),ROUND(M40/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O40" s="5" t="str">
-        <f>IF(入力!$B36="","",IF(AND(NOT(ISNUMBER(G40)),NOT(ISNUMBER(M40))),"",IF(ISNUMBER(G40),G40,0)+IF(ISNUMBER(M40),M40,0)))</f>
-        <v/>
-      </c>
-      <c r="P40" s="4" t="str">
-        <f>IF(入力!$B36="","",IF(AND(NOT(ISNUMBER(H40)),NOT(ISNUMBER(N40))),"",IF(ISNUMBER(H40),H40,0)+IF(ISNUMBER(N40),N40,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="7" t="str">
-        <f>IF(入力!$B37="","",入力!$B37)</f>
-        <v/>
-      </c>
-      <c r="C41" s="5" t="str">
-        <f>IF(入力!$B37="","",IF(ISNUMBER(入力!$C37),入力!$C37,""))</f>
-        <v/>
-      </c>
-      <c r="D41" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C37),MAX(0,入力!$C37-入力!$B$5),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="4" t="str">
-        <f>IF(入力!$B37="","",IF(ISNUMBER(入力!$O37),入力!$O37,""))</f>
-        <v/>
-      </c>
-      <c r="F41" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C37),ISNUMBER(入力!$O37)),入力!$C37*入力!$O37,"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C37),ISNUMBER(入力!$O37)),MAX(0,入力!$C37-入力!$B$5)*入力!$O37,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="4" t="str">
-        <f>IF(ISNUMBER(G41),ROUND(G41/入力!$B$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="5" t="str">
-        <f>IF(入力!$B37="","",IF(ISNUMBER(入力!$D37),入力!$D37,""))</f>
-        <v/>
-      </c>
-      <c r="J41" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D37),MAX(0,入力!$D37-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K41" s="4" t="str">
-        <f>IF(入力!$B37="","",IF(ISNUMBER(入力!$P37),入力!$P37,""))</f>
-        <v/>
-      </c>
-      <c r="L41" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D37),ISNUMBER(入力!$P37)),入力!$D37*入力!$P37,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D37),ISNUMBER(入力!$P37)),MAX(0,入力!$D37-入力!$C$5)*入力!$P37,"")</f>
-        <v/>
-      </c>
-      <c r="N41" s="4" t="str">
-        <f>IF(ISNUMBER(M41),ROUND(M41/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O41" s="5" t="str">
-        <f>IF(入力!$B37="","",IF(AND(NOT(ISNUMBER(G41)),NOT(ISNUMBER(M41))),"",IF(ISNUMBER(G41),G41,0)+IF(ISNUMBER(M41),M41,0)))</f>
-        <v/>
-      </c>
-      <c r="P41" s="4" t="str">
-        <f>IF(入力!$B37="","",IF(AND(NOT(ISNUMBER(H41)),NOT(ISNUMBER(N41))),"",IF(ISNUMBER(H41),H41,0)+IF(ISNUMBER(N41),N41,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="7" t="str">
-        <f>IF(入力!$B38="","",入力!$B38)</f>
-        <v/>
-      </c>
-      <c r="C42" s="5" t="str">
-        <f>IF(入力!$B38="","",IF(ISNUMBER(入力!$C38),入力!$C38,""))</f>
-        <v/>
-      </c>
-      <c r="D42" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C38),MAX(0,入力!$C38-入力!$B$5),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="4" t="str">
-        <f>IF(入力!$B38="","",IF(ISNUMBER(入力!$O38),入力!$O38,""))</f>
-        <v/>
-      </c>
-      <c r="F42" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C38),ISNUMBER(入力!$O38)),入力!$C38*入力!$O38,"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C38),ISNUMBER(入力!$O38)),MAX(0,入力!$C38-入力!$B$5)*入力!$O38,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="4" t="str">
-        <f>IF(ISNUMBER(G42),ROUND(G42/入力!$B$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="5" t="str">
-        <f>IF(入力!$B38="","",IF(ISNUMBER(入力!$D38),入力!$D38,""))</f>
-        <v/>
-      </c>
-      <c r="J42" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D38),MAX(0,入力!$D38-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K42" s="4" t="str">
-        <f>IF(入力!$B38="","",IF(ISNUMBER(入力!$P38),入力!$P38,""))</f>
-        <v/>
-      </c>
-      <c r="L42" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D38),ISNUMBER(入力!$P38)),入力!$D38*入力!$P38,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D38),ISNUMBER(入力!$P38)),MAX(0,入力!$D38-入力!$C$5)*入力!$P38,"")</f>
-        <v/>
-      </c>
-      <c r="N42" s="4" t="str">
-        <f>IF(ISNUMBER(M42),ROUND(M42/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O42" s="5" t="str">
-        <f>IF(入力!$B38="","",IF(AND(NOT(ISNUMBER(G42)),NOT(ISNUMBER(M42))),"",IF(ISNUMBER(G42),G42,0)+IF(ISNUMBER(M42),M42,0)))</f>
-        <v/>
-      </c>
-      <c r="P42" s="4" t="str">
-        <f>IF(入力!$B38="","",IF(AND(NOT(ISNUMBER(H42)),NOT(ISNUMBER(N42))),"",IF(ISNUMBER(H42),H42,0)+IF(ISNUMBER(N42),N42,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="7" t="str">
-        <f>IF(入力!$B39="","",入力!$B39)</f>
-        <v/>
-      </c>
-      <c r="C43" s="5" t="str">
-        <f>IF(入力!$B39="","",IF(ISNUMBER(入力!$C39),入力!$C39,""))</f>
-        <v/>
-      </c>
-      <c r="D43" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C39),MAX(0,入力!$C39-入力!$B$5),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="4" t="str">
-        <f>IF(入力!$B39="","",IF(ISNUMBER(入力!$O39),入力!$O39,""))</f>
-        <v/>
-      </c>
-      <c r="F43" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C39),ISNUMBER(入力!$O39)),入力!$C39*入力!$O39,"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C39),ISNUMBER(入力!$O39)),MAX(0,入力!$C39-入力!$B$5)*入力!$O39,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="4" t="str">
-        <f>IF(ISNUMBER(G43),ROUND(G43/入力!$B$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="5" t="str">
-        <f>IF(入力!$B39="","",IF(ISNUMBER(入力!$D39),入力!$D39,""))</f>
-        <v/>
-      </c>
-      <c r="J43" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D39),MAX(0,入力!$D39-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K43" s="4" t="str">
-        <f>IF(入力!$B39="","",IF(ISNUMBER(入力!$P39),入力!$P39,""))</f>
-        <v/>
-      </c>
-      <c r="L43" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D39),ISNUMBER(入力!$P39)),入力!$D39*入力!$P39,"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D39),ISNUMBER(入力!$P39)),MAX(0,入力!$D39-入力!$C$5)*入力!$P39,"")</f>
-        <v/>
-      </c>
-      <c r="N43" s="4" t="str">
-        <f>IF(ISNUMBER(M43),ROUND(M43/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O43" s="5" t="str">
-        <f>IF(入力!$B39="","",IF(AND(NOT(ISNUMBER(G43)),NOT(ISNUMBER(M43))),"",IF(ISNUMBER(G43),G43,0)+IF(ISNUMBER(M43),M43,0)))</f>
-        <v/>
-      </c>
-      <c r="P43" s="4" t="str">
-        <f>IF(入力!$B39="","",IF(AND(NOT(ISNUMBER(H43)),NOT(ISNUMBER(N43))),"",IF(ISNUMBER(H43),H43,0)+IF(ISNUMBER(N43),N43,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="7" t="str">
-        <f>IF(入力!$B40="","",入力!$B40)</f>
-        <v/>
-      </c>
-      <c r="C44" s="5" t="str">
-        <f>IF(入力!$B40="","",IF(ISNUMBER(入力!$C40),入力!$C40,""))</f>
-        <v/>
-      </c>
-      <c r="D44" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C40),MAX(0,入力!$C40-入力!$B$5),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="4" t="str">
-        <f>IF(入力!$B40="","",IF(ISNUMBER(入力!$O40),入力!$O40,""))</f>
-        <v/>
-      </c>
-      <c r="F44" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C40),ISNUMBER(入力!$O40)),入力!$C40*入力!$O40,"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C40),ISNUMBER(入力!$O40)),MAX(0,入力!$C40-入力!$B$5)*入力!$O40,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="4" t="str">
-        <f>IF(ISNUMBER(G44),ROUND(G44/入力!$B$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="5" t="str">
-        <f>IF(入力!$B40="","",IF(ISNUMBER(入力!$D40),入力!$D40,""))</f>
-        <v/>
-      </c>
-      <c r="J44" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D40),MAX(0,入力!$D40-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K44" s="4" t="str">
-        <f>IF(入力!$B40="","",IF(ISNUMBER(入力!$P40),入力!$P40,""))</f>
-        <v/>
-      </c>
-      <c r="L44" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D40),ISNUMBER(入力!$P40)),入力!$D40*入力!$P40,"")</f>
-        <v/>
-      </c>
-      <c r="M44" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D40),ISNUMBER(入力!$P40)),MAX(0,入力!$D40-入力!$C$5)*入力!$P40,"")</f>
-        <v/>
-      </c>
-      <c r="N44" s="4" t="str">
-        <f>IF(ISNUMBER(M44),ROUND(M44/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O44" s="5" t="str">
-        <f>IF(入力!$B40="","",IF(AND(NOT(ISNUMBER(G44)),NOT(ISNUMBER(M44))),"",IF(ISNUMBER(G44),G44,0)+IF(ISNUMBER(M44),M44,0)))</f>
-        <v/>
-      </c>
-      <c r="P44" s="4" t="str">
-        <f>IF(入力!$B40="","",IF(AND(NOT(ISNUMBER(H44)),NOT(ISNUMBER(N44))),"",IF(ISNUMBER(H44),H44,0)+IF(ISNUMBER(N44),N44,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="7" t="str">
-        <f>IF(入力!$B41="","",入力!$B41)</f>
-        <v/>
-      </c>
-      <c r="C45" s="5" t="str">
-        <f>IF(入力!$B41="","",IF(ISNUMBER(入力!$C41),入力!$C41,""))</f>
-        <v/>
-      </c>
-      <c r="D45" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C41),MAX(0,入力!$C41-入力!$B$5),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="4" t="str">
-        <f>IF(入力!$B41="","",IF(ISNUMBER(入力!$O41),入力!$O41,""))</f>
-        <v/>
-      </c>
-      <c r="F45" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C41),ISNUMBER(入力!$O41)),入力!$C41*入力!$O41,"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C41),ISNUMBER(入力!$O41)),MAX(0,入力!$C41-入力!$B$5)*入力!$O41,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="4" t="str">
-        <f>IF(ISNUMBER(G45),ROUND(G45/入力!$B$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="5" t="str">
-        <f>IF(入力!$B41="","",IF(ISNUMBER(入力!$D41),入力!$D41,""))</f>
-        <v/>
-      </c>
-      <c r="J45" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D41),MAX(0,入力!$D41-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K45" s="4" t="str">
-        <f>IF(入力!$B41="","",IF(ISNUMBER(入力!$P41),入力!$P41,""))</f>
-        <v/>
-      </c>
-      <c r="L45" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D41),ISNUMBER(入力!$P41)),入力!$D41*入力!$P41,"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D41),ISNUMBER(入力!$P41)),MAX(0,入力!$D41-入力!$C$5)*入力!$P41,"")</f>
-        <v/>
-      </c>
-      <c r="N45" s="4" t="str">
-        <f>IF(ISNUMBER(M45),ROUND(M45/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O45" s="5" t="str">
-        <f>IF(入力!$B41="","",IF(AND(NOT(ISNUMBER(G45)),NOT(ISNUMBER(M45))),"",IF(ISNUMBER(G45),G45,0)+IF(ISNUMBER(M45),M45,0)))</f>
-        <v/>
-      </c>
-      <c r="P45" s="4" t="str">
-        <f>IF(入力!$B41="","",IF(AND(NOT(ISNUMBER(H45)),NOT(ISNUMBER(N45))),"",IF(ISNUMBER(H45),H45,0)+IF(ISNUMBER(N45),N45,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="7" t="str">
-        <f>IF(入力!$B42="","",入力!$B42)</f>
-        <v/>
-      </c>
-      <c r="C46" s="5" t="str">
-        <f>IF(入力!$B42="","",IF(ISNUMBER(入力!$C42),入力!$C42,""))</f>
-        <v/>
-      </c>
-      <c r="D46" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C42),MAX(0,入力!$C42-入力!$B$5),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="4" t="str">
-        <f>IF(入力!$B42="","",IF(ISNUMBER(入力!$O42),入力!$O42,""))</f>
-        <v/>
-      </c>
-      <c r="F46" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C42),ISNUMBER(入力!$O42)),入力!$C42*入力!$O42,"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C42),ISNUMBER(入力!$O42)),MAX(0,入力!$C42-入力!$B$5)*入力!$O42,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="4" t="str">
-        <f>IF(ISNUMBER(G46),ROUND(G46/入力!$B$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="5" t="str">
-        <f>IF(入力!$B42="","",IF(ISNUMBER(入力!$D42),入力!$D42,""))</f>
-        <v/>
-      </c>
-      <c r="J46" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D42),MAX(0,入力!$D42-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K46" s="4" t="str">
-        <f>IF(入力!$B42="","",IF(ISNUMBER(入力!$P42),入力!$P42,""))</f>
-        <v/>
-      </c>
-      <c r="L46" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D42),ISNUMBER(入力!$P42)),入力!$D42*入力!$P42,"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D42),ISNUMBER(入力!$P42)),MAX(0,入力!$D42-入力!$C$5)*入力!$P42,"")</f>
-        <v/>
-      </c>
-      <c r="N46" s="4" t="str">
-        <f>IF(ISNUMBER(M46),ROUND(M46/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O46" s="5" t="str">
-        <f>IF(入力!$B42="","",IF(AND(NOT(ISNUMBER(G46)),NOT(ISNUMBER(M46))),"",IF(ISNUMBER(G46),G46,0)+IF(ISNUMBER(M46),M46,0)))</f>
-        <v/>
-      </c>
-      <c r="P46" s="4" t="str">
-        <f>IF(入力!$B42="","",IF(AND(NOT(ISNUMBER(H46)),NOT(ISNUMBER(N46))),"",IF(ISNUMBER(H46),H46,0)+IF(ISNUMBER(N46),N46,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="7" t="str">
-        <f>IF(入力!$B43="","",入力!$B43)</f>
-        <v/>
-      </c>
-      <c r="C47" s="5" t="str">
-        <f>IF(入力!$B43="","",IF(ISNUMBER(入力!$C43),入力!$C43,""))</f>
-        <v/>
-      </c>
-      <c r="D47" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C43),MAX(0,入力!$C43-入力!$B$5),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="4" t="str">
-        <f>IF(入力!$B43="","",IF(ISNUMBER(入力!$O43),入力!$O43,""))</f>
-        <v/>
-      </c>
-      <c r="F47" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C43),ISNUMBER(入力!$O43)),入力!$C43*入力!$O43,"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C43),ISNUMBER(入力!$O43)),MAX(0,入力!$C43-入力!$B$5)*入力!$O43,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="4" t="str">
-        <f>IF(ISNUMBER(G47),ROUND(G47/入力!$B$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="5" t="str">
-        <f>IF(入力!$B43="","",IF(ISNUMBER(入力!$D43),入力!$D43,""))</f>
-        <v/>
-      </c>
-      <c r="J47" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D43),MAX(0,入力!$D43-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K47" s="4" t="str">
-        <f>IF(入力!$B43="","",IF(ISNUMBER(入力!$P43),入力!$P43,""))</f>
-        <v/>
-      </c>
-      <c r="L47" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D43),ISNUMBER(入力!$P43)),入力!$D43*入力!$P43,"")</f>
-        <v/>
-      </c>
-      <c r="M47" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D43),ISNUMBER(入力!$P43)),MAX(0,入力!$D43-入力!$C$5)*入力!$P43,"")</f>
-        <v/>
-      </c>
-      <c r="N47" s="4" t="str">
-        <f>IF(ISNUMBER(M47),ROUND(M47/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O47" s="5" t="str">
-        <f>IF(入力!$B43="","",IF(AND(NOT(ISNUMBER(G47)),NOT(ISNUMBER(M47))),"",IF(ISNUMBER(G47),G47,0)+IF(ISNUMBER(M47),M47,0)))</f>
-        <v/>
-      </c>
-      <c r="P47" s="4" t="str">
-        <f>IF(入力!$B43="","",IF(AND(NOT(ISNUMBER(H47)),NOT(ISNUMBER(N47))),"",IF(ISNUMBER(H47),H47,0)+IF(ISNUMBER(N47),N47,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="7" t="str">
-        <f>IF(入力!$B44="","",入力!$B44)</f>
-        <v/>
-      </c>
-      <c r="C48" s="5" t="str">
-        <f>IF(入力!$B44="","",IF(ISNUMBER(入力!$C44),入力!$C44,""))</f>
-        <v/>
-      </c>
-      <c r="D48" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C44),MAX(0,入力!$C44-入力!$B$5),"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="4" t="str">
-        <f>IF(入力!$B44="","",IF(ISNUMBER(入力!$O44),入力!$O44,""))</f>
-        <v/>
-      </c>
-      <c r="F48" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C44),ISNUMBER(入力!$O44)),入力!$C44*入力!$O44,"")</f>
-        <v/>
-      </c>
-      <c r="G48" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C44),ISNUMBER(入力!$O44)),MAX(0,入力!$C44-入力!$B$5)*入力!$O44,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="4" t="str">
-        <f>IF(ISNUMBER(G48),ROUND(G48/入力!$B$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="5" t="str">
-        <f>IF(入力!$B44="","",IF(ISNUMBER(入力!$D44),入力!$D44,""))</f>
-        <v/>
-      </c>
-      <c r="J48" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D44),MAX(0,入力!$D44-入力!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="K48" s="4" t="str">
-        <f>IF(入力!$B44="","",IF(ISNUMBER(入力!$P44),入力!$P44,""))</f>
-        <v/>
-      </c>
-      <c r="L48" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D44),ISNUMBER(入力!$P44)),入力!$D44*入力!$P44,"")</f>
-        <v/>
-      </c>
-      <c r="M48" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D44),ISNUMBER(入力!$P44)),MAX(0,入力!$D44-入力!$C$5)*入力!$P44,"")</f>
-        <v/>
-      </c>
-      <c r="N48" s="4" t="str">
-        <f>IF(ISNUMBER(M48),ROUND(M48/入力!$C$5,0),"")</f>
-        <v/>
-      </c>
-      <c r="O48" s="5" t="str">
-        <f>IF(入力!$B44="","",IF(AND(NOT(ISNUMBER(G48)),NOT(ISNUMBER(M48))),"",IF(ISNUMBER(G48),G48,0)+IF(ISNUMBER(M48),M48,0)))</f>
-        <v/>
-      </c>
-      <c r="P48" s="4" t="str">
-        <f>IF(入力!$B44="","",IF(AND(NOT(ISNUMBER(H48)),NOT(ISNUMBER(N48))),"",IF(ISNUMBER(H48),H48,0)+IF(ISNUMBER(N48),N48,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="7" t="str">
-        <f>IF(入力!$B45="","",入力!$B45)</f>
-        <v/>
-      </c>
-      <c r="C49" s="5" t="str">
-        <f>IF(入力!$B45="","",IF(ISNUMBER(入力!$C45),入力!$C45,""))</f>
-        <v/>
-      </c>
-      <c r="D49" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C45),MAX(0,入力!$C45-入力!$B$5),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="4" t="str">
-        <f>IF(入力!$B45="","",IF(ISNUMBER(入力!$O45),入力!$O45,""))</f>
-        <v/>
-      </c>
-      <c r="F49" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C45),ISNUMBER(入力!$O45)),入力!$C45*入力!$O45,"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C45),ISNUMBER(入力!$O45)),MAX(0,入力!$C45-入力!$B$5)*入力!$O45,"")</f>
         <v/>
       </c>
       <c r="H49" s="4" t="str">
@@ -25756,23 +25330,23 @@
         <v/>
       </c>
       <c r="I49" s="5" t="str">
-        <f>IF(入力!$B45="","",IF(ISNUMBER(入力!$D45),入力!$D45,""))</f>
+        <f>IF(入力!$B36="","",IF(ISNUMBER(入力!$D36),入力!$D36,""))</f>
         <v/>
       </c>
       <c r="J49" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D45),MAX(0,入力!$D45-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D36),MAX(0,入力!$D36-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K49" s="4" t="str">
-        <f>IF(入力!$B45="","",IF(ISNUMBER(入力!$P45),入力!$P45,""))</f>
+        <f>IF(入力!$B36="","",IF(ISNUMBER(入力!$P36),入力!$P36,""))</f>
         <v/>
       </c>
       <c r="L49" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D45),ISNUMBER(入力!$P45)),入力!$D45*入力!$P45,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D36),ISNUMBER(入力!$P36)),入力!$D36*入力!$P36,"")</f>
         <v/>
       </c>
       <c r="M49" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D45),ISNUMBER(入力!$P45)),MAX(0,入力!$D45-入力!$C$5)*入力!$P45,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D36),ISNUMBER(入力!$P36)),MAX(0,入力!$D36-入力!$C$5)*入力!$P36,"")</f>
         <v/>
       </c>
       <c r="N49" s="4" t="str">
@@ -25780,37 +25354,37 @@
         <v/>
       </c>
       <c r="O49" s="5" t="str">
-        <f>IF(入力!$B45="","",IF(AND(NOT(ISNUMBER(G49)),NOT(ISNUMBER(M49))),"",IF(ISNUMBER(G49),G49,0)+IF(ISNUMBER(M49),M49,0)))</f>
+        <f>IF(入力!$B36="","",IF(AND(NOT(ISNUMBER(G49)),NOT(ISNUMBER(M49))),"",IF(ISNUMBER(G49),G49,0)+IF(ISNUMBER(M49),M49,0)))</f>
         <v/>
       </c>
       <c r="P49" s="4" t="str">
-        <f>IF(入力!$B45="","",IF(AND(NOT(ISNUMBER(H49)),NOT(ISNUMBER(N49))),"",IF(ISNUMBER(H49),H49,0)+IF(ISNUMBER(N49),N49,0)))</f>
+        <f>IF(入力!$B36="","",IF(AND(NOT(ISNUMBER(H49)),NOT(ISNUMBER(N49))),"",IF(ISNUMBER(H49),H49,0)+IF(ISNUMBER(N49),N49,0)))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="7" t="str">
-        <f>IF(入力!$B46="","",入力!$B46)</f>
+        <f>IF(入力!$B37="","",入力!$B37)</f>
         <v/>
       </c>
       <c r="C50" s="5" t="str">
-        <f>IF(入力!$B46="","",IF(ISNUMBER(入力!$C46),入力!$C46,""))</f>
+        <f>IF(入力!$B37="","",IF(ISNUMBER(入力!$C37),入力!$C37,""))</f>
         <v/>
       </c>
       <c r="D50" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C46),MAX(0,入力!$C46-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C37),MAX(0,入力!$C37-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E50" s="4" t="str">
-        <f>IF(入力!$B46="","",IF(ISNUMBER(入力!$O46),入力!$O46,""))</f>
+        <f>IF(入力!$B37="","",IF(ISNUMBER(入力!$O37),入力!$O37,""))</f>
         <v/>
       </c>
       <c r="F50" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C46),ISNUMBER(入力!$O46)),入力!$C46*入力!$O46,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C37),ISNUMBER(入力!$O37)),入力!$C37*入力!$O37,"")</f>
         <v/>
       </c>
       <c r="G50" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C46),ISNUMBER(入力!$O46)),MAX(0,入力!$C46-入力!$B$5)*入力!$O46,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C37),ISNUMBER(入力!$O37)),MAX(0,入力!$C37-入力!$B$5)*入力!$O37,"")</f>
         <v/>
       </c>
       <c r="H50" s="4" t="str">
@@ -25818,23 +25392,23 @@
         <v/>
       </c>
       <c r="I50" s="5" t="str">
-        <f>IF(入力!$B46="","",IF(ISNUMBER(入力!$D46),入力!$D46,""))</f>
+        <f>IF(入力!$B37="","",IF(ISNUMBER(入力!$D37),入力!$D37,""))</f>
         <v/>
       </c>
       <c r="J50" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D46),MAX(0,入力!$D46-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D37),MAX(0,入力!$D37-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K50" s="4" t="str">
-        <f>IF(入力!$B46="","",IF(ISNUMBER(入力!$P46),入力!$P46,""))</f>
+        <f>IF(入力!$B37="","",IF(ISNUMBER(入力!$P37),入力!$P37,""))</f>
         <v/>
       </c>
       <c r="L50" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D46),ISNUMBER(入力!$P46)),入力!$D46*入力!$P46,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D37),ISNUMBER(入力!$P37)),入力!$D37*入力!$P37,"")</f>
         <v/>
       </c>
       <c r="M50" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D46),ISNUMBER(入力!$P46)),MAX(0,入力!$D46-入力!$C$5)*入力!$P46,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D37),ISNUMBER(入力!$P37)),MAX(0,入力!$D37-入力!$C$5)*入力!$P37,"")</f>
         <v/>
       </c>
       <c r="N50" s="4" t="str">
@@ -25842,37 +25416,37 @@
         <v/>
       </c>
       <c r="O50" s="5" t="str">
-        <f>IF(入力!$B46="","",IF(AND(NOT(ISNUMBER(G50)),NOT(ISNUMBER(M50))),"",IF(ISNUMBER(G50),G50,0)+IF(ISNUMBER(M50),M50,0)))</f>
+        <f>IF(入力!$B37="","",IF(AND(NOT(ISNUMBER(G50)),NOT(ISNUMBER(M50))),"",IF(ISNUMBER(G50),G50,0)+IF(ISNUMBER(M50),M50,0)))</f>
         <v/>
       </c>
       <c r="P50" s="4" t="str">
-        <f>IF(入力!$B46="","",IF(AND(NOT(ISNUMBER(H50)),NOT(ISNUMBER(N50))),"",IF(ISNUMBER(H50),H50,0)+IF(ISNUMBER(N50),N50,0)))</f>
+        <f>IF(入力!$B37="","",IF(AND(NOT(ISNUMBER(H50)),NOT(ISNUMBER(N50))),"",IF(ISNUMBER(H50),H50,0)+IF(ISNUMBER(N50),N50,0)))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="7" t="str">
-        <f>IF(入力!$B47="","",入力!$B47)</f>
+        <f>IF(入力!$B38="","",入力!$B38)</f>
         <v/>
       </c>
       <c r="C51" s="5" t="str">
-        <f>IF(入力!$B47="","",IF(ISNUMBER(入力!$C47),入力!$C47,""))</f>
+        <f>IF(入力!$B38="","",IF(ISNUMBER(入力!$C38),入力!$C38,""))</f>
         <v/>
       </c>
       <c r="D51" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C47),MAX(0,入力!$C47-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C38),MAX(0,入力!$C38-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E51" s="4" t="str">
-        <f>IF(入力!$B47="","",IF(ISNUMBER(入力!$O47),入力!$O47,""))</f>
+        <f>IF(入力!$B38="","",IF(ISNUMBER(入力!$O38),入力!$O38,""))</f>
         <v/>
       </c>
       <c r="F51" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C47),ISNUMBER(入力!$O47)),入力!$C47*入力!$O47,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C38),ISNUMBER(入力!$O38)),入力!$C38*入力!$O38,"")</f>
         <v/>
       </c>
       <c r="G51" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C47),ISNUMBER(入力!$O47)),MAX(0,入力!$C47-入力!$B$5)*入力!$O47,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C38),ISNUMBER(入力!$O38)),MAX(0,入力!$C38-入力!$B$5)*入力!$O38,"")</f>
         <v/>
       </c>
       <c r="H51" s="4" t="str">
@@ -25880,23 +25454,23 @@
         <v/>
       </c>
       <c r="I51" s="5" t="str">
-        <f>IF(入力!$B47="","",IF(ISNUMBER(入力!$D47),入力!$D47,""))</f>
+        <f>IF(入力!$B38="","",IF(ISNUMBER(入力!$D38),入力!$D38,""))</f>
         <v/>
       </c>
       <c r="J51" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D47),MAX(0,入力!$D47-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D38),MAX(0,入力!$D38-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K51" s="4" t="str">
-        <f>IF(入力!$B47="","",IF(ISNUMBER(入力!$P47),入力!$P47,""))</f>
+        <f>IF(入力!$B38="","",IF(ISNUMBER(入力!$P38),入力!$P38,""))</f>
         <v/>
       </c>
       <c r="L51" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D47),ISNUMBER(入力!$P47)),入力!$D47*入力!$P47,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D38),ISNUMBER(入力!$P38)),入力!$D38*入力!$P38,"")</f>
         <v/>
       </c>
       <c r="M51" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D47),ISNUMBER(入力!$P47)),MAX(0,入力!$D47-入力!$C$5)*入力!$P47,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D38),ISNUMBER(入力!$P38)),MAX(0,入力!$D38-入力!$C$5)*入力!$P38,"")</f>
         <v/>
       </c>
       <c r="N51" s="4" t="str">
@@ -25904,37 +25478,37 @@
         <v/>
       </c>
       <c r="O51" s="5" t="str">
-        <f>IF(入力!$B47="","",IF(AND(NOT(ISNUMBER(G51)),NOT(ISNUMBER(M51))),"",IF(ISNUMBER(G51),G51,0)+IF(ISNUMBER(M51),M51,0)))</f>
+        <f>IF(入力!$B38="","",IF(AND(NOT(ISNUMBER(G51)),NOT(ISNUMBER(M51))),"",IF(ISNUMBER(G51),G51,0)+IF(ISNUMBER(M51),M51,0)))</f>
         <v/>
       </c>
       <c r="P51" s="4" t="str">
-        <f>IF(入力!$B47="","",IF(AND(NOT(ISNUMBER(H51)),NOT(ISNUMBER(N51))),"",IF(ISNUMBER(H51),H51,0)+IF(ISNUMBER(N51),N51,0)))</f>
+        <f>IF(入力!$B38="","",IF(AND(NOT(ISNUMBER(H51)),NOT(ISNUMBER(N51))),"",IF(ISNUMBER(H51),H51,0)+IF(ISNUMBER(N51),N51,0)))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="7" t="str">
-        <f>IF(入力!$B48="","",入力!$B48)</f>
+        <f>IF(入力!$B39="","",入力!$B39)</f>
         <v/>
       </c>
       <c r="C52" s="5" t="str">
-        <f>IF(入力!$B48="","",IF(ISNUMBER(入力!$C48),入力!$C48,""))</f>
+        <f>IF(入力!$B39="","",IF(ISNUMBER(入力!$C39),入力!$C39,""))</f>
         <v/>
       </c>
       <c r="D52" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C48),MAX(0,入力!$C48-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C39),MAX(0,入力!$C39-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E52" s="4" t="str">
-        <f>IF(入力!$B48="","",IF(ISNUMBER(入力!$O48),入力!$O48,""))</f>
+        <f>IF(入力!$B39="","",IF(ISNUMBER(入力!$O39),入力!$O39,""))</f>
         <v/>
       </c>
       <c r="F52" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C48),ISNUMBER(入力!$O48)),入力!$C48*入力!$O48,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C39),ISNUMBER(入力!$O39)),入力!$C39*入力!$O39,"")</f>
         <v/>
       </c>
       <c r="G52" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C48),ISNUMBER(入力!$O48)),MAX(0,入力!$C48-入力!$B$5)*入力!$O48,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C39),ISNUMBER(入力!$O39)),MAX(0,入力!$C39-入力!$B$5)*入力!$O39,"")</f>
         <v/>
       </c>
       <c r="H52" s="4" t="str">
@@ -25942,23 +25516,23 @@
         <v/>
       </c>
       <c r="I52" s="5" t="str">
-        <f>IF(入力!$B48="","",IF(ISNUMBER(入力!$D48),入力!$D48,""))</f>
+        <f>IF(入力!$B39="","",IF(ISNUMBER(入力!$D39),入力!$D39,""))</f>
         <v/>
       </c>
       <c r="J52" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D48),MAX(0,入力!$D48-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D39),MAX(0,入力!$D39-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K52" s="4" t="str">
-        <f>IF(入力!$B48="","",IF(ISNUMBER(入力!$P48),入力!$P48,""))</f>
+        <f>IF(入力!$B39="","",IF(ISNUMBER(入力!$P39),入力!$P39,""))</f>
         <v/>
       </c>
       <c r="L52" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D48),ISNUMBER(入力!$P48)),入力!$D48*入力!$P48,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D39),ISNUMBER(入力!$P39)),入力!$D39*入力!$P39,"")</f>
         <v/>
       </c>
       <c r="M52" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D48),ISNUMBER(入力!$P48)),MAX(0,入力!$D48-入力!$C$5)*入力!$P48,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D39),ISNUMBER(入力!$P39)),MAX(0,入力!$D39-入力!$C$5)*入力!$P39,"")</f>
         <v/>
       </c>
       <c r="N52" s="4" t="str">
@@ -25966,37 +25540,37 @@
         <v/>
       </c>
       <c r="O52" s="5" t="str">
-        <f>IF(入力!$B48="","",IF(AND(NOT(ISNUMBER(G52)),NOT(ISNUMBER(M52))),"",IF(ISNUMBER(G52),G52,0)+IF(ISNUMBER(M52),M52,0)))</f>
+        <f>IF(入力!$B39="","",IF(AND(NOT(ISNUMBER(G52)),NOT(ISNUMBER(M52))),"",IF(ISNUMBER(G52),G52,0)+IF(ISNUMBER(M52),M52,0)))</f>
         <v/>
       </c>
       <c r="P52" s="4" t="str">
-        <f>IF(入力!$B48="","",IF(AND(NOT(ISNUMBER(H52)),NOT(ISNUMBER(N52))),"",IF(ISNUMBER(H52),H52,0)+IF(ISNUMBER(N52),N52,0)))</f>
+        <f>IF(入力!$B39="","",IF(AND(NOT(ISNUMBER(H52)),NOT(ISNUMBER(N52))),"",IF(ISNUMBER(H52),H52,0)+IF(ISNUMBER(N52),N52,0)))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="7" t="str">
-        <f>IF(入力!$B49="","",入力!$B49)</f>
+        <f>IF(入力!$B40="","",入力!$B40)</f>
         <v/>
       </c>
       <c r="C53" s="5" t="str">
-        <f>IF(入力!$B49="","",IF(ISNUMBER(入力!$C49),入力!$C49,""))</f>
+        <f>IF(入力!$B40="","",IF(ISNUMBER(入力!$C40),入力!$C40,""))</f>
         <v/>
       </c>
       <c r="D53" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C49),MAX(0,入力!$C49-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C40),MAX(0,入力!$C40-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E53" s="4" t="str">
-        <f>IF(入力!$B49="","",IF(ISNUMBER(入力!$O49),入力!$O49,""))</f>
+        <f>IF(入力!$B40="","",IF(ISNUMBER(入力!$O40),入力!$O40,""))</f>
         <v/>
       </c>
       <c r="F53" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C49),ISNUMBER(入力!$O49)),入力!$C49*入力!$O49,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C40),ISNUMBER(入力!$O40)),入力!$C40*入力!$O40,"")</f>
         <v/>
       </c>
       <c r="G53" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C49),ISNUMBER(入力!$O49)),MAX(0,入力!$C49-入力!$B$5)*入力!$O49,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C40),ISNUMBER(入力!$O40)),MAX(0,入力!$C40-入力!$B$5)*入力!$O40,"")</f>
         <v/>
       </c>
       <c r="H53" s="4" t="str">
@@ -26004,23 +25578,23 @@
         <v/>
       </c>
       <c r="I53" s="5" t="str">
-        <f>IF(入力!$B49="","",IF(ISNUMBER(入力!$D49),入力!$D49,""))</f>
+        <f>IF(入力!$B40="","",IF(ISNUMBER(入力!$D40),入力!$D40,""))</f>
         <v/>
       </c>
       <c r="J53" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D49),MAX(0,入力!$D49-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D40),MAX(0,入力!$D40-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K53" s="4" t="str">
-        <f>IF(入力!$B49="","",IF(ISNUMBER(入力!$P49),入力!$P49,""))</f>
+        <f>IF(入力!$B40="","",IF(ISNUMBER(入力!$P40),入力!$P40,""))</f>
         <v/>
       </c>
       <c r="L53" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D49),ISNUMBER(入力!$P49)),入力!$D49*入力!$P49,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D40),ISNUMBER(入力!$P40)),入力!$D40*入力!$P40,"")</f>
         <v/>
       </c>
       <c r="M53" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D49),ISNUMBER(入力!$P49)),MAX(0,入力!$D49-入力!$C$5)*入力!$P49,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D40),ISNUMBER(入力!$P40)),MAX(0,入力!$D40-入力!$C$5)*入力!$P40,"")</f>
         <v/>
       </c>
       <c r="N53" s="4" t="str">
@@ -26028,37 +25602,37 @@
         <v/>
       </c>
       <c r="O53" s="5" t="str">
-        <f>IF(入力!$B49="","",IF(AND(NOT(ISNUMBER(G53)),NOT(ISNUMBER(M53))),"",IF(ISNUMBER(G53),G53,0)+IF(ISNUMBER(M53),M53,0)))</f>
+        <f>IF(入力!$B40="","",IF(AND(NOT(ISNUMBER(G53)),NOT(ISNUMBER(M53))),"",IF(ISNUMBER(G53),G53,0)+IF(ISNUMBER(M53),M53,0)))</f>
         <v/>
       </c>
       <c r="P53" s="4" t="str">
-        <f>IF(入力!$B49="","",IF(AND(NOT(ISNUMBER(H53)),NOT(ISNUMBER(N53))),"",IF(ISNUMBER(H53),H53,0)+IF(ISNUMBER(N53),N53,0)))</f>
+        <f>IF(入力!$B40="","",IF(AND(NOT(ISNUMBER(H53)),NOT(ISNUMBER(N53))),"",IF(ISNUMBER(H53),H53,0)+IF(ISNUMBER(N53),N53,0)))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="7" t="str">
-        <f>IF(入力!$B50="","",入力!$B50)</f>
+        <f>IF(入力!$B41="","",入力!$B41)</f>
         <v/>
       </c>
       <c r="C54" s="5" t="str">
-        <f>IF(入力!$B50="","",IF(ISNUMBER(入力!$C50),入力!$C50,""))</f>
+        <f>IF(入力!$B41="","",IF(ISNUMBER(入力!$C41),入力!$C41,""))</f>
         <v/>
       </c>
       <c r="D54" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C50),MAX(0,入力!$C50-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C41),MAX(0,入力!$C41-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E54" s="4" t="str">
-        <f>IF(入力!$B50="","",IF(ISNUMBER(入力!$O50),入力!$O50,""))</f>
+        <f>IF(入力!$B41="","",IF(ISNUMBER(入力!$O41),入力!$O41,""))</f>
         <v/>
       </c>
       <c r="F54" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C50),ISNUMBER(入力!$O50)),入力!$C50*入力!$O50,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C41),ISNUMBER(入力!$O41)),入力!$C41*入力!$O41,"")</f>
         <v/>
       </c>
       <c r="G54" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C50),ISNUMBER(入力!$O50)),MAX(0,入力!$C50-入力!$B$5)*入力!$O50,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C41),ISNUMBER(入力!$O41)),MAX(0,入力!$C41-入力!$B$5)*入力!$O41,"")</f>
         <v/>
       </c>
       <c r="H54" s="4" t="str">
@@ -26066,23 +25640,23 @@
         <v/>
       </c>
       <c r="I54" s="5" t="str">
-        <f>IF(入力!$B50="","",IF(ISNUMBER(入力!$D50),入力!$D50,""))</f>
+        <f>IF(入力!$B41="","",IF(ISNUMBER(入力!$D41),入力!$D41,""))</f>
         <v/>
       </c>
       <c r="J54" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D50),MAX(0,入力!$D50-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D41),MAX(0,入力!$D41-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K54" s="4" t="str">
-        <f>IF(入力!$B50="","",IF(ISNUMBER(入力!$P50),入力!$P50,""))</f>
+        <f>IF(入力!$B41="","",IF(ISNUMBER(入力!$P41),入力!$P41,""))</f>
         <v/>
       </c>
       <c r="L54" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D50),ISNUMBER(入力!$P50)),入力!$D50*入力!$P50,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D41),ISNUMBER(入力!$P41)),入力!$D41*入力!$P41,"")</f>
         <v/>
       </c>
       <c r="M54" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D50),ISNUMBER(入力!$P50)),MAX(0,入力!$D50-入力!$C$5)*入力!$P50,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D41),ISNUMBER(入力!$P41)),MAX(0,入力!$D41-入力!$C$5)*入力!$P41,"")</f>
         <v/>
       </c>
       <c r="N54" s="4" t="str">
@@ -26090,37 +25664,37 @@
         <v/>
       </c>
       <c r="O54" s="5" t="str">
-        <f>IF(入力!$B50="","",IF(AND(NOT(ISNUMBER(G54)),NOT(ISNUMBER(M54))),"",IF(ISNUMBER(G54),G54,0)+IF(ISNUMBER(M54),M54,0)))</f>
+        <f>IF(入力!$B41="","",IF(AND(NOT(ISNUMBER(G54)),NOT(ISNUMBER(M54))),"",IF(ISNUMBER(G54),G54,0)+IF(ISNUMBER(M54),M54,0)))</f>
         <v/>
       </c>
       <c r="P54" s="4" t="str">
-        <f>IF(入力!$B50="","",IF(AND(NOT(ISNUMBER(H54)),NOT(ISNUMBER(N54))),"",IF(ISNUMBER(H54),H54,0)+IF(ISNUMBER(N54),N54,0)))</f>
+        <f>IF(入力!$B41="","",IF(AND(NOT(ISNUMBER(H54)),NOT(ISNUMBER(N54))),"",IF(ISNUMBER(H54),H54,0)+IF(ISNUMBER(N54),N54,0)))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="7" t="str">
-        <f>IF(入力!$B51="","",入力!$B51)</f>
+        <f>IF(入力!$B42="","",入力!$B42)</f>
         <v/>
       </c>
       <c r="C55" s="5" t="str">
-        <f>IF(入力!$B51="","",IF(ISNUMBER(入力!$C51),入力!$C51,""))</f>
+        <f>IF(入力!$B42="","",IF(ISNUMBER(入力!$C42),入力!$C42,""))</f>
         <v/>
       </c>
       <c r="D55" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C51),MAX(0,入力!$C51-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C42),MAX(0,入力!$C42-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E55" s="4" t="str">
-        <f>IF(入力!$B51="","",IF(ISNUMBER(入力!$O51),入力!$O51,""))</f>
+        <f>IF(入力!$B42="","",IF(ISNUMBER(入力!$O42),入力!$O42,""))</f>
         <v/>
       </c>
       <c r="F55" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C51),ISNUMBER(入力!$O51)),入力!$C51*入力!$O51,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C42),ISNUMBER(入力!$O42)),入力!$C42*入力!$O42,"")</f>
         <v/>
       </c>
       <c r="G55" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C51),ISNUMBER(入力!$O51)),MAX(0,入力!$C51-入力!$B$5)*入力!$O51,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C42),ISNUMBER(入力!$O42)),MAX(0,入力!$C42-入力!$B$5)*入力!$O42,"")</f>
         <v/>
       </c>
       <c r="H55" s="4" t="str">
@@ -26128,23 +25702,23 @@
         <v/>
       </c>
       <c r="I55" s="5" t="str">
-        <f>IF(入力!$B51="","",IF(ISNUMBER(入力!$D51),入力!$D51,""))</f>
+        <f>IF(入力!$B42="","",IF(ISNUMBER(入力!$D42),入力!$D42,""))</f>
         <v/>
       </c>
       <c r="J55" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D51),MAX(0,入力!$D51-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D42),MAX(0,入力!$D42-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K55" s="4" t="str">
-        <f>IF(入力!$B51="","",IF(ISNUMBER(入力!$P51),入力!$P51,""))</f>
+        <f>IF(入力!$B42="","",IF(ISNUMBER(入力!$P42),入力!$P42,""))</f>
         <v/>
       </c>
       <c r="L55" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D51),ISNUMBER(入力!$P51)),入力!$D51*入力!$P51,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D42),ISNUMBER(入力!$P42)),入力!$D42*入力!$P42,"")</f>
         <v/>
       </c>
       <c r="M55" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D51),ISNUMBER(入力!$P51)),MAX(0,入力!$D51-入力!$C$5)*入力!$P51,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D42),ISNUMBER(入力!$P42)),MAX(0,入力!$D42-入力!$C$5)*入力!$P42,"")</f>
         <v/>
       </c>
       <c r="N55" s="4" t="str">
@@ -26152,37 +25726,37 @@
         <v/>
       </c>
       <c r="O55" s="5" t="str">
-        <f>IF(入力!$B51="","",IF(AND(NOT(ISNUMBER(G55)),NOT(ISNUMBER(M55))),"",IF(ISNUMBER(G55),G55,0)+IF(ISNUMBER(M55),M55,0)))</f>
+        <f>IF(入力!$B42="","",IF(AND(NOT(ISNUMBER(G55)),NOT(ISNUMBER(M55))),"",IF(ISNUMBER(G55),G55,0)+IF(ISNUMBER(M55),M55,0)))</f>
         <v/>
       </c>
       <c r="P55" s="4" t="str">
-        <f>IF(入力!$B51="","",IF(AND(NOT(ISNUMBER(H55)),NOT(ISNUMBER(N55))),"",IF(ISNUMBER(H55),H55,0)+IF(ISNUMBER(N55),N55,0)))</f>
+        <f>IF(入力!$B42="","",IF(AND(NOT(ISNUMBER(H55)),NOT(ISNUMBER(N55))),"",IF(ISNUMBER(H55),H55,0)+IF(ISNUMBER(N55),N55,0)))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="7" t="str">
-        <f>IF(入力!$B52="","",入力!$B52)</f>
+        <f>IF(入力!$B43="","",入力!$B43)</f>
         <v/>
       </c>
       <c r="C56" s="5" t="str">
-        <f>IF(入力!$B52="","",IF(ISNUMBER(入力!$C52),入力!$C52,""))</f>
+        <f>IF(入力!$B43="","",IF(ISNUMBER(入力!$C43),入力!$C43,""))</f>
         <v/>
       </c>
       <c r="D56" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C52),MAX(0,入力!$C52-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C43),MAX(0,入力!$C43-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E56" s="4" t="str">
-        <f>IF(入力!$B52="","",IF(ISNUMBER(入力!$O52),入力!$O52,""))</f>
+        <f>IF(入力!$B43="","",IF(ISNUMBER(入力!$O43),入力!$O43,""))</f>
         <v/>
       </c>
       <c r="F56" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C52),ISNUMBER(入力!$O52)),入力!$C52*入力!$O52,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C43),ISNUMBER(入力!$O43)),入力!$C43*入力!$O43,"")</f>
         <v/>
       </c>
       <c r="G56" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C52),ISNUMBER(入力!$O52)),MAX(0,入力!$C52-入力!$B$5)*入力!$O52,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C43),ISNUMBER(入力!$O43)),MAX(0,入力!$C43-入力!$B$5)*入力!$O43,"")</f>
         <v/>
       </c>
       <c r="H56" s="4" t="str">
@@ -26190,23 +25764,23 @@
         <v/>
       </c>
       <c r="I56" s="5" t="str">
-        <f>IF(入力!$B52="","",IF(ISNUMBER(入力!$D52),入力!$D52,""))</f>
+        <f>IF(入力!$B43="","",IF(ISNUMBER(入力!$D43),入力!$D43,""))</f>
         <v/>
       </c>
       <c r="J56" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D52),MAX(0,入力!$D52-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D43),MAX(0,入力!$D43-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K56" s="4" t="str">
-        <f>IF(入力!$B52="","",IF(ISNUMBER(入力!$P52),入力!$P52,""))</f>
+        <f>IF(入力!$B43="","",IF(ISNUMBER(入力!$P43),入力!$P43,""))</f>
         <v/>
       </c>
       <c r="L56" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D52),ISNUMBER(入力!$P52)),入力!$D52*入力!$P52,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D43),ISNUMBER(入力!$P43)),入力!$D43*入力!$P43,"")</f>
         <v/>
       </c>
       <c r="M56" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D52),ISNUMBER(入力!$P52)),MAX(0,入力!$D52-入力!$C$5)*入力!$P52,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D43),ISNUMBER(入力!$P43)),MAX(0,入力!$D43-入力!$C$5)*入力!$P43,"")</f>
         <v/>
       </c>
       <c r="N56" s="4" t="str">
@@ -26214,37 +25788,37 @@
         <v/>
       </c>
       <c r="O56" s="5" t="str">
-        <f>IF(入力!$B52="","",IF(AND(NOT(ISNUMBER(G56)),NOT(ISNUMBER(M56))),"",IF(ISNUMBER(G56),G56,0)+IF(ISNUMBER(M56),M56,0)))</f>
+        <f>IF(入力!$B43="","",IF(AND(NOT(ISNUMBER(G56)),NOT(ISNUMBER(M56))),"",IF(ISNUMBER(G56),G56,0)+IF(ISNUMBER(M56),M56,0)))</f>
         <v/>
       </c>
       <c r="P56" s="4" t="str">
-        <f>IF(入力!$B52="","",IF(AND(NOT(ISNUMBER(H56)),NOT(ISNUMBER(N56))),"",IF(ISNUMBER(H56),H56,0)+IF(ISNUMBER(N56),N56,0)))</f>
+        <f>IF(入力!$B43="","",IF(AND(NOT(ISNUMBER(H56)),NOT(ISNUMBER(N56))),"",IF(ISNUMBER(H56),H56,0)+IF(ISNUMBER(N56),N56,0)))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="7" t="str">
-        <f>IF(入力!$B53="","",入力!$B53)</f>
+        <f>IF(入力!$B44="","",入力!$B44)</f>
         <v/>
       </c>
       <c r="C57" s="5" t="str">
-        <f>IF(入力!$B53="","",IF(ISNUMBER(入力!$C53),入力!$C53,""))</f>
+        <f>IF(入力!$B44="","",IF(ISNUMBER(入力!$C44),入力!$C44,""))</f>
         <v/>
       </c>
       <c r="D57" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C53),MAX(0,入力!$C53-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C44),MAX(0,入力!$C44-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E57" s="4" t="str">
-        <f>IF(入力!$B53="","",IF(ISNUMBER(入力!$O53),入力!$O53,""))</f>
+        <f>IF(入力!$B44="","",IF(ISNUMBER(入力!$O44),入力!$O44,""))</f>
         <v/>
       </c>
       <c r="F57" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C53),ISNUMBER(入力!$O53)),入力!$C53*入力!$O53,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C44),ISNUMBER(入力!$O44)),入力!$C44*入力!$O44,"")</f>
         <v/>
       </c>
       <c r="G57" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C53),ISNUMBER(入力!$O53)),MAX(0,入力!$C53-入力!$B$5)*入力!$O53,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C44),ISNUMBER(入力!$O44)),MAX(0,入力!$C44-入力!$B$5)*入力!$O44,"")</f>
         <v/>
       </c>
       <c r="H57" s="4" t="str">
@@ -26252,23 +25826,23 @@
         <v/>
       </c>
       <c r="I57" s="5" t="str">
-        <f>IF(入力!$B53="","",IF(ISNUMBER(入力!$D53),入力!$D53,""))</f>
+        <f>IF(入力!$B44="","",IF(ISNUMBER(入力!$D44),入力!$D44,""))</f>
         <v/>
       </c>
       <c r="J57" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D53),MAX(0,入力!$D53-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D44),MAX(0,入力!$D44-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K57" s="4" t="str">
-        <f>IF(入力!$B53="","",IF(ISNUMBER(入力!$P53),入力!$P53,""))</f>
+        <f>IF(入力!$B44="","",IF(ISNUMBER(入力!$P44),入力!$P44,""))</f>
         <v/>
       </c>
       <c r="L57" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D53),ISNUMBER(入力!$P53)),入力!$D53*入力!$P53,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D44),ISNUMBER(入力!$P44)),入力!$D44*入力!$P44,"")</f>
         <v/>
       </c>
       <c r="M57" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D53),ISNUMBER(入力!$P53)),MAX(0,入力!$D53-入力!$C$5)*入力!$P53,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D44),ISNUMBER(入力!$P44)),MAX(0,入力!$D44-入力!$C$5)*入力!$P44,"")</f>
         <v/>
       </c>
       <c r="N57" s="4" t="str">
@@ -26276,37 +25850,37 @@
         <v/>
       </c>
       <c r="O57" s="5" t="str">
-        <f>IF(入力!$B53="","",IF(AND(NOT(ISNUMBER(G57)),NOT(ISNUMBER(M57))),"",IF(ISNUMBER(G57),G57,0)+IF(ISNUMBER(M57),M57,0)))</f>
+        <f>IF(入力!$B44="","",IF(AND(NOT(ISNUMBER(G57)),NOT(ISNUMBER(M57))),"",IF(ISNUMBER(G57),G57,0)+IF(ISNUMBER(M57),M57,0)))</f>
         <v/>
       </c>
       <c r="P57" s="4" t="str">
-        <f>IF(入力!$B53="","",IF(AND(NOT(ISNUMBER(H57)),NOT(ISNUMBER(N57))),"",IF(ISNUMBER(H57),H57,0)+IF(ISNUMBER(N57),N57,0)))</f>
+        <f>IF(入力!$B44="","",IF(AND(NOT(ISNUMBER(H57)),NOT(ISNUMBER(N57))),"",IF(ISNUMBER(H57),H57,0)+IF(ISNUMBER(N57),N57,0)))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="7" t="str">
-        <f>IF(入力!$B54="","",入力!$B54)</f>
+        <f>IF(入力!$B45="","",入力!$B45)</f>
         <v/>
       </c>
       <c r="C58" s="5" t="str">
-        <f>IF(入力!$B54="","",IF(ISNUMBER(入力!$C54),入力!$C54,""))</f>
+        <f>IF(入力!$B45="","",IF(ISNUMBER(入力!$C45),入力!$C45,""))</f>
         <v/>
       </c>
       <c r="D58" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C54),MAX(0,入力!$C54-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C45),MAX(0,入力!$C45-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E58" s="4" t="str">
-        <f>IF(入力!$B54="","",IF(ISNUMBER(入力!$O54),入力!$O54,""))</f>
+        <f>IF(入力!$B45="","",IF(ISNUMBER(入力!$O45),入力!$O45,""))</f>
         <v/>
       </c>
       <c r="F58" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C54),ISNUMBER(入力!$O54)),入力!$C54*入力!$O54,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C45),ISNUMBER(入力!$O45)),入力!$C45*入力!$O45,"")</f>
         <v/>
       </c>
       <c r="G58" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C54),ISNUMBER(入力!$O54)),MAX(0,入力!$C54-入力!$B$5)*入力!$O54,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C45),ISNUMBER(入力!$O45)),MAX(0,入力!$C45-入力!$B$5)*入力!$O45,"")</f>
         <v/>
       </c>
       <c r="H58" s="4" t="str">
@@ -26314,23 +25888,23 @@
         <v/>
       </c>
       <c r="I58" s="5" t="str">
-        <f>IF(入力!$B54="","",IF(ISNUMBER(入力!$D54),入力!$D54,""))</f>
+        <f>IF(入力!$B45="","",IF(ISNUMBER(入力!$D45),入力!$D45,""))</f>
         <v/>
       </c>
       <c r="J58" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D54),MAX(0,入力!$D54-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D45),MAX(0,入力!$D45-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K58" s="4" t="str">
-        <f>IF(入力!$B54="","",IF(ISNUMBER(入力!$P54),入力!$P54,""))</f>
+        <f>IF(入力!$B45="","",IF(ISNUMBER(入力!$P45),入力!$P45,""))</f>
         <v/>
       </c>
       <c r="L58" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D54),ISNUMBER(入力!$P54)),入力!$D54*入力!$P54,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D45),ISNUMBER(入力!$P45)),入力!$D45*入力!$P45,"")</f>
         <v/>
       </c>
       <c r="M58" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D54),ISNUMBER(入力!$P54)),MAX(0,入力!$D54-入力!$C$5)*入力!$P54,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D45),ISNUMBER(入力!$P45)),MAX(0,入力!$D45-入力!$C$5)*入力!$P45,"")</f>
         <v/>
       </c>
       <c r="N58" s="4" t="str">
@@ -26338,37 +25912,37 @@
         <v/>
       </c>
       <c r="O58" s="5" t="str">
-        <f>IF(入力!$B54="","",IF(AND(NOT(ISNUMBER(G58)),NOT(ISNUMBER(M58))),"",IF(ISNUMBER(G58),G58,0)+IF(ISNUMBER(M58),M58,0)))</f>
+        <f>IF(入力!$B45="","",IF(AND(NOT(ISNUMBER(G58)),NOT(ISNUMBER(M58))),"",IF(ISNUMBER(G58),G58,0)+IF(ISNUMBER(M58),M58,0)))</f>
         <v/>
       </c>
       <c r="P58" s="4" t="str">
-        <f>IF(入力!$B54="","",IF(AND(NOT(ISNUMBER(H58)),NOT(ISNUMBER(N58))),"",IF(ISNUMBER(H58),H58,0)+IF(ISNUMBER(N58),N58,0)))</f>
+        <f>IF(入力!$B45="","",IF(AND(NOT(ISNUMBER(H58)),NOT(ISNUMBER(N58))),"",IF(ISNUMBER(H58),H58,0)+IF(ISNUMBER(N58),N58,0)))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="7" t="str">
-        <f>IF(入力!$B55="","",入力!$B55)</f>
+        <f>IF(入力!$B46="","",入力!$B46)</f>
         <v/>
       </c>
       <c r="C59" s="5" t="str">
-        <f>IF(入力!$B55="","",IF(ISNUMBER(入力!$C55),入力!$C55,""))</f>
+        <f>IF(入力!$B46="","",IF(ISNUMBER(入力!$C46),入力!$C46,""))</f>
         <v/>
       </c>
       <c r="D59" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C55),MAX(0,入力!$C55-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C46),MAX(0,入力!$C46-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E59" s="4" t="str">
-        <f>IF(入力!$B55="","",IF(ISNUMBER(入力!$O55),入力!$O55,""))</f>
+        <f>IF(入力!$B46="","",IF(ISNUMBER(入力!$O46),入力!$O46,""))</f>
         <v/>
       </c>
       <c r="F59" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C55),ISNUMBER(入力!$O55)),入力!$C55*入力!$O55,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C46),ISNUMBER(入力!$O46)),入力!$C46*入力!$O46,"")</f>
         <v/>
       </c>
       <c r="G59" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C55),ISNUMBER(入力!$O55)),MAX(0,入力!$C55-入力!$B$5)*入力!$O55,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C46),ISNUMBER(入力!$O46)),MAX(0,入力!$C46-入力!$B$5)*入力!$O46,"")</f>
         <v/>
       </c>
       <c r="H59" s="4" t="str">
@@ -26376,23 +25950,23 @@
         <v/>
       </c>
       <c r="I59" s="5" t="str">
-        <f>IF(入力!$B55="","",IF(ISNUMBER(入力!$D55),入力!$D55,""))</f>
+        <f>IF(入力!$B46="","",IF(ISNUMBER(入力!$D46),入力!$D46,""))</f>
         <v/>
       </c>
       <c r="J59" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D55),MAX(0,入力!$D55-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D46),MAX(0,入力!$D46-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K59" s="4" t="str">
-        <f>IF(入力!$B55="","",IF(ISNUMBER(入力!$P55),入力!$P55,""))</f>
+        <f>IF(入力!$B46="","",IF(ISNUMBER(入力!$P46),入力!$P46,""))</f>
         <v/>
       </c>
       <c r="L59" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D55),ISNUMBER(入力!$P55)),入力!$D55*入力!$P55,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D46),ISNUMBER(入力!$P46)),入力!$D46*入力!$P46,"")</f>
         <v/>
       </c>
       <c r="M59" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D55),ISNUMBER(入力!$P55)),MAX(0,入力!$D55-入力!$C$5)*入力!$P55,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D46),ISNUMBER(入力!$P46)),MAX(0,入力!$D46-入力!$C$5)*入力!$P46,"")</f>
         <v/>
       </c>
       <c r="N59" s="4" t="str">
@@ -26400,37 +25974,37 @@
         <v/>
       </c>
       <c r="O59" s="5" t="str">
-        <f>IF(入力!$B55="","",IF(AND(NOT(ISNUMBER(G59)),NOT(ISNUMBER(M59))),"",IF(ISNUMBER(G59),G59,0)+IF(ISNUMBER(M59),M59,0)))</f>
+        <f>IF(入力!$B46="","",IF(AND(NOT(ISNUMBER(G59)),NOT(ISNUMBER(M59))),"",IF(ISNUMBER(G59),G59,0)+IF(ISNUMBER(M59),M59,0)))</f>
         <v/>
       </c>
       <c r="P59" s="4" t="str">
-        <f>IF(入力!$B55="","",IF(AND(NOT(ISNUMBER(H59)),NOT(ISNUMBER(N59))),"",IF(ISNUMBER(H59),H59,0)+IF(ISNUMBER(N59),N59,0)))</f>
+        <f>IF(入力!$B46="","",IF(AND(NOT(ISNUMBER(H59)),NOT(ISNUMBER(N59))),"",IF(ISNUMBER(H59),H59,0)+IF(ISNUMBER(N59),N59,0)))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="7" t="str">
-        <f>IF(入力!$B56="","",入力!$B56)</f>
+        <f>IF(入力!$B47="","",入力!$B47)</f>
         <v/>
       </c>
       <c r="C60" s="5" t="str">
-        <f>IF(入力!$B56="","",IF(ISNUMBER(入力!$C56),入力!$C56,""))</f>
+        <f>IF(入力!$B47="","",IF(ISNUMBER(入力!$C47),入力!$C47,""))</f>
         <v/>
       </c>
       <c r="D60" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C56),MAX(0,入力!$C56-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C47),MAX(0,入力!$C47-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E60" s="4" t="str">
-        <f>IF(入力!$B56="","",IF(ISNUMBER(入力!$O56),入力!$O56,""))</f>
+        <f>IF(入力!$B47="","",IF(ISNUMBER(入力!$O47),入力!$O47,""))</f>
         <v/>
       </c>
       <c r="F60" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C56),ISNUMBER(入力!$O56)),入力!$C56*入力!$O56,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C47),ISNUMBER(入力!$O47)),入力!$C47*入力!$O47,"")</f>
         <v/>
       </c>
       <c r="G60" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C56),ISNUMBER(入力!$O56)),MAX(0,入力!$C56-入力!$B$5)*入力!$O56,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C47),ISNUMBER(入力!$O47)),MAX(0,入力!$C47-入力!$B$5)*入力!$O47,"")</f>
         <v/>
       </c>
       <c r="H60" s="4" t="str">
@@ -26438,23 +26012,23 @@
         <v/>
       </c>
       <c r="I60" s="5" t="str">
-        <f>IF(入力!$B56="","",IF(ISNUMBER(入力!$D56),入力!$D56,""))</f>
+        <f>IF(入力!$B47="","",IF(ISNUMBER(入力!$D47),入力!$D47,""))</f>
         <v/>
       </c>
       <c r="J60" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D56),MAX(0,入力!$D56-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D47),MAX(0,入力!$D47-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K60" s="4" t="str">
-        <f>IF(入力!$B56="","",IF(ISNUMBER(入力!$P56),入力!$P56,""))</f>
+        <f>IF(入力!$B47="","",IF(ISNUMBER(入力!$P47),入力!$P47,""))</f>
         <v/>
       </c>
       <c r="L60" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D56),ISNUMBER(入力!$P56)),入力!$D56*入力!$P56,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D47),ISNUMBER(入力!$P47)),入力!$D47*入力!$P47,"")</f>
         <v/>
       </c>
       <c r="M60" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D56),ISNUMBER(入力!$P56)),MAX(0,入力!$D56-入力!$C$5)*入力!$P56,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D47),ISNUMBER(入力!$P47)),MAX(0,入力!$D47-入力!$C$5)*入力!$P47,"")</f>
         <v/>
       </c>
       <c r="N60" s="4" t="str">
@@ -26462,37 +26036,37 @@
         <v/>
       </c>
       <c r="O60" s="5" t="str">
-        <f>IF(入力!$B56="","",IF(AND(NOT(ISNUMBER(G60)),NOT(ISNUMBER(M60))),"",IF(ISNUMBER(G60),G60,0)+IF(ISNUMBER(M60),M60,0)))</f>
+        <f>IF(入力!$B47="","",IF(AND(NOT(ISNUMBER(G60)),NOT(ISNUMBER(M60))),"",IF(ISNUMBER(G60),G60,0)+IF(ISNUMBER(M60),M60,0)))</f>
         <v/>
       </c>
       <c r="P60" s="4" t="str">
-        <f>IF(入力!$B56="","",IF(AND(NOT(ISNUMBER(H60)),NOT(ISNUMBER(N60))),"",IF(ISNUMBER(H60),H60,0)+IF(ISNUMBER(N60),N60,0)))</f>
+        <f>IF(入力!$B47="","",IF(AND(NOT(ISNUMBER(H60)),NOT(ISNUMBER(N60))),"",IF(ISNUMBER(H60),H60,0)+IF(ISNUMBER(N60),N60,0)))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="7" t="str">
-        <f>IF(入力!$B57="","",入力!$B57)</f>
+        <f>IF(入力!$B48="","",入力!$B48)</f>
         <v/>
       </c>
       <c r="C61" s="5" t="str">
-        <f>IF(入力!$B57="","",IF(ISNUMBER(入力!$C57),入力!$C57,""))</f>
+        <f>IF(入力!$B48="","",IF(ISNUMBER(入力!$C48),入力!$C48,""))</f>
         <v/>
       </c>
       <c r="D61" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C57),MAX(0,入力!$C57-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C48),MAX(0,入力!$C48-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E61" s="4" t="str">
-        <f>IF(入力!$B57="","",IF(ISNUMBER(入力!$O57),入力!$O57,""))</f>
+        <f>IF(入力!$B48="","",IF(ISNUMBER(入力!$O48),入力!$O48,""))</f>
         <v/>
       </c>
       <c r="F61" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C57),ISNUMBER(入力!$O57)),入力!$C57*入力!$O57,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C48),ISNUMBER(入力!$O48)),入力!$C48*入力!$O48,"")</f>
         <v/>
       </c>
       <c r="G61" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C57),ISNUMBER(入力!$O57)),MAX(0,入力!$C57-入力!$B$5)*入力!$O57,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C48),ISNUMBER(入力!$O48)),MAX(0,入力!$C48-入力!$B$5)*入力!$O48,"")</f>
         <v/>
       </c>
       <c r="H61" s="4" t="str">
@@ -26500,23 +26074,23 @@
         <v/>
       </c>
       <c r="I61" s="5" t="str">
-        <f>IF(入力!$B57="","",IF(ISNUMBER(入力!$D57),入力!$D57,""))</f>
+        <f>IF(入力!$B48="","",IF(ISNUMBER(入力!$D48),入力!$D48,""))</f>
         <v/>
       </c>
       <c r="J61" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D57),MAX(0,入力!$D57-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D48),MAX(0,入力!$D48-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K61" s="4" t="str">
-        <f>IF(入力!$B57="","",IF(ISNUMBER(入力!$P57),入力!$P57,""))</f>
+        <f>IF(入力!$B48="","",IF(ISNUMBER(入力!$P48),入力!$P48,""))</f>
         <v/>
       </c>
       <c r="L61" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D57),ISNUMBER(入力!$P57)),入力!$D57*入力!$P57,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D48),ISNUMBER(入力!$P48)),入力!$D48*入力!$P48,"")</f>
         <v/>
       </c>
       <c r="M61" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D57),ISNUMBER(入力!$P57)),MAX(0,入力!$D57-入力!$C$5)*入力!$P57,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D48),ISNUMBER(入力!$P48)),MAX(0,入力!$D48-入力!$C$5)*入力!$P48,"")</f>
         <v/>
       </c>
       <c r="N61" s="4" t="str">
@@ -26524,37 +26098,37 @@
         <v/>
       </c>
       <c r="O61" s="5" t="str">
-        <f>IF(入力!$B57="","",IF(AND(NOT(ISNUMBER(G61)),NOT(ISNUMBER(M61))),"",IF(ISNUMBER(G61),G61,0)+IF(ISNUMBER(M61),M61,0)))</f>
+        <f>IF(入力!$B48="","",IF(AND(NOT(ISNUMBER(G61)),NOT(ISNUMBER(M61))),"",IF(ISNUMBER(G61),G61,0)+IF(ISNUMBER(M61),M61,0)))</f>
         <v/>
       </c>
       <c r="P61" s="4" t="str">
-        <f>IF(入力!$B57="","",IF(AND(NOT(ISNUMBER(H61)),NOT(ISNUMBER(N61))),"",IF(ISNUMBER(H61),H61,0)+IF(ISNUMBER(N61),N61,0)))</f>
+        <f>IF(入力!$B48="","",IF(AND(NOT(ISNUMBER(H61)),NOT(ISNUMBER(N61))),"",IF(ISNUMBER(H61),H61,0)+IF(ISNUMBER(N61),N61,0)))</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="7" t="str">
-        <f>IF(入力!$B58="","",入力!$B58)</f>
+        <f>IF(入力!$B49="","",入力!$B49)</f>
         <v/>
       </c>
       <c r="C62" s="5" t="str">
-        <f>IF(入力!$B58="","",IF(ISNUMBER(入力!$C58),入力!$C58,""))</f>
+        <f>IF(入力!$B49="","",IF(ISNUMBER(入力!$C49),入力!$C49,""))</f>
         <v/>
       </c>
       <c r="D62" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$C58),MAX(0,入力!$C58-入力!$B$5),"")</f>
+        <f>IF(ISNUMBER(入力!$C49),MAX(0,入力!$C49-入力!$B$5),"")</f>
         <v/>
       </c>
       <c r="E62" s="4" t="str">
-        <f>IF(入力!$B58="","",IF(ISNUMBER(入力!$O58),入力!$O58,""))</f>
+        <f>IF(入力!$B49="","",IF(ISNUMBER(入力!$O49),入力!$O49,""))</f>
         <v/>
       </c>
       <c r="F62" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C58),ISNUMBER(入力!$O58)),入力!$C58*入力!$O58,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C49),ISNUMBER(入力!$O49)),入力!$C49*入力!$O49,"")</f>
         <v/>
       </c>
       <c r="G62" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$C58),ISNUMBER(入力!$O58)),MAX(0,入力!$C58-入力!$B$5)*入力!$O58,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$C49),ISNUMBER(入力!$O49)),MAX(0,入力!$C49-入力!$B$5)*入力!$O49,"")</f>
         <v/>
       </c>
       <c r="H62" s="4" t="str">
@@ -26562,23 +26136,23 @@
         <v/>
       </c>
       <c r="I62" s="5" t="str">
-        <f>IF(入力!$B58="","",IF(ISNUMBER(入力!$D58),入力!$D58,""))</f>
+        <f>IF(入力!$B49="","",IF(ISNUMBER(入力!$D49),入力!$D49,""))</f>
         <v/>
       </c>
       <c r="J62" s="5" t="str">
-        <f>IF(ISNUMBER(入力!$D58),MAX(0,入力!$D58-入力!$C$5),"")</f>
+        <f>IF(ISNUMBER(入力!$D49),MAX(0,入力!$D49-入力!$C$5),"")</f>
         <v/>
       </c>
       <c r="K62" s="4" t="str">
-        <f>IF(入力!$B58="","",IF(ISNUMBER(入力!$P58),入力!$P58,""))</f>
+        <f>IF(入力!$B49="","",IF(ISNUMBER(入力!$P49),入力!$P49,""))</f>
         <v/>
       </c>
       <c r="L62" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D58),ISNUMBER(入力!$P58)),入力!$D58*入力!$P58,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D49),ISNUMBER(入力!$P49)),入力!$D49*入力!$P49,"")</f>
         <v/>
       </c>
       <c r="M62" s="5" t="str">
-        <f>IF(AND(ISNUMBER(入力!$D58),ISNUMBER(入力!$P58)),MAX(0,入力!$D58-入力!$C$5)*入力!$P58,"")</f>
+        <f>IF(AND(ISNUMBER(入力!$D49),ISNUMBER(入力!$P49)),MAX(0,入力!$D49-入力!$C$5)*入力!$P49,"")</f>
         <v/>
       </c>
       <c r="N62" s="4" t="str">
@@ -26586,94 +26160,655 @@
         <v/>
       </c>
       <c r="O62" s="5" t="str">
-        <f>IF(入力!$B58="","",IF(AND(NOT(ISNUMBER(G62)),NOT(ISNUMBER(M62))),"",IF(ISNUMBER(G62),G62,0)+IF(ISNUMBER(M62),M62,0)))</f>
+        <f>IF(入力!$B49="","",IF(AND(NOT(ISNUMBER(G62)),NOT(ISNUMBER(M62))),"",IF(ISNUMBER(G62),G62,0)+IF(ISNUMBER(M62),M62,0)))</f>
         <v/>
       </c>
       <c r="P62" s="4" t="str">
-        <f>IF(入力!$B58="","",IF(AND(NOT(ISNUMBER(H62)),NOT(ISNUMBER(N62))),"",IF(ISNUMBER(H62),H62,0)+IF(ISNUMBER(N62),N62,0)))</f>
+        <f>IF(入力!$B49="","",IF(AND(NOT(ISNUMBER(H62)),NOT(ISNUMBER(N62))),"",IF(ISNUMBER(H62),H62,0)+IF(ISNUMBER(N62),N62,0)))</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="24" t="inlineStr">
+      <c r="B63" s="7" t="str">
+        <f>IF(入力!$B50="","",入力!$B50)</f>
+        <v/>
+      </c>
+      <c r="C63" s="5" t="str">
+        <f>IF(入力!$B50="","",IF(ISNUMBER(入力!$C50),入力!$C50,""))</f>
+        <v/>
+      </c>
+      <c r="D63" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$C50),MAX(0,入力!$C50-入力!$B$5),"")</f>
+        <v/>
+      </c>
+      <c r="E63" s="4" t="str">
+        <f>IF(入力!$B50="","",IF(ISNUMBER(入力!$O50),入力!$O50,""))</f>
+        <v/>
+      </c>
+      <c r="F63" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C50),ISNUMBER(入力!$O50)),入力!$C50*入力!$O50,"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C50),ISNUMBER(入力!$O50)),MAX(0,入力!$C50-入力!$B$5)*入力!$O50,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="4" t="str">
+        <f>IF(ISNUMBER(G63),ROUND(G63/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I63" s="5" t="str">
+        <f>IF(入力!$B50="","",IF(ISNUMBER(入力!$D50),入力!$D50,""))</f>
+        <v/>
+      </c>
+      <c r="J63" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D50),MAX(0,入力!$D50-入力!$C$5),"")</f>
+        <v/>
+      </c>
+      <c r="K63" s="4" t="str">
+        <f>IF(入力!$B50="","",IF(ISNUMBER(入力!$P50),入力!$P50,""))</f>
+        <v/>
+      </c>
+      <c r="L63" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D50),ISNUMBER(入力!$P50)),入力!$D50*入力!$P50,"")</f>
+        <v/>
+      </c>
+      <c r="M63" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D50),ISNUMBER(入力!$P50)),MAX(0,入力!$D50-入力!$C$5)*入力!$P50,"")</f>
+        <v/>
+      </c>
+      <c r="N63" s="4" t="str">
+        <f>IF(ISNUMBER(M63),ROUND(M63/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O63" s="5" t="str">
+        <f>IF(入力!$B50="","",IF(AND(NOT(ISNUMBER(G63)),NOT(ISNUMBER(M63))),"",IF(ISNUMBER(G63),G63,0)+IF(ISNUMBER(M63),M63,0)))</f>
+        <v/>
+      </c>
+      <c r="P63" s="4" t="str">
+        <f>IF(入力!$B50="","",IF(AND(NOT(ISNUMBER(H63)),NOT(ISNUMBER(N63))),"",IF(ISNUMBER(H63),H63,0)+IF(ISNUMBER(N63),N63,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="7" t="str">
+        <f>IF(入力!$B51="","",入力!$B51)</f>
+        <v/>
+      </c>
+      <c r="C64" s="5" t="str">
+        <f>IF(入力!$B51="","",IF(ISNUMBER(入力!$C51),入力!$C51,""))</f>
+        <v/>
+      </c>
+      <c r="D64" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$C51),MAX(0,入力!$C51-入力!$B$5),"")</f>
+        <v/>
+      </c>
+      <c r="E64" s="4" t="str">
+        <f>IF(入力!$B51="","",IF(ISNUMBER(入力!$O51),入力!$O51,""))</f>
+        <v/>
+      </c>
+      <c r="F64" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C51),ISNUMBER(入力!$O51)),入力!$C51*入力!$O51,"")</f>
+        <v/>
+      </c>
+      <c r="G64" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C51),ISNUMBER(入力!$O51)),MAX(0,入力!$C51-入力!$B$5)*入力!$O51,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="4" t="str">
+        <f>IF(ISNUMBER(G64),ROUND(G64/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I64" s="5" t="str">
+        <f>IF(入力!$B51="","",IF(ISNUMBER(入力!$D51),入力!$D51,""))</f>
+        <v/>
+      </c>
+      <c r="J64" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D51),MAX(0,入力!$D51-入力!$C$5),"")</f>
+        <v/>
+      </c>
+      <c r="K64" s="4" t="str">
+        <f>IF(入力!$B51="","",IF(ISNUMBER(入力!$P51),入力!$P51,""))</f>
+        <v/>
+      </c>
+      <c r="L64" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D51),ISNUMBER(入力!$P51)),入力!$D51*入力!$P51,"")</f>
+        <v/>
+      </c>
+      <c r="M64" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D51),ISNUMBER(入力!$P51)),MAX(0,入力!$D51-入力!$C$5)*入力!$P51,"")</f>
+        <v/>
+      </c>
+      <c r="N64" s="4" t="str">
+        <f>IF(ISNUMBER(M64),ROUND(M64/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O64" s="5" t="str">
+        <f>IF(入力!$B51="","",IF(AND(NOT(ISNUMBER(G64)),NOT(ISNUMBER(M64))),"",IF(ISNUMBER(G64),G64,0)+IF(ISNUMBER(M64),M64,0)))</f>
+        <v/>
+      </c>
+      <c r="P64" s="4" t="str">
+        <f>IF(入力!$B51="","",IF(AND(NOT(ISNUMBER(H64)),NOT(ISNUMBER(N64))),"",IF(ISNUMBER(H64),H64,0)+IF(ISNUMBER(N64),N64,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="7" t="str">
+        <f>IF(入力!$B52="","",入力!$B52)</f>
+        <v/>
+      </c>
+      <c r="C65" s="5" t="str">
+        <f>IF(入力!$B52="","",IF(ISNUMBER(入力!$C52),入力!$C52,""))</f>
+        <v/>
+      </c>
+      <c r="D65" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$C52),MAX(0,入力!$C52-入力!$B$5),"")</f>
+        <v/>
+      </c>
+      <c r="E65" s="4" t="str">
+        <f>IF(入力!$B52="","",IF(ISNUMBER(入力!$O52),入力!$O52,""))</f>
+        <v/>
+      </c>
+      <c r="F65" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C52),ISNUMBER(入力!$O52)),入力!$C52*入力!$O52,"")</f>
+        <v/>
+      </c>
+      <c r="G65" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C52),ISNUMBER(入力!$O52)),MAX(0,入力!$C52-入力!$B$5)*入力!$O52,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="4" t="str">
+        <f>IF(ISNUMBER(G65),ROUND(G65/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I65" s="5" t="str">
+        <f>IF(入力!$B52="","",IF(ISNUMBER(入力!$D52),入力!$D52,""))</f>
+        <v/>
+      </c>
+      <c r="J65" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D52),MAX(0,入力!$D52-入力!$C$5),"")</f>
+        <v/>
+      </c>
+      <c r="K65" s="4" t="str">
+        <f>IF(入力!$B52="","",IF(ISNUMBER(入力!$P52),入力!$P52,""))</f>
+        <v/>
+      </c>
+      <c r="L65" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D52),ISNUMBER(入力!$P52)),入力!$D52*入力!$P52,"")</f>
+        <v/>
+      </c>
+      <c r="M65" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D52),ISNUMBER(入力!$P52)),MAX(0,入力!$D52-入力!$C$5)*入力!$P52,"")</f>
+        <v/>
+      </c>
+      <c r="N65" s="4" t="str">
+        <f>IF(ISNUMBER(M65),ROUND(M65/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O65" s="5" t="str">
+        <f>IF(入力!$B52="","",IF(AND(NOT(ISNUMBER(G65)),NOT(ISNUMBER(M65))),"",IF(ISNUMBER(G65),G65,0)+IF(ISNUMBER(M65),M65,0)))</f>
+        <v/>
+      </c>
+      <c r="P65" s="4" t="str">
+        <f>IF(入力!$B52="","",IF(AND(NOT(ISNUMBER(H65)),NOT(ISNUMBER(N65))),"",IF(ISNUMBER(H65),H65,0)+IF(ISNUMBER(N65),N65,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="7" t="str">
+        <f>IF(入力!$B53="","",入力!$B53)</f>
+        <v/>
+      </c>
+      <c r="C66" s="5" t="str">
+        <f>IF(入力!$B53="","",IF(ISNUMBER(入力!$C53),入力!$C53,""))</f>
+        <v/>
+      </c>
+      <c r="D66" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$C53),MAX(0,入力!$C53-入力!$B$5),"")</f>
+        <v/>
+      </c>
+      <c r="E66" s="4" t="str">
+        <f>IF(入力!$B53="","",IF(ISNUMBER(入力!$O53),入力!$O53,""))</f>
+        <v/>
+      </c>
+      <c r="F66" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C53),ISNUMBER(入力!$O53)),入力!$C53*入力!$O53,"")</f>
+        <v/>
+      </c>
+      <c r="G66" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C53),ISNUMBER(入力!$O53)),MAX(0,入力!$C53-入力!$B$5)*入力!$O53,"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="4" t="str">
+        <f>IF(ISNUMBER(G66),ROUND(G66/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I66" s="5" t="str">
+        <f>IF(入力!$B53="","",IF(ISNUMBER(入力!$D53),入力!$D53,""))</f>
+        <v/>
+      </c>
+      <c r="J66" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D53),MAX(0,入力!$D53-入力!$C$5),"")</f>
+        <v/>
+      </c>
+      <c r="K66" s="4" t="str">
+        <f>IF(入力!$B53="","",IF(ISNUMBER(入力!$P53),入力!$P53,""))</f>
+        <v/>
+      </c>
+      <c r="L66" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D53),ISNUMBER(入力!$P53)),入力!$D53*入力!$P53,"")</f>
+        <v/>
+      </c>
+      <c r="M66" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D53),ISNUMBER(入力!$P53)),MAX(0,入力!$D53-入力!$C$5)*入力!$P53,"")</f>
+        <v/>
+      </c>
+      <c r="N66" s="4" t="str">
+        <f>IF(ISNUMBER(M66),ROUND(M66/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O66" s="5" t="str">
+        <f>IF(入力!$B53="","",IF(AND(NOT(ISNUMBER(G66)),NOT(ISNUMBER(M66))),"",IF(ISNUMBER(G66),G66,0)+IF(ISNUMBER(M66),M66,0)))</f>
+        <v/>
+      </c>
+      <c r="P66" s="4" t="str">
+        <f>IF(入力!$B53="","",IF(AND(NOT(ISNUMBER(H66)),NOT(ISNUMBER(N66))),"",IF(ISNUMBER(H66),H66,0)+IF(ISNUMBER(N66),N66,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="7" t="str">
+        <f>IF(入力!$B54="","",入力!$B54)</f>
+        <v/>
+      </c>
+      <c r="C67" s="5" t="str">
+        <f>IF(入力!$B54="","",IF(ISNUMBER(入力!$C54),入力!$C54,""))</f>
+        <v/>
+      </c>
+      <c r="D67" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$C54),MAX(0,入力!$C54-入力!$B$5),"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="4" t="str">
+        <f>IF(入力!$B54="","",IF(ISNUMBER(入力!$O54),入力!$O54,""))</f>
+        <v/>
+      </c>
+      <c r="F67" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C54),ISNUMBER(入力!$O54)),入力!$C54*入力!$O54,"")</f>
+        <v/>
+      </c>
+      <c r="G67" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C54),ISNUMBER(入力!$O54)),MAX(0,入力!$C54-入力!$B$5)*入力!$O54,"")</f>
+        <v/>
+      </c>
+      <c r="H67" s="4" t="str">
+        <f>IF(ISNUMBER(G67),ROUND(G67/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I67" s="5" t="str">
+        <f>IF(入力!$B54="","",IF(ISNUMBER(入力!$D54),入力!$D54,""))</f>
+        <v/>
+      </c>
+      <c r="J67" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D54),MAX(0,入力!$D54-入力!$C$5),"")</f>
+        <v/>
+      </c>
+      <c r="K67" s="4" t="str">
+        <f>IF(入力!$B54="","",IF(ISNUMBER(入力!$P54),入力!$P54,""))</f>
+        <v/>
+      </c>
+      <c r="L67" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D54),ISNUMBER(入力!$P54)),入力!$D54*入力!$P54,"")</f>
+        <v/>
+      </c>
+      <c r="M67" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D54),ISNUMBER(入力!$P54)),MAX(0,入力!$D54-入力!$C$5)*入力!$P54,"")</f>
+        <v/>
+      </c>
+      <c r="N67" s="4" t="str">
+        <f>IF(ISNUMBER(M67),ROUND(M67/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O67" s="5" t="str">
+        <f>IF(入力!$B54="","",IF(AND(NOT(ISNUMBER(G67)),NOT(ISNUMBER(M67))),"",IF(ISNUMBER(G67),G67,0)+IF(ISNUMBER(M67),M67,0)))</f>
+        <v/>
+      </c>
+      <c r="P67" s="4" t="str">
+        <f>IF(入力!$B54="","",IF(AND(NOT(ISNUMBER(H67)),NOT(ISNUMBER(N67))),"",IF(ISNUMBER(H67),H67,0)+IF(ISNUMBER(N67),N67,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="7" t="str">
+        <f>IF(入力!$B55="","",入力!$B55)</f>
+        <v/>
+      </c>
+      <c r="C68" s="5" t="str">
+        <f>IF(入力!$B55="","",IF(ISNUMBER(入力!$C55),入力!$C55,""))</f>
+        <v/>
+      </c>
+      <c r="D68" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$C55),MAX(0,入力!$C55-入力!$B$5),"")</f>
+        <v/>
+      </c>
+      <c r="E68" s="4" t="str">
+        <f>IF(入力!$B55="","",IF(ISNUMBER(入力!$O55),入力!$O55,""))</f>
+        <v/>
+      </c>
+      <c r="F68" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C55),ISNUMBER(入力!$O55)),入力!$C55*入力!$O55,"")</f>
+        <v/>
+      </c>
+      <c r="G68" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C55),ISNUMBER(入力!$O55)),MAX(0,入力!$C55-入力!$B$5)*入力!$O55,"")</f>
+        <v/>
+      </c>
+      <c r="H68" s="4" t="str">
+        <f>IF(ISNUMBER(G68),ROUND(G68/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I68" s="5" t="str">
+        <f>IF(入力!$B55="","",IF(ISNUMBER(入力!$D55),入力!$D55,""))</f>
+        <v/>
+      </c>
+      <c r="J68" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D55),MAX(0,入力!$D55-入力!$C$5),"")</f>
+        <v/>
+      </c>
+      <c r="K68" s="4" t="str">
+        <f>IF(入力!$B55="","",IF(ISNUMBER(入力!$P55),入力!$P55,""))</f>
+        <v/>
+      </c>
+      <c r="L68" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D55),ISNUMBER(入力!$P55)),入力!$D55*入力!$P55,"")</f>
+        <v/>
+      </c>
+      <c r="M68" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D55),ISNUMBER(入力!$P55)),MAX(0,入力!$D55-入力!$C$5)*入力!$P55,"")</f>
+        <v/>
+      </c>
+      <c r="N68" s="4" t="str">
+        <f>IF(ISNUMBER(M68),ROUND(M68/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O68" s="5" t="str">
+        <f>IF(入力!$B55="","",IF(AND(NOT(ISNUMBER(G68)),NOT(ISNUMBER(M68))),"",IF(ISNUMBER(G68),G68,0)+IF(ISNUMBER(M68),M68,0)))</f>
+        <v/>
+      </c>
+      <c r="P68" s="4" t="str">
+        <f>IF(入力!$B55="","",IF(AND(NOT(ISNUMBER(H68)),NOT(ISNUMBER(N68))),"",IF(ISNUMBER(H68),H68,0)+IF(ISNUMBER(N68),N68,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="7" t="str">
+        <f>IF(入力!$B56="","",入力!$B56)</f>
+        <v/>
+      </c>
+      <c r="C69" s="5" t="str">
+        <f>IF(入力!$B56="","",IF(ISNUMBER(入力!$C56),入力!$C56,""))</f>
+        <v/>
+      </c>
+      <c r="D69" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$C56),MAX(0,入力!$C56-入力!$B$5),"")</f>
+        <v/>
+      </c>
+      <c r="E69" s="4" t="str">
+        <f>IF(入力!$B56="","",IF(ISNUMBER(入力!$O56),入力!$O56,""))</f>
+        <v/>
+      </c>
+      <c r="F69" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C56),ISNUMBER(入力!$O56)),入力!$C56*入力!$O56,"")</f>
+        <v/>
+      </c>
+      <c r="G69" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C56),ISNUMBER(入力!$O56)),MAX(0,入力!$C56-入力!$B$5)*入力!$O56,"")</f>
+        <v/>
+      </c>
+      <c r="H69" s="4" t="str">
+        <f>IF(ISNUMBER(G69),ROUND(G69/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I69" s="5" t="str">
+        <f>IF(入力!$B56="","",IF(ISNUMBER(入力!$D56),入力!$D56,""))</f>
+        <v/>
+      </c>
+      <c r="J69" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D56),MAX(0,入力!$D56-入力!$C$5),"")</f>
+        <v/>
+      </c>
+      <c r="K69" s="4" t="str">
+        <f>IF(入力!$B56="","",IF(ISNUMBER(入力!$P56),入力!$P56,""))</f>
+        <v/>
+      </c>
+      <c r="L69" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D56),ISNUMBER(入力!$P56)),入力!$D56*入力!$P56,"")</f>
+        <v/>
+      </c>
+      <c r="M69" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D56),ISNUMBER(入力!$P56)),MAX(0,入力!$D56-入力!$C$5)*入力!$P56,"")</f>
+        <v/>
+      </c>
+      <c r="N69" s="4" t="str">
+        <f>IF(ISNUMBER(M69),ROUND(M69/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O69" s="5" t="str">
+        <f>IF(入力!$B56="","",IF(AND(NOT(ISNUMBER(G69)),NOT(ISNUMBER(M69))),"",IF(ISNUMBER(G69),G69,0)+IF(ISNUMBER(M69),M69,0)))</f>
+        <v/>
+      </c>
+      <c r="P69" s="4" t="str">
+        <f>IF(入力!$B56="","",IF(AND(NOT(ISNUMBER(H69)),NOT(ISNUMBER(N69))),"",IF(ISNUMBER(H69),H69,0)+IF(ISNUMBER(N69),N69,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="7" t="str">
+        <f>IF(入力!$B57="","",入力!$B57)</f>
+        <v/>
+      </c>
+      <c r="C70" s="5" t="str">
+        <f>IF(入力!$B57="","",IF(ISNUMBER(入力!$C57),入力!$C57,""))</f>
+        <v/>
+      </c>
+      <c r="D70" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$C57),MAX(0,入力!$C57-入力!$B$5),"")</f>
+        <v/>
+      </c>
+      <c r="E70" s="4" t="str">
+        <f>IF(入力!$B57="","",IF(ISNUMBER(入力!$O57),入力!$O57,""))</f>
+        <v/>
+      </c>
+      <c r="F70" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C57),ISNUMBER(入力!$O57)),入力!$C57*入力!$O57,"")</f>
+        <v/>
+      </c>
+      <c r="G70" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C57),ISNUMBER(入力!$O57)),MAX(0,入力!$C57-入力!$B$5)*入力!$O57,"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="4" t="str">
+        <f>IF(ISNUMBER(G70),ROUND(G70/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I70" s="5" t="str">
+        <f>IF(入力!$B57="","",IF(ISNUMBER(入力!$D57),入力!$D57,""))</f>
+        <v/>
+      </c>
+      <c r="J70" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D57),MAX(0,入力!$D57-入力!$C$5),"")</f>
+        <v/>
+      </c>
+      <c r="K70" s="4" t="str">
+        <f>IF(入力!$B57="","",IF(ISNUMBER(入力!$P57),入力!$P57,""))</f>
+        <v/>
+      </c>
+      <c r="L70" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D57),ISNUMBER(入力!$P57)),入力!$D57*入力!$P57,"")</f>
+        <v/>
+      </c>
+      <c r="M70" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D57),ISNUMBER(入力!$P57)),MAX(0,入力!$D57-入力!$C$5)*入力!$P57,"")</f>
+        <v/>
+      </c>
+      <c r="N70" s="4" t="str">
+        <f>IF(ISNUMBER(M70),ROUND(M70/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O70" s="5" t="str">
+        <f>IF(入力!$B57="","",IF(AND(NOT(ISNUMBER(G70)),NOT(ISNUMBER(M70))),"",IF(ISNUMBER(G70),G70,0)+IF(ISNUMBER(M70),M70,0)))</f>
+        <v/>
+      </c>
+      <c r="P70" s="4" t="str">
+        <f>IF(入力!$B57="","",IF(AND(NOT(ISNUMBER(H70)),NOT(ISNUMBER(N70))),"",IF(ISNUMBER(H70),H70,0)+IF(ISNUMBER(N70),N70,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="7" t="str">
+        <f>IF(入力!$B58="","",入力!$B58)</f>
+        <v/>
+      </c>
+      <c r="C71" s="5" t="str">
+        <f>IF(入力!$B58="","",IF(ISNUMBER(入力!$C58),入力!$C58,""))</f>
+        <v/>
+      </c>
+      <c r="D71" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$C58),MAX(0,入力!$C58-入力!$B$5),"")</f>
+        <v/>
+      </c>
+      <c r="E71" s="4" t="str">
+        <f>IF(入力!$B58="","",IF(ISNUMBER(入力!$O58),入力!$O58,""))</f>
+        <v/>
+      </c>
+      <c r="F71" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C58),ISNUMBER(入力!$O58)),入力!$C58*入力!$O58,"")</f>
+        <v/>
+      </c>
+      <c r="G71" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$C58),ISNUMBER(入力!$O58)),MAX(0,入力!$C58-入力!$B$5)*入力!$O58,"")</f>
+        <v/>
+      </c>
+      <c r="H71" s="4" t="str">
+        <f>IF(ISNUMBER(G71),ROUND(G71/入力!$B$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="I71" s="5" t="str">
+        <f>IF(入力!$B58="","",IF(ISNUMBER(入力!$D58),入力!$D58,""))</f>
+        <v/>
+      </c>
+      <c r="J71" s="5" t="str">
+        <f>IF(ISNUMBER(入力!$D58),MAX(0,入力!$D58-入力!$C$5),"")</f>
+        <v/>
+      </c>
+      <c r="K71" s="4" t="str">
+        <f>IF(入力!$B58="","",IF(ISNUMBER(入力!$P58),入力!$P58,""))</f>
+        <v/>
+      </c>
+      <c r="L71" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D58),ISNUMBER(入力!$P58)),入力!$D58*入力!$P58,"")</f>
+        <v/>
+      </c>
+      <c r="M71" s="5" t="str">
+        <f>IF(AND(ISNUMBER(入力!$D58),ISNUMBER(入力!$P58)),MAX(0,入力!$D58-入力!$C$5)*入力!$P58,"")</f>
+        <v/>
+      </c>
+      <c r="N71" s="4" t="str">
+        <f>IF(ISNUMBER(M71),ROUND(M71/入力!$C$5,0),"")</f>
+        <v/>
+      </c>
+      <c r="O71" s="5" t="str">
+        <f>IF(入力!$B58="","",IF(AND(NOT(ISNUMBER(G71)),NOT(ISNUMBER(M71))),"",IF(ISNUMBER(G71),G71,0)+IF(ISNUMBER(M71),M71,0)))</f>
+        <v/>
+      </c>
+      <c r="P71" s="4" t="str">
+        <f>IF(入力!$B58="","",IF(AND(NOT(ISNUMBER(H71)),NOT(ISNUMBER(N71))),"",IF(ISNUMBER(H71),H71,0)+IF(ISNUMBER(N71),N71,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">合計 / 加重平均</t>
         </is>
       </c>
-      <c r="C63" s="5">
-        <f>IF(SUM(E13:E62)=0,"",SUM(F13:F62)/SUM(E13:E62))</f>
+      <c r="C72" s="5">
+        <f>IF(SUM(E22:E71)=0,"",SUM(F22:F71)/SUM(E22:E71))</f>
         <v>1.501798</v>
       </c>
-      <c r="D63" s="5">
-        <f>IF(C63="","",MAX(0,C63-入力!$B$5))</f>
+      <c r="D72" s="5">
+        <f>IF(C72="","",MAX(0,C72-入力!$B$5))</f>
         <v>0</v>
       </c>
-      <c r="E63" s="4">
-        <f>SUM(E13:E62)</f>
+      <c r="E72" s="4">
+        <f>SUM(E22:E71)</f>
         <v>19739</v>
       </c>
-      <c r="F63" s="5">
-        <f>SUM(F13:F62)</f>
+      <c r="F72" s="5">
+        <f>SUM(F22:F71)</f>
         <v>29644</v>
       </c>
-      <c r="G63" s="5">
-        <f>SUM(G13:G62)</f>
+      <c r="G72" s="5">
+        <f>SUM(G22:G71)</f>
         <v>1577</v>
       </c>
-      <c r="H63" s="4">
-        <f>SUM(H13:H62)</f>
+      <c r="H72" s="4">
+        <f>SUM(H22:H71)</f>
         <v>985</v>
       </c>
-      <c r="I63" s="5">
-        <f>IF(SUM(K13:K62)=0,"",SUM(L13:L62)/SUM(K13:K62))</f>
+      <c r="I72" s="5">
+        <f>IF(SUM(K22:K71)=0,"",SUM(L22:L71)/SUM(K22:K71))</f>
         <v>1.472862</v>
       </c>
-      <c r="J63" s="5">
-        <f>IF(I63="","",MAX(0,I63-入力!$C$5))</f>
+      <c r="J72" s="5">
+        <f>IF(I72="","",MAX(0,I72-入力!$C$5))</f>
         <v>0</v>
       </c>
-      <c r="K63" s="4">
-        <f>SUM(K13:K62)</f>
+      <c r="K72" s="4">
+        <f>SUM(K22:K71)</f>
         <v>20116</v>
       </c>
-      <c r="L63" s="5">
-        <f>SUM(L13:L62)</f>
+      <c r="L72" s="5">
+        <f>SUM(L22:L71)</f>
         <v>29628.1</v>
       </c>
-      <c r="M63" s="5">
-        <f>SUM(M13:M62)</f>
+      <c r="M72" s="5">
+        <f>SUM(M22:M71)</f>
         <v>2961.2</v>
       </c>
-      <c r="N63" s="4">
-        <f>SUM(N13:N62)</f>
+      <c r="N72" s="4">
+        <f>SUM(N22:N71)</f>
         <v>1850</v>
       </c>
-      <c r="O63" s="5">
-        <f>SUM(O13:O62)</f>
+      <c r="O72" s="5">
+        <f>SUM(O22:O71)</f>
         <v>4538.2</v>
       </c>
-      <c r="P63" s="4">
-        <f>SUM(P13:P62)</f>
+      <c r="P72" s="4">
+        <f>SUM(P22:P71)</f>
         <v>2835</v>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="35" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">※ 加重平均＝件数で重み付けした平均速度。追加可能件数＝短縮効果(分)÷目標1.6分/個＝全員が目標達成した場合、浮いた時間で追加処理できる件数の目安（0.5未満は四捨五入）。</t>
+          <t xml:space="preserve">※ 加重平均＝件数で重み付けした平均速度。追加可能件数＝短縮効果(分)÷目標1.6分/個（目標達成で浮いた時間に追加処理できる件数の目安、四捨五入）。全体サマリーは明細の合計。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
     <mergeCell ref="B1:P1"/>
     <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B10:P10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="I11:N11"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:B11"/>
+    <mergeCell ref="B17:P17"/>
+    <mergeCell ref="B19:P19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="I20:N20"/>
+    <mergeCell ref="O20:O21"/>
+    <mergeCell ref="P20:P21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
